--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1086,14 +1086,14 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>110990000</v>
+        <v>108990000</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>119990000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T03:40:11+00:00</t>
+          <t>2026-09-26T12:43:44+00:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:51</t>
+          <t>2026-09-27 12:18:44</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>111990000</v>
+        <v>104990000</v>
       </c>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T03:38:05+00:00</t>
+          <t>2026-09-27T02:33:50+00:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>138990000</v>
+        <v>133990000</v>
       </c>
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T16:24:52+00:00</t>
+          <t>2026-09-26T11:52:03+00:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:58:01</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
@@ -7265,22 +7265,20 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:50</t>
+          <t>2026-09-27 12:18:41</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion Pro 7 16IAX10H 83F5008WVN</t>
+          <t>Laptop ASUS ROG Strix G16 G614PW-TS051W</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>118990000</v>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>96990000</v>
-      </c>
+        <v>87990000</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr"/>
       <c r="D177" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -7290,36 +7288,36 @@
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 16 WQXGA 240Hz</t>
+          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5080 | Màn hình: 16" 2.5K</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f5008wvn</t>
+          <t>https://xgear.net/products/asus-rog-strix-g16-g614pw-ts051w</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T03:52:30+00:00</t>
+          <t>2026-09-06T09:37:41+00:00</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion Pro 7 16IAX10H 83F500ANVN (Ultra 9 275HX | RTX 5080 | 64GB | 1TB | 16 inch OLED)</t>
+          <t>Laptop Acer Gaming Aspire 7 A715 59G 79XF</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>156990000</v>
+        <v>26990000</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>81990000</v>
+        <v>22990000</v>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
@@ -7330,37 +7328,35 @@
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 16GB | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500anvn</t>
+          <t>https://xgear.net/products/laptop-acer-gaming-aspire-7-a715-59g-79xf</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T07:48:39+00:00</t>
+          <t>2026-09-19T07:14:43+00:00</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Legion Pro 7i FIFA World Cup 26™ Edition)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R7ZJ (Ryzen 7 AI 350 | RTX 5060 | 16GB | 512GB | 16 inch)</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>109790000</v>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>83990000</v>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr"/>
       <c r="D179" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -7370,37 +7366,35 @@
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti | Màn hình: 16" WQXGA 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: Ryzen 7 AI 350 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5060 8GB | Màn hình: 16" WQXGA 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://xgear.net/products/laptop-acer-gaming-nitro-propanel-an16s-61-r7zj-nh-qxfsv-002</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T03:48:03+00:00</t>
+          <t>2026-08-10T10:56:23+00:00</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15AHP10 83JG0047VN (Ryzen 7 250 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN (Ryzen 7 AI 350 | RTX 5070 | 16GB | 512GB | 16 inch)</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>32490000</v>
-      </c>
+        <v>53590000</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr"/>
       <c r="D180" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -7410,35 +7404,37 @@
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: Ryzen 7 AI 350 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5070 8GB | Màn hình: 16" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15ahp10-83jg0047vn</t>
+          <t>https://xgear.net/products/laptop-acer-gaming-nitro-propanel-an16s-61-r9cn-nh-qxgsv-001</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:37:32+00:00</t>
+          <t>2026-08-30T03:37:23+00:00</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7 250 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Acer Gaming Nitro V ANV15-41-R2UP (Ryzen 5 6600H, RTX 2050, 144Hz)</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C181" s="2" t="inlineStr"/>
+        <v>18990000</v>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>16990000</v>
+      </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -7448,111 +7444,113 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Acer | CPU: R5 6600H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 2050 | Màn hình: 15.6" FHD 165Hz</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn</t>
+          <t>https://xgear.net/products/laptop-acer-gaming-nitro-v-anv15-41-r2up</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T05:44:36+00:00</t>
+          <t>2026-09-19T02:51:52+00:00</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15APH8 82XT00BTVN</t>
+          <t>Laptop Gaming Acer Nitro 5 Eagle AN515 57 54MV / 553E</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>21890000</v>
+        <v>16590000</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>27362500</v>
+        <v>24990000</v>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-34%</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R5 7640HS | RAM: 16GB DDR5 | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: i5 11400H | RAM: 8GB DDR4 | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15aph8-82xt00btvn</t>
+          <t>https://xgear.net/products/laptop-acer-nitro-5-an515-57-54mv</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T15:56:06+00:00</t>
+          <t>2026-09-19T03:34:33+00:00</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0000GVN (R5 7535HS | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
+          <t>Laptop Gaming Acer Nitro 5 Tiger AN515 58 52SP i5 12500H/8GB/512GB/15.6F 144Hz/RTX3050 4GB/Win11</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>37990000</v>
-      </c>
-      <c r="C183" s="2" t="inlineStr"/>
+        <v>16490000</v>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>29490000</v>
+      </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-44%</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 5 7535HS | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Acer | CPU: i5 12500H | RAM: 8GB DDR4 | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp10e-83s0000gvn</t>
+          <t>https://xgear.net/products/laptop-acer-nitro-5-tiger-an515-58-52sp</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T07:23:54+00:00</t>
+          <t>2026-04-01T02:12:56+00:00</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000G7VN (Ryzen 5 150 | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Acer Nitro ProPanel ANV16-72-782F</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>35990000</v>
+        <v>37590000</v>
       </c>
       <c r="C184" s="2" t="inlineStr"/>
       <c r="D184" s="2" t="inlineStr">
@@ -7564,77 +7562,75 @@
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 5 150 | RAM: 16GB DDR5 | Ổ cứng: 512GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5050 | Màn hình: 16" WUXGA180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp10e-83s000g7vn</t>
+          <t>https://xgear.net/products/laptop-acer-nitro-propanel-anv16-72-782f</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T10:08:14+00:00</t>
+          <t>2026-08-10T10:45:39+00:00</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15ARP9 83JC00HXVN (Ryzen 5 7235HS, RTX 3050 6GB, 100% sRGB)</t>
+          <t>Laptop Acer Predator Helios 18 PH18 71 981G</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>21990000</v>
+        <v>79490000</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>27990000</v>
+        <v>79990000</v>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R5 7235HS | RAM: 12GB DDR5 | Ổ cứng: 512GB | VGA: Geforce RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: Intel Core i9 13900HX | RAM: DDR5 24GB (16GB+8GB) 5600MHz ; 2 slots | Ổ cứng: 2TB (2 x 1TB) SSD NVMe M.2 PCIe Gen 4 x 4 | VGA: Geforce RTX 4080 12GB Mux Swicth | Màn hình: 18" WQXGA (2560 x 1600) IPS 240Hz DCI-P3 100%</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp9-83jc00hxvn</t>
+          <t>https://xgear.net/products/laptop-acer-predator-helios-18-ph18-71-981g</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:38:48+00:00</t>
+          <t>2026-09-19T10:10:23+00:00</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15ARP9 83JC00LVVN (Ryzen 5 7235HS, RTX 3050 6GB, 100% sRGB)</t>
+          <t>Laptop ASUS ProArt P16 H7606WP SR335W (Ryzen AI 9 HX 370 | RTX 5070 | 64GB | 2TB | 16inch OLED)</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>27990000</v>
-      </c>
+        <v>119990000</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr"/>
       <c r="D186" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -7644,33 +7640,33 @@
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R5 7235HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: Geforce RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Asus | CPU: Ryzen™ AI 9 HX 370 | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5070 | Màn hình: 16" 3K OLED 120Hz</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp9-83jc00lvvn</t>
+          <t>https://xgear.net/products/laptop-asus-proart-p16-h7606wp-sr335w</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T03:04:10+00:00</t>
+          <t>2026-08-27T03:15:37+00:00</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IPH11 83SL000LVN (Ultra 7-356H | RTX 5060 | 16GB | 512 GB | 15.3 inch)</t>
+          <t>Laptop ASUS ProArt PX13 HN7306EA LX050W (Ryzen AI MAX+ 395 | Radeon Graphics | 32GB | 1TB | 3K OLED)</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>46990000</v>
+        <v>71990000</v>
       </c>
       <c r="C187" s="2" t="inlineStr"/>
       <c r="D187" s="2" t="inlineStr">
@@ -7682,33 +7678,33 @@
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7-356H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Asus | CPU: Ryzen™ AI 9 HX 370 | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: Radeon Graphics | Màn hình: 16" 3K OLED 120Hz</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15iph11-83sl000lvn</t>
+          <t>https://xgear.net/products/laptop-asus-proart-px13-hn7306ea-lx050w</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T05:06:31+00:00</t>
+          <t>2026-08-27T03:25:31+00:00</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IPH11E 83Y8000MVN (Ultra X7-358H | ARC B390 | 16GB | 512 GB | 15.3 inch WUXGA)</t>
+          <t>Laptop ASUS ROG Flow Z13 GZ302EAC-RU184WS (Ryzen AI MAX+ 395 | Radeon 8060S | 128GB | 1TB | 2.5K)</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>45990000</v>
+        <v>107490000</v>
       </c>
       <c r="C188" s="2" t="inlineStr"/>
       <c r="D188" s="2" t="inlineStr">
@@ -7720,73 +7716,73 @@
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra X7-358H | RAM: 16GB LPDDR5X-9600 | Ổ cứng: 512GB | VGA: Intel ARC B390 | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Asus | CPU: Ryzen AI Max+ 395 | RAM: 128GB LPDDR5X | Ổ cứng: 1TB SSD | VGA: Radeon 8060S | Màn hình: 13.4" WQXGA 180Hz</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15iph11e-83y8000mvn</t>
+          <t>https://xgear.net/products/laptop-asus-rog-flow-z13-gz302eac-ru184ws</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T07:13:36+00:00</t>
+          <t>2026-09-21T05:26:51+00:00</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRH8 82XV00QQVN</t>
+          <t>Laptop Gaming ASUS ROG Zephyrus G16 GU606AW TB121W (Ultra 9 386H | RTX 5080 | 32GB | 1TB | 16.0 WQXGA OLED 240Hz)</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>15990000</v>
+        <v>112590000</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>19987500</v>
+        <v>125990000</v>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 12450H | RAM: 8GB DDR5 | VGA: RTX 2050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Asus | CPU: Ultra 9 386H | RAM: 32GB | VGA: RTX 5080 16GB | Màn hình: 16" WQXGA OLED 240Hz</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irh8-82xv00qqvn</t>
+          <t>https://xgear.net/products/laptop-asus-rog-gu606aw-tb121w-u9</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T15:58:24+00:00</t>
+          <t>2026-09-18T04:28:17+00:00</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX10 83JE01N4VN (Core  i7-14650HX | RTX 5050 | 16GB | 512GB | 15.6 inch)</t>
+          <t>Laptop ASUS ROG Strix G16 G614PH-TS118W ( Ryzen 9 8940HX | 16GB  | 512GB | RTX 5050 )</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>53990000</v>
+        <v>46990000</v>
       </c>
       <c r="C190" s="2" t="inlineStr"/>
       <c r="D190" s="2" t="inlineStr">
@@ -7798,37 +7794,35 @@
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7-14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" 2.5K</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx10-83je01n4vn</t>
+          <t>https://xgear.net/products/laptop-asus-rog-strix-g16-g614ph-ts118w</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T10:15:20+00:00</t>
+          <t>2026-09-24T05:18:00+00:00</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV003CVN (Core i5 | RTX 3050 |16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9 8940HX | RTX 5060 | 16GB | 512GB | 2.5K 300Hz)</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>29690000</v>
-      </c>
-      <c r="C191" s="2" t="n">
-        <v>25490000</v>
-      </c>
+        <v>51990000</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr"/>
       <c r="D191" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -7838,37 +7832,35 @@
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" 2.5K 240Hz</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv003cvn</t>
+          <t>https://xgear.net/products/laptop-asus-rog-strix-g16-g614pm-ts147w</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T07:21:55+00:00</t>
+          <t>2026-09-16T05:00:50+00:00</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01ALVN (Core i7-13650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop ASUS ROG Strix G16 G614PP-TS112W</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C192" s="2" t="n">
-        <v>29990000</v>
-      </c>
+        <v>56990000</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr"/>
       <c r="D192" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -7878,33 +7870,33 @@
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5070 | Màn hình: 16" 2.5K</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://xgear.net/products/laptop-asus-rog-strix-g16-g614pp-ts112w</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:58:13+00:00</t>
+          <t>2026-09-19T06:37:14+00:00</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01H2VN (Core i7-13650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop ASUS ROG Strix G16 G614PR TS103W (Ryzen 9 8940HX | RTX 5070Ti | 16GB | 512GB | 16 inch 2.5K 100% sRGB)</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>33990000</v>
+        <v>66990000</v>
       </c>
       <c r="C193" s="2" t="inlineStr"/>
       <c r="D193" s="2" t="inlineStr">
@@ -7916,33 +7908,33 @@
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5070Ti | Màn hình: 16" 2.5K</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01h2vn</t>
+          <t>https://xgear.net/products/laptop-asus-rog-strix-g16-g614pr-ts103w</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T05:38:14+00:00</t>
+          <t>2026-09-03T06:20:24+00:00</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01H3VN (Core i7-13645HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop ASUS ROG Zephyrus G14 GU405AW-SY029W (Ultra 9 386H | RTX 5080 | 32GB | 1TB | 14 inch)</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>34590000</v>
+        <v>109990000</v>
       </c>
       <c r="C194" s="2" t="inlineStr"/>
       <c r="D194" s="2" t="inlineStr">
@@ -7954,33 +7946,33 @@
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13645HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 14" 3K OLED 120Hz</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01h3vn</t>
+          <t>https://xgear.net/products/laptop-asus-rog-zephyrus-g14-gu405aw-sy029w</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T13:24:18+00:00</t>
+          <t>2026-09-06T04:46:37+00:00</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01MCVN (Core i7-14650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming ASUS ROG Zephyrus G16 GU606AW TB052WS (Ultra 9 386H | RTX 5080 | 64GB | 1TB | 16.0 inch OLED 240Hz)</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>46990000</v>
+        <v>130990000</v>
       </c>
       <c r="C195" s="2" t="inlineStr"/>
       <c r="D195" s="2" t="inlineStr">
@@ -7992,37 +7984,35 @@
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Asus | CPU: Ultra 9 386H | RAM: 64GB DR5X | VGA: RTX 5080 16GB | Màn hình: 16" WQXGA OLED 240Hz</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01mcvn</t>
+          <t>https://xgear.net/products/laptop-asus-rog-zephyrus-gu606aw-tb052ws</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T04:06:56+00:00</t>
+          <t>2026-09-12T05:14:49+00:00</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0006QVN (Ryzen 7 | RTX 3050 | 16GB | 512GB | 144Hz)</t>
+          <t>Laptop Asus TUF F16 FX608JHI-TU210W (Intel Core i5-14450HX | RTX  5050 | 16GB | 512GB | 16 inch WUXGA)</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>25490000</v>
-      </c>
-      <c r="C196" s="2" t="n">
-        <v>23990000</v>
-      </c>
+        <v>39890000</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr"/>
       <c r="D196" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8032,37 +8022,35 @@
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: i5-14450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" FHD+ 144Hz</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10-83s0006qvn</t>
+          <t>https://xgear.net/products/laptop-asus-tuf-f16-fx608jhi-tu210w</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:39:28+00:00</t>
+          <t>2026-08-11T05:16:27+00:00</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo LOQ 15ARP10E 83S0004FVN ( Ryzen 7 7735HS | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming ASUS TUF A16 FA608UHI TU121W (Ryzen 7 260 | 16GB | 512GB | RTX 5050 | 16 inch)</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>34590000</v>
-      </c>
-      <c r="C197" s="2" t="n">
-        <v>26990000</v>
-      </c>
+        <v>44990000</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr"/>
       <c r="D197" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8072,33 +8060,33 @@
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Asus | CPU: Ryzen 7 260 | RAM: 16GB DDR5 | VGA: RTX 5050 8GB | Màn hình: 16" FHD+ 144Hz</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0004fvn</t>
+          <t>https://xgear.net/products/laptop-asus-tuf-fa608uhi-tu121w</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T05:06:41+00:00</t>
+          <t>2026-09-23T04:16:14+00:00</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0006RVN</t>
+          <t>Laptop ASUS TUF Gaming A14 FA401EA-RG034W (Ryzen AI MAX+ 392 | Radeon 8060S | 64GB | 1TB | 2.5K)</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>29990000</v>
+        <v>59390000</v>
       </c>
       <c r="C198" s="2" t="inlineStr"/>
       <c r="D198" s="2" t="inlineStr">
@@ -8110,73 +8098,71 @@
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: Ryzen™ AI MAX+ 392 | RAM: 64GB LPDDR5X | Ổ cứng: 1TB Gen 4 | VGA: Radeon 8060S | Màn hình: 14" 2.5K 165Hz</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0006rvn</t>
+          <t>https://xgear.net/products/laptop-asus-tuf-gaming-a14-fa401ea-rg034w</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T08:27:17+00:00</t>
+          <t>2026-08-15T05:05:13+00:00</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0007AVN</t>
+          <t>Laptop ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465 | RTX 5060 | 32GB | 1TB | 2.5K)</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="C199" s="2" t="n">
-        <v>31490000</v>
-      </c>
+        <v>53990000</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr"/>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr"/>
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: Ryzen AI 9 465 | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" 2K 165Hz</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0007avn</t>
+          <t>https://xgear.net/products/laptop-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:38:09+00:00</t>
+          <t>2026-08-10T13:45:19+00:00</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S000DCVN ( Ryzen 7 - 170 | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
+          <t>Laptop Asus TUF Gaming A15 FA506NCG-HN329W (Ryzen 7 8845HS | RTX 3050 | 16GB | 512GB | FHD)</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>28990000</v>
+        <v>26990000</v>
       </c>
       <c r="C200" s="2" t="inlineStr"/>
       <c r="D200" s="2" t="inlineStr">
@@ -8188,33 +8174,33 @@
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 170 | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: R7 8845HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 4GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s000dcvn</t>
+          <t>https://xgear.net/products/laptop-asus-tuf-gaming-a15-fa506ncg-hn329w</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T06:01:38+00:00</t>
+          <t>2026-09-24T05:36:08+00:00</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003XVN (Core 7 230H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming ASUS TUF A16 FA608UMI TU162W (Ryzen 7 260 | 16GB| 512GB| RTX 5060 | 16 inch)</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>41990000</v>
+        <v>46990000</v>
       </c>
       <c r="C201" s="2" t="inlineStr"/>
       <c r="D201" s="2" t="inlineStr">
@@ -8226,33 +8212,33 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: Ryzen 7 260 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5060 8GB | Màn hình: 16" FHD+ 144Hz</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003xvn</t>
+          <t>https://xgear.net/products/laptop-asus-tuf-gaming-a16-fa608umi-tu162w</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T05:57:43+00:00</t>
+          <t>2026-09-19T06:46:47+00:00</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003YVN (Core 7 230H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming ASUS TUF A14 FA401EA RG041W (Ryzen AI MAX+ 392 | Radeon 8060S| 32GB | 512GB | 14 inch)</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>36490000</v>
+        <v>54990000</v>
       </c>
       <c r="C202" s="2" t="inlineStr"/>
       <c r="D202" s="2" t="inlineStr">
@@ -8264,37 +8250,35 @@
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: Ryzen AI MAX+ 392 | RAM: 32GB LPDDR5X | VGA: Radeon 8060S | Màn hình: 14" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003yvn</t>
+          <t>https://xgear.net/products/laptop-asus-tuf-gaming-fa401ea-rg041w</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T05:58:44+00:00</t>
+          <t>2026-09-19T08:21:12+00:00</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRX11 83SC003RVN (i5-13450HX | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop ASUS Zenbook DUO UX8407AA-SN138WS (Ultra X9 388H | Arc™ Graphics | 32 GB | 1TB | 14 inch)</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="C203" s="2" t="n">
-        <v>28490000</v>
-      </c>
+        <v>87990000</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr"/>
       <c r="D203" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8304,33 +8288,33 @@
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: Ultra X9 388H | RAM: 32GB LPDDR5X | Ổ cứng: 1TB SSD | VGA: Arc Graphics | Màn hình: 14" 3K OLED 144Hz</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irx11-83sc003rvn</t>
+          <t>https://xgear.net/products/laptop-asus-zenbook-duo-ux8407aa-sn138ws</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T05:38:36+00:00</t>
+          <t>2026-07-24T09:23:55+00:00</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003VVN (Core 5 205H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
+          <t>Laptop ASUS Zenbook DUO UX8407AA-SN439WS (Ultra X7 358H | Arc Graphics | 32 GB | 512GB | 14 inch)</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>35990000</v>
+        <v>77990000</v>
       </c>
       <c r="C204" s="2" t="inlineStr"/>
       <c r="D204" s="2" t="inlineStr">
@@ -8342,35 +8326,37 @@
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
+          <t>Thương hiệu: Asus | CPU: Ultra X7 358H | RAM: 32GB LPDDR5X | Ổ cứng: 512GB SSD | VGA: Arc Graphics | Màn hình: 14" 3K OLED 144Hz</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003vvn</t>
+          <t>https://xgear.net/products/laptop-asus-zenbook-duo-ux8407aa-sn439ws</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T02:46:40+00:00</t>
+          <t>2026-08-13T05:49:21+00:00</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential LOQ 15IRH11E 83Y9003WVN (Core 5 205H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Acer Aspire 7 A715 59G 53GZ</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C205" s="2" t="inlineStr"/>
+        <v>24990000</v>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>22990000</v>
+      </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8380,37 +8366,35 @@
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
+          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003wvn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T05:03:38+00:00</t>
+          <t>2026-09-19T07:16:51+00:00</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX AI D2XWFKG-036VN (Ultra 7 | RTX 5060 | 16GB | 1TB | 2K)</t>
+          <t>Laptop Gaming Acer Aspire 7 A715-59G-59RD NH.DXUSV.001 (Core 5 210H | RTX 3050 | 16GB | 512GB | 144Hz)</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C206" s="2" t="n">
-        <v>44990000</v>
-      </c>
+        <v>24490000</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr"/>
       <c r="D206" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8420,35 +8404,37 @@
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 4GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-ai-d2xwfkg-036vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T04:38:20+00:00</t>
+          <t>2026-09-26T09:09:52+00:00</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WFK-074VN (i7 14650HX | 16GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming Acer Aspire 7 A715 59G 73LB</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>52490000</v>
-      </c>
-      <c r="C207" s="2" t="inlineStr"/>
+        <v>22990000</v>
+      </c>
+      <c r="C207" s="2" t="n">
+        <v>22990000</v>
+      </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8458,35 +8444,37 @@
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: i7 12650H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-074vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-aspire-7-a715-59g-73lb</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T09:48:44+00:00</t>
+          <t>2026-09-20T09:29:29+00:00</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14VFK-075VN (i9 14900HX | 32GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming Acer Aspire 7 A715 59G 78WG</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>60990000</v>
-      </c>
-      <c r="C208" s="2" t="inlineStr"/>
+        <v>25890000</v>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>22990000</v>
+      </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8496,35 +8484,37 @@
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-075vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T10:30:50+00:00</t>
+          <t>2026-09-19T07:17:39+00:00</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 076VN (Core i9-14900HX | RTX 5050 | 32GB | 1TB SSD | QHD+)</t>
+          <t>Laptop Gaming Acer Nitro 16 AI ProPanel AN16S 61 R5F4</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>56790000</v>
-      </c>
-      <c r="C209" s="2" t="inlineStr"/>
+        <v>45990000</v>
+      </c>
+      <c r="C209" s="2" t="n">
+        <v>30990000</v>
+      </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8534,33 +8524,33 @@
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" FHD+ 180Hz</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-076vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:48:15+00:00</t>
+          <t>2026-07-02T07:45:59+00:00</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 077VN (Core i7 14650HX | RTX 5050 | 16GB | 512GB | 16 inch)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS | RTX 4050 | 16GB | 512GB | 15.6inch FHD)</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>49990000</v>
+        <v>32990000</v>
       </c>
       <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="inlineStr">
@@ -8572,111 +8562,117 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: R5 7640HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-077vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-anv15-42-r5ef</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T09:44:38+00:00</t>
+          <t>2026-09-12T02:51:12+00:00</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WGK</t>
+          <t>Laptop Gaming Nitro ProPanel ANV16S-71-58WQ</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>69990000</v>
-      </c>
-      <c r="C211" s="2" t="inlineStr"/>
+        <v>38990000</v>
+      </c>
+      <c r="C211" s="2" t="n">
+        <v>44990000</v>
+      </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr"/>
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 8GB | Màn hình: 16" 2K+ 180Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wgk</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-anv16s-71-58wq</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T04:42:13+00:00</t>
+          <t>2026-08-10T10:24:36+00:00</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-051VN (Ultra 9 290HX Plus | 32GB | 1TB | RTX 5070 12GB | 16 inch)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV16-72-71T9</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>70990000</v>
-      </c>
-      <c r="C212" s="2" t="inlineStr"/>
+        <v>42990000</v>
+      </c>
+      <c r="C212" s="2" t="n">
+        <v>44990000</v>
+      </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ Oled 165Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16inch FHD+</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-051vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-anv16s-71-71t9</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T09:46:40+00:00</t>
+          <t>2026-09-13T04:23:28+00:00</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-052VN  (Ultra 7 251HX | 16GB | 1TB | RTX 5070 12GB | 16 inch OLED 165Hz )</t>
+          <t>Laptop Gaming Acer Nitro Lite 16 NL16 71G 56WQ (Intel Core i5-13420H, RTX 3050 6GB, 165Hz)</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>60990000</v>
-      </c>
-      <c r="C213" s="2" t="inlineStr"/>
+        <v>24490000</v>
+      </c>
+      <c r="C213" s="2" t="n">
+        <v>22990000</v>
+      </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8686,35 +8682,37 @@
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 251HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ OLED 165Hz</t>
+          <t>Thương hiệu: Acer | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 16" FHD+ 165Hz</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-052vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T09:47:42+00:00</t>
+          <t>2026-09-19T02:27:35+00:00</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
+          <t>Laptop Gaming Acer Nitro Lite 16 NL16-71G 71FN</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>64990000</v>
-      </c>
-      <c r="C214" s="2" t="inlineStr"/>
+        <v>29990000</v>
+      </c>
+      <c r="C214" s="2" t="n">
+        <v>22990000</v>
+      </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8724,35 +8722,37 @@
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 | Màn hình: 16" FHD+ 165Hz</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71fn</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T07:15:48+00:00</t>
+          <t>2026-08-21T02:47:46+00:00</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
+          <t>Laptop Gaming Acer Nitro Lite 16 NL16 71G 71UJ (Core i7 | RTX 3050 | 16GB | 512GB | 16 inch)</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>56990000</v>
-      </c>
-      <c r="C215" s="2" t="inlineStr"/>
+        <v>27990000</v>
+      </c>
+      <c r="C215" s="2" t="n">
+        <v>22990000</v>
+      </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8762,33 +8762,33 @@
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 7 8840HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 16" FHD+ 165Hz</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk-1</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71uj</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T07:16:04+00:00</t>
+          <t>2026-07-17T02:40:44+00:00</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WGK-067VN (Ryzen 9 8940HX | RTX 5060 | 16GB | 1TB | 16inch QHD+)</t>
+          <t>Laptop Gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS | RTX 4050 | 16GB | 512GB | 15.6inch)</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>59990000</v>
+        <v>34590000</v>
       </c>
       <c r="C216" s="2" t="inlineStr"/>
       <c r="D216" s="2" t="inlineStr">
@@ -8800,33 +8800,33 @@
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI</t>
+          <t>Thương hiệu: Acer | CPU: Ryzen 7 7445HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wgk-067vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T08:26:26+00:00</t>
+          <t>2026-08-04T10:57:57+00:00</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WGK-093VN (Ryzen 9 8940HX | RTX 5070 | 16GB | 1TB | 16inch QHD+)</t>
+          <t>Laptop Gaming Acer Nitro ProPanel ANV15-52-50RB (Intel Core 5 210H | RTX 4050 | 16GB | 512GB | 15.6 inch)</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>65990000</v>
+        <v>33490000</v>
       </c>
       <c r="C217" s="2" t="inlineStr"/>
       <c r="D217" s="2" t="inlineStr">
@@ -8838,33 +8838,33 @@
       <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI</t>
+          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wgk-093vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-propanel-anv15-52-50rb</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T08:28:22+00:00</t>
+          <t>2026-08-05T04:22:14+00:00</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 A13VEK 2089VN</t>
+          <t>Laptop Gaming Acer Nitro ProPanel ANV15-52-74UM (Intel Core 7 240H | RTX 3050 | 16GB | 512Gb | 15.6inch)</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
-        <v>30990000</v>
+        <v>33990000</v>
       </c>
       <c r="C218" s="2" t="inlineStr"/>
       <c r="D218" s="2" t="inlineStr">
@@ -8876,37 +8876,35 @@
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-a13vek-2089vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-propanel-anv15-52-74um</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12T09:35:09+00:00</t>
+          <t>2026-09-26T05:54:35+00:00</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 B13WEKG 676VN</t>
+          <t>Laptop Gaming Nitro ProPanel ANV15-41-R0FE</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>32490000</v>
-      </c>
-      <c r="C219" s="2" t="n">
-        <v>26990000</v>
-      </c>
+        <v>27490000</v>
+      </c>
+      <c r="C219" s="2" t="inlineStr"/>
       <c r="D219" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -8916,111 +8914,113 @@
       <c r="F219" s="2" t="inlineStr"/>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: ryzen 7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 180Hz</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wekg-676vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r0fe</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T01:56:26+00:00</t>
+          <t>2026-05-18T03:33:20+00:00</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 B13WFKG 658VN</t>
+          <t>Laptop gaming Acer Nitro V 15 ProPanel ANV15 41 R0Y4</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>34490000</v>
-      </c>
-      <c r="C220" s="2" t="inlineStr"/>
+        <v>28990000</v>
+      </c>
+      <c r="C220" s="2" t="n">
+        <v>30990000</v>
+      </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: R7 7735HS | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wfkg-658vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r0y4</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T01:55:59+00:00</t>
+          <t>2026-09-19T03:06:17+00:00</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VE-2410VN (Core i5-13420H | RTX 4050 | 16GB | 512GB | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV15-41-R7CR</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>27490000</v>
+        <v>26790000</v>
       </c>
       <c r="C221" s="2" t="n">
-        <v>18990000</v>
+        <v>26990000</v>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr"/>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: R5 7535HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13ve-2410vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r7cr</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T11:27:02+00:00</t>
+          <t>2026-09-19T03:12:05+00:00</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2608VN (i7 13620H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz )</t>
+          <t>Laptop Gaming Acer Nitro V 15 ProPanel ANV15-51-534U</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>28490000</v>
+        <v>23990000</v>
       </c>
       <c r="C222" s="2" t="inlineStr"/>
       <c r="D222" s="2" t="inlineStr">
@@ -9032,71 +9032,73 @@
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-51-534u</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T03:57:02+00:00</t>
+          <t>2026-09-19T03:04:28+00:00</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2610VN (i5 13420H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV15-52-50VA</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>26490000</v>
-      </c>
-      <c r="C223" s="2" t="inlineStr"/>
+        <v>29990000</v>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v>30990000</v>
+      </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr"/>
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T11:25:28+00:00</t>
+          <t>2026-05-18T03:32:27+00:00</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Max C13WE-422VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5050 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming Acer Nitro V 15 ProPanel ANV15-52-59RR (Core 5 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>35990000</v>
+        <v>34990000</v>
       </c>
       <c r="C224" s="2" t="inlineStr"/>
       <c r="D224" s="2" t="inlineStr">
@@ -9108,35 +9110,37 @@
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 5-210H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-59rr</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T05:23:03+00:00</t>
+          <t>2026-08-25T06:58:32+00:00</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Max C13WF-421VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5060 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV15-52-73Z8</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="C225" s="2" t="inlineStr"/>
+        <v>34990000</v>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v>30990000</v>
+      </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9146,76 +9150,76 @@
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13wf-421vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T07:56:42+00:00</t>
+          <t>2026-05-18T03:35:55+00:00</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 B13UDXK 2412VN (Core i5-13420H | RTX 3050 | 8GB | 1TB | 15.6 inch FHD)</t>
+          <t>Laptop Gaming Nitro ProPanel AN16S-61-R193</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>22890000</v>
+        <v>56490000</v>
       </c>
       <c r="C226" s="2" t="n">
-        <v>25990000</v>
+        <v>51990000</v>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: Ryzen Ai 9 365 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5070 8GB | Màn hình: 16" 2K 180Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13udxk-2412vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-an16s-61-r193</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:11:58+00:00</t>
+          <t>2026-07-02T04:33:53+00:00</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 B13VEK-2440VN (Core i7 | RTX 4050 | 16GB | 1TB | 144Hz)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV16S-41-R337</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>32990000</v>
+        <v>40990000</v>
       </c>
       <c r="C227" s="2" t="n">
-        <v>29990000</v>
+        <v>38990000</v>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
@@ -9226,36 +9230,36 @@
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7-13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Acer | CPU: R7 260 | RAM: 16GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5050 8GB | Màn hình: 16" FHD+ 180Hz 100%sRGB</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T03:23:34+00:00</t>
+          <t>2026-09-26T04:26:40+00:00</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WEK 027VN (Core i7 | RTX 5050 | 32GB | 512GB | 2K)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV16S-61-R0B8</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>39990000</v>
+        <v>41990000</v>
       </c>
       <c r="C228" s="2" t="n">
-        <v>37990000</v>
+        <v>34990000</v>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
@@ -9266,36 +9270,36 @@
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: Acer | CPU: Ryzen AI 5 340 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 8GB | Màn hình: 16" FHD+ 180Hz 100%sRGB</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:12:31+00:00</t>
+          <t>2026-05-18T03:39:00+00:00</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WEK 286VN (Core i5 | RTX 5050 | 16GB | 512GB | 2K)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV16S-61-R7KQ</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>35990000</v>
+        <v>43990000</v>
       </c>
       <c r="C229" s="2" t="n">
-        <v>34990000</v>
+        <v>38990000</v>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
@@ -9306,36 +9310,36 @@
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 14450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: Acer | CPU: Ryzen AI 5 340 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" FHD+ 180Hz 100%sRGB</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-286vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-61-r7kq</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T08:10:25+00:00</t>
+          <t>2026-07-05T11:10:46+00:00</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WFK 025VN (Core i7 14650HX | RTX 5060 | 16GB | 512GB | 15.6inch 165Hz)</t>
+          <t>Laptop Gaming Nitro ProPanel ANV16S-61-R9ZV</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>42990000</v>
+        <v>53990000</v>
       </c>
       <c r="C230" s="2" t="n">
-        <v>38990000</v>
+        <v>44990000</v>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
@@ -9346,36 +9350,36 @@
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: Acer | CPU: Ryzen AI 7 350 | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5060 8GB | Màn hình: 16" 2K 180Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-025vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:22:23+00:00</t>
+          <t>2026-08-10T03:48:35+00:00</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WFK 267VN (Core i7 14650HX | RTX 5060 | 32GB | 512GB | 15.6inch 165Hz)</t>
+          <t>Laptop Gaming Acer Nitro V 16S AI ProPanel ANV16S 71 75LR</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>48990000</v>
+        <v>39990000</v>
       </c>
       <c r="C231" s="2" t="n">
-        <v>40990000</v>
+        <v>38990000</v>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
@@ -9386,113 +9390,117 @@
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" FHD 180Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-267vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-71-75lr</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:21:55+00:00</t>
+          <t>2026-09-19T10:03:08+00:00</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Pulse 16 AI C1VGKG 061VN</t>
+          <t>Laptop gaming Acer Nitro V ANV15-41-R1JY</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>39990000</v>
+        <v>20990000</v>
       </c>
       <c r="C232" s="2" t="n">
-        <v>52990000</v>
+        <v>30990000</v>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-32%</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 185H | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: R5 6600H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-pulse-16-ai-c1vgkg-061vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-anv15-41-r1jy</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23T06:44:58+00:00</t>
+          <t>2026-09-18T14:27:19+00:00</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 HX B2WH 258VN (Ultra 9 275HX | 32GB | 1TB | RTX 5070 Ti | 16inch)</t>
+          <t>Laptop gaming Acer Nitro V ANV15-41-R732</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>78990000</v>
-      </c>
-      <c r="C233" s="2" t="inlineStr"/>
+        <v>26290000</v>
+      </c>
+      <c r="C233" s="2" t="n">
+        <v>30990000</v>
+      </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr"/>
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: R5 6600H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 165Hz</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wh-258vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-anv15-41-r732</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T03:42:50+00:00</t>
+          <t>2026-09-19T02:57:39+00:00</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 HX B2WI-257VN</t>
+          <t>Laptop Gaming Acer Nitro V ANV15 41 R9M1</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>92990000</v>
-      </c>
-      <c r="C234" s="2" t="inlineStr"/>
+        <v>23990000</v>
+      </c>
+      <c r="C234" s="2" t="n">
+        <v>22990000</v>
+      </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9502,33 +9510,33 @@
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5080 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: R5 7535HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wi-257vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-anv15-41-r9m1</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T10:01:54+00:00</t>
+          <t>2026-09-19T03:06:44+00:00</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX | RTX5070Ti | 32GB | 1TB | 16inch)</t>
+          <t>Laptop Gaming Acer Nitro V ANV16 41 R36Y</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>75990000</v>
+        <v>29490000</v>
       </c>
       <c r="C235" s="2" t="inlineStr"/>
       <c r="D235" s="2" t="inlineStr">
@@ -9540,35 +9548,37 @@
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070Ti | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Acer | CPU: R7 8845HS | RAM: 16GB DDR5 | VGA: RTX 4050 6GB | Màn hình: 16.1"F 165Hz</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b8wh-031vn</t>
+          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-anv16-41-r36y-nh-qp1sv-004</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T09:58:01+00:00</t>
+          <t>2026-09-19T02:51:23+00:00</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:53</t>
+          <t>2026-09-27 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PW-TS051W</t>
+          <t>Laptop Gaming Lenovo Legion Pro 7 16IAX10H 83F5008WVN</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>87990000</v>
-      </c>
-      <c r="C236" s="2" t="inlineStr"/>
+        <v>118990000</v>
+      </c>
+      <c r="C236" s="2" t="n">
+        <v>96990000</v>
+      </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9578,36 +9588,36 @@
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5080 | Màn hình: 16" 2.5K</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 16 WQXGA 240Hz</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/asus-rog-strix-g16-g614pw-ts051w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f5008wvn</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T09:37:41+00:00</t>
+          <t>2026-08-02T03:52:30+00:00</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Aspire 7 A715 59G 79XF</t>
+          <t>Laptop Gaming LENOVO Legion Pro 7 16IAX10H 83F500ANVN (Ultra 9 275HX | RTX 5080 | 64GB | 1TB | 16 inch OLED)</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>26990000</v>
+        <v>156990000</v>
       </c>
       <c r="C237" s="2" t="n">
-        <v>22990000</v>
+        <v>81990000</v>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
@@ -9618,35 +9628,37 @@
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 16GB | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-acer-gaming-aspire-7-a715-59g-79xf</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500anvn</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T07:14:43+00:00</t>
+          <t>2026-08-21T07:48:39+00:00</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R7ZJ (Ryzen 7 AI 350 | RTX 5060 | 16GB | 512GB | 16 inch)</t>
+          <t>Laptop Gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Legion Pro 7i FIFA World Cup 26™ Edition)</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>46990000</v>
-      </c>
-      <c r="C238" s="2" t="inlineStr"/>
+        <v>109790000</v>
+      </c>
+      <c r="C238" s="2" t="n">
+        <v>83990000</v>
+      </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9656,35 +9668,37 @@
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Ryzen 7 AI 350 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5060 8GB | Màn hình: 16" WQXGA 180Hz 100%SRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti | Màn hình: 16" WQXGA 240Hz</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-acer-gaming-nitro-propanel-an16s-61-r7zj-nh-qxfsv-002</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T10:56:23+00:00</t>
+          <t>2026-08-02T03:48:03+00:00</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro ProPanel AN16S-61-R9CN (Ryzen 7 AI 350 | RTX 5070 | 16GB | 512GB | 16 inch)</t>
+          <t>Laptop Gaming Lenovo LOQ 15AHP10 83JG0047VN (Ryzen 7 250 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>53590000</v>
-      </c>
-      <c r="C239" s="2" t="inlineStr"/>
+        <v>32990000</v>
+      </c>
+      <c r="C239" s="2" t="n">
+        <v>32490000</v>
+      </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9694,37 +9708,35 @@
       <c r="F239" s="2" t="inlineStr"/>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Ryzen 7 AI 350 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5070 8GB | Màn hình: 16" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-acer-gaming-nitro-propanel-an16s-61-r9cn-nh-qxgsv-001</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15ahp10-83jg0047vn</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T03:37:23+00:00</t>
+          <t>2026-09-18T13:37:32+00:00</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Gaming Nitro V ANV15-41-R2UP (Ryzen 5 6600H, RTX 2050, 144Hz)</t>
+          <t>Laptop Gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7 250 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="C240" s="2" t="n">
-        <v>16990000</v>
-      </c>
+        <v>39990000</v>
+      </c>
+      <c r="C240" s="2" t="inlineStr"/>
       <c r="D240" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9734,113 +9746,111 @@
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R5 6600H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 2050 | Màn hình: 15.6" FHD 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.3" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-acer-gaming-nitro-v-anv15-41-r2up</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T02:51:52+00:00</t>
+          <t>2026-09-22T05:44:36+00:00</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro 5 Eagle AN515 57 54MV / 553E</t>
+          <t>Laptop Gaming Lenovo LOQ 15APH8 82XT00BTVN</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>16590000</v>
+        <v>21890000</v>
       </c>
       <c r="C241" s="2" t="n">
-        <v>24990000</v>
+        <v>27362500</v>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>-34%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr"/>
       <c r="F241" s="2" t="inlineStr"/>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: i5 11400H | RAM: 8GB DDR4 | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R5 7640HS | RAM: 16GB DDR5 | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-acer-nitro-5-an515-57-54mv</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15aph8-82xt00btvn</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T03:34:33+00:00</t>
+          <t>2026-05-18T15:56:06+00:00</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro 5 Tiger AN515 58 52SP i5 12500H/8GB/512GB/15.6F 144Hz/RTX3050 4GB/Win11</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0000GVN (R5 7535HS | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>16490000</v>
-      </c>
-      <c r="C242" s="2" t="n">
-        <v>29490000</v>
-      </c>
+        <v>37990000</v>
+      </c>
+      <c r="C242" s="2" t="inlineStr"/>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>-44%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr"/>
       <c r="F242" s="2" t="inlineStr"/>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: i5 12500H | RAM: 8GB DDR4 | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 5 7535HS | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-acer-nitro-5-tiger-an515-58-52sp</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp10e-83s0000gvn</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01T02:12:56+00:00</t>
+          <t>2026-09-16T07:23:54+00:00</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro ProPanel ANV16-72-782F</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000G7VN (Ryzen 5 150 | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>37590000</v>
+        <v>35990000</v>
       </c>
       <c r="C243" s="2" t="inlineStr"/>
       <c r="D243" s="2" t="inlineStr">
@@ -9852,75 +9862,77 @@
       <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5050 | Màn hình: 16" WUXGA180Hz 100%SRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 5 150 | RAM: 16GB DDR5 | Ổ cứng: 512GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-acer-nitro-propanel-anv16-72-782f</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp10e-83s000g7vn</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T10:45:39+00:00</t>
+          <t>2026-08-01T10:08:14+00:00</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Predator Helios 18 PH18 71 981G</t>
+          <t>Laptop Gaming Lenovo LOQ 15ARP9 83JC00HXVN (Ryzen 5 7235HS, RTX 3050 6GB, 100% sRGB)</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>79490000</v>
+        <v>21990000</v>
       </c>
       <c r="C244" s="2" t="n">
-        <v>79990000</v>
+        <v>27990000</v>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr"/>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Intel Core i9 13900HX | RAM: DDR5 24GB (16GB+8GB) 5600MHz ; 2 slots | Ổ cứng: 2TB (2 x 1TB) SSD NVMe M.2 PCIe Gen 4 x 4 | VGA: Geforce RTX 4080 12GB Mux Swicth | Màn hình: 18" WQXGA (2560 x 1600) IPS 240Hz DCI-P3 100%</t>
+          <t>Thương hiệu: Lenovo | CPU: R5 7235HS | RAM: 12GB DDR5 | Ổ cứng: 512GB | VGA: Geforce RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-acer-predator-helios-18-ph18-71-981g</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp9-83jc00hxvn</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T10:10:23+00:00</t>
+          <t>2026-09-18T13:38:48+00:00</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt P16 H7606WP SR335W (Ryzen AI 9 HX 370 | RTX 5070 | 64GB | 2TB | 16inch OLED)</t>
+          <t>Laptop Gaming Lenovo LOQ 15ARP9 83JC00LVVN (Ryzen 5 7235HS, RTX 3050 6GB, 100% sRGB)</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>119990000</v>
-      </c>
-      <c r="C245" s="2" t="inlineStr"/>
+        <v>27990000</v>
+      </c>
+      <c r="C245" s="2" t="n">
+        <v>27990000</v>
+      </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9930,33 +9942,33 @@
       <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ryzen™ AI 9 HX 370 | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5070 | Màn hình: 16" 3K OLED 120Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R5 7235HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: Geforce RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-proart-p16-h7606wp-sr335w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp9-83jc00lvvn</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T03:15:37+00:00</t>
+          <t>2026-09-14T03:04:10+00:00</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt PX13 HN7306EA LX050W (Ryzen AI MAX+ 395 | Radeon Graphics | 32GB | 1TB | 3K OLED)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IPH11 83SL000LVN (Ultra 7-356H | RTX 5060 | 16GB | 512 GB | 15.3 inch)</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>71990000</v>
+        <v>46990000</v>
       </c>
       <c r="C246" s="2" t="inlineStr"/>
       <c r="D246" s="2" t="inlineStr">
@@ -9968,33 +9980,33 @@
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ryzen™ AI 9 HX 370 | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: Radeon Graphics | Màn hình: 16" 3K OLED 120Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7-356H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-proart-px13-hn7306ea-lx050w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15iph11-83sl000lvn</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T03:25:31+00:00</t>
+          <t>2026-09-03T05:06:31+00:00</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Flow Z13 GZ302EAC-RU184WS (Ryzen AI MAX+ 395 | Radeon 8060S | 128GB | 1TB | 2.5K)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IPH11E 83Y8000MVN (Ultra X7-358H | ARC B390 | 16GB | 512 GB | 15.3 inch WUXGA)</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>107490000</v>
+        <v>45990000</v>
       </c>
       <c r="C247" s="2" t="inlineStr"/>
       <c r="D247" s="2" t="inlineStr">
@@ -10006,73 +10018,73 @@
       <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ryzen AI Max+ 395 | RAM: 128GB LPDDR5X | Ổ cứng: 1TB SSD | VGA: Radeon 8060S | Màn hình: 13.4" WQXGA 180Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra X7-358H | RAM: 16GB LPDDR5X-9600 | Ổ cứng: 512GB | VGA: Intel ARC B390 | Màn hình: 15.3" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-rog-flow-z13-gz302eac-ru184ws</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15iph11e-83y8000mvn</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T05:26:51+00:00</t>
+          <t>2026-09-10T07:13:36+00:00</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS ROG Zephyrus G16 GU606AW TB121W (Ultra 9 386H | RTX 5080 | 32GB | 1TB | 16.0 WQXGA OLED 240Hz)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRH8 82XV00QQVN</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>112590000</v>
+        <v>15990000</v>
       </c>
       <c r="C248" s="2" t="n">
-        <v>125990000</v>
+        <v>19987500</v>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr"/>
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ultra 9 386H | RAM: 32GB | VGA: RTX 5080 16GB | Màn hình: 16" WQXGA OLED 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 12450H | RAM: 8GB DDR5 | VGA: RTX 2050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-rog-gu606aw-tb121w-u9</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irh8-82xv00qqvn</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T04:28:17+00:00</t>
+          <t>2026-05-17T15:58:24+00:00</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PH-TS118W ( Ryzen 9 8940HX | 16GB  | 512GB | RTX 5050 )</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX10 83JE01N4VN (Core  i7-14650HX | RTX 5050 | 16GB | 512GB | 15.6 inch)</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>46990000</v>
+        <v>53990000</v>
       </c>
       <c r="C249" s="2" t="inlineStr"/>
       <c r="D249" s="2" t="inlineStr">
@@ -10084,35 +10096,37 @@
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" 2.5K</t>
+          <t>Thương hiệu: Lenovo | CPU: i7-14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-rog-strix-g16-g614ph-ts118w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx10-83je01n4vn</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T05:18:00+00:00</t>
+          <t>2026-08-01T10:15:20+00:00</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9 8940HX | RTX 5060 | 16GB | 512GB | 2.5K 300Hz)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV003CVN (Core i5 | RTX 3050 |16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>51990000</v>
-      </c>
-      <c r="C250" s="2" t="inlineStr"/>
+        <v>29690000</v>
+      </c>
+      <c r="C250" s="2" t="n">
+        <v>25490000</v>
+      </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10122,35 +10136,37 @@
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" 2.5K 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-rog-strix-g16-g614pm-ts147w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv003cvn</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T05:00:50+00:00</t>
+          <t>2026-09-23T07:21:55+00:00</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PP-TS112W</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01ALVN (Core i7-13650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>56990000</v>
-      </c>
-      <c r="C251" s="2" t="inlineStr"/>
+        <v>34990000</v>
+      </c>
+      <c r="C251" s="2" t="n">
+        <v>29990000</v>
+      </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10160,33 +10176,33 @@
       <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5070 | Màn hình: 16" 2.5K</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-rog-strix-g16-g614pp-ts112w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T06:37:14+00:00</t>
+          <t>2026-09-09T10:58:13+00:00</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PR TS103W (Ryzen 9 8940HX | RTX 5070Ti | 16GB | 512GB | 16 inch 2.5K 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01H2VN (Core i7-13650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>66990000</v>
+        <v>33990000</v>
       </c>
       <c r="C252" s="2" t="inlineStr"/>
       <c r="D252" s="2" t="inlineStr">
@@ -10198,33 +10214,33 @@
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5070Ti | Màn hình: 16" 2.5K</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-rog-strix-g16-g614pr-ts103w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01h2vn</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T06:20:24+00:00</t>
+          <t>2026-07-20T05:38:14+00:00</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Zephyrus G14 GU405AW-SY029W (Ultra 9 386H | RTX 5080 | 32GB | 1TB | 14 inch)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01H3VN (Core i7-13645HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>109990000</v>
+        <v>34590000</v>
       </c>
       <c r="C253" s="2" t="inlineStr"/>
       <c r="D253" s="2" t="inlineStr">
@@ -10236,33 +10252,33 @@
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 14" 3K OLED 120Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13645HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 100% sRGB</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-rog-zephyrus-g14-gu405aw-sy029w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01h3vn</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T04:46:37+00:00</t>
+          <t>2026-09-09T13:24:18+00:00</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS ROG Zephyrus G16 GU606AW TB052WS (Ultra 9 386H | RTX 5080 | 64GB | 1TB | 16.0 inch OLED 240Hz)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01MCVN (Core i7-14650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>130990000</v>
+        <v>46990000</v>
       </c>
       <c r="C254" s="2" t="inlineStr"/>
       <c r="D254" s="2" t="inlineStr">
@@ -10274,35 +10290,37 @@
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ultra 9 386H | RAM: 64GB DR5X | VGA: RTX 5080 16GB | Màn hình: 16" WQXGA OLED 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-rog-zephyrus-gu606aw-tb052ws</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01mcvn</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T05:14:49+00:00</t>
+          <t>2026-09-25T04:06:56+00:00</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF F16 FX608JHI-TU210W (Intel Core i5-14450HX | RTX  5050 | 16GB | 512GB | 16 inch WUXGA)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0006QVN (Ryzen 7 | RTX 3050 | 16GB | 512GB | 144Hz)</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>39890000</v>
-      </c>
-      <c r="C255" s="2" t="inlineStr"/>
+        <v>25490000</v>
+      </c>
+      <c r="C255" s="2" t="n">
+        <v>23990000</v>
+      </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10312,35 +10330,37 @@
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: i5-14450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" FHD+ 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-tuf-f16-fx608jhi-tu210w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10-83s0006qvn</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11T05:16:27+00:00</t>
+          <t>2026-09-18T13:39:28+00:00</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS TUF A16 FA608UHI TU121W (Ryzen 7 260 | 16GB | 512GB | RTX 5050 | 16 inch)</t>
+          <t>Laptop Lenovo LOQ 15ARP10E 83S0004FVN ( Ryzen 7 7735HS | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="C256" s="2" t="inlineStr"/>
+        <v>34590000</v>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>26990000</v>
+      </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10350,33 +10370,33 @@
       <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ryzen 7 260 | RAM: 16GB DDR5 | VGA: RTX 5050 8GB | Màn hình: 16" FHD+ 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-tuf-fa608uhi-tu121w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T04:16:14+00:00</t>
+          <t>2026-09-22T05:06:41+00:00</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS TUF Gaming A14 FA401EA-RG034W (Ryzen AI MAX+ 392 | Radeon 8060S | 64GB | 1TB | 2.5K)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0006RVN</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>59390000</v>
+        <v>29990000</v>
       </c>
       <c r="C257" s="2" t="inlineStr"/>
       <c r="D257" s="2" t="inlineStr">
@@ -10388,71 +10408,73 @@
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ryzen™ AI MAX+ 392 | RAM: 64GB LPDDR5X | Ổ cứng: 1TB Gen 4 | VGA: Radeon 8060S | Màn hình: 14" 2.5K 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-tuf-gaming-a14-fa401ea-rg034w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0006rvn</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T05:05:13+00:00</t>
+          <t>2026-09-15T08:27:17+00:00</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465 | RTX 5060 | 32GB | 1TB | 2.5K)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0007AVN</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>53990000</v>
-      </c>
-      <c r="C258" s="2" t="inlineStr"/>
+        <v>26990000</v>
+      </c>
+      <c r="C258" s="2" t="n">
+        <v>31490000</v>
+      </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr"/>
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ryzen AI 9 465 | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" 2K 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0007avn</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T13:45:19+00:00</t>
+          <t>2026-09-18T13:38:09+00:00</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF Gaming A15 FA506NCG-HN329W (Ryzen 7 8845HS | RTX 3050 | 16GB | 512GB | FHD)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S000DCVN ( Ryzen 7 - 170 | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>26990000</v>
+        <v>28990000</v>
       </c>
       <c r="C259" s="2" t="inlineStr"/>
       <c r="D259" s="2" t="inlineStr">
@@ -10464,33 +10486,33 @@
       <c r="F259" s="2" t="inlineStr"/>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: R7 8845HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 4GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 170 | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-tuf-gaming-a15-fa506ncg-hn329w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s000dcvn</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T05:36:08+00:00</t>
+          <t>2026-09-19T06:01:38+00:00</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS TUF A16 FA608UMI TU162W (Ryzen 7 260 | 16GB| 512GB| RTX 5060 | 16 inch)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003XVN (Core 7 230H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>46990000</v>
+        <v>41990000</v>
       </c>
       <c r="C260" s="2" t="inlineStr"/>
       <c r="D260" s="2" t="inlineStr">
@@ -10502,33 +10524,33 @@
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ryzen 7 260 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5060 8GB | Màn hình: 16" FHD+ 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-tuf-gaming-a16-fa608umi-tu162w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003xvn</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T06:46:47+00:00</t>
+          <t>2026-09-22T05:57:43+00:00</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS TUF A14 FA401EA RG041W (Ryzen AI MAX+ 392 | Radeon 8060S| 32GB | 512GB | 14 inch)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003YVN (Core 7 230H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>54990000</v>
+        <v>36490000</v>
       </c>
       <c r="C261" s="2" t="inlineStr"/>
       <c r="D261" s="2" t="inlineStr">
@@ -10540,35 +10562,37 @@
       <c r="F261" s="2" t="inlineStr"/>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ryzen AI MAX+ 392 | RAM: 32GB LPDDR5X | VGA: Radeon 8060S | Màn hình: 14" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-tuf-gaming-fa401ea-rg041w</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003yvn</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T08:21:12+00:00</t>
+          <t>2026-09-22T05:58:44+00:00</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook DUO UX8407AA-SN138WS (Ultra X9 388H | Arc™ Graphics | 32 GB | 1TB | 14 inch)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRX11 83SC003RVN (i5-13450HX | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>87990000</v>
-      </c>
-      <c r="C262" s="2" t="inlineStr"/>
+        <v>38990000</v>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>28490000</v>
+      </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10578,33 +10602,33 @@
       <c r="F262" s="2" t="inlineStr"/>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ultra X9 388H | RAM: 32GB LPDDR5X | Ổ cứng: 1TB SSD | VGA: Arc Graphics | Màn hình: 14" 3K OLED 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-zenbook-duo-ux8407aa-sn138ws</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irx11-83sc003rvn</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T09:23:55+00:00</t>
+          <t>2026-07-01T05:38:36+00:00</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook DUO UX8407AA-SN439WS (Ultra X7 358H | Arc Graphics | 32 GB | 512GB | 14 inch)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003VVN (Core 5 205H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>77990000</v>
+        <v>35990000</v>
       </c>
       <c r="C263" s="2" t="inlineStr"/>
       <c r="D263" s="2" t="inlineStr">
@@ -10616,37 +10640,35 @@
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Ultra X7 358H | RAM: 32GB LPDDR5X | Ổ cứng: 512GB SSD | VGA: Arc Graphics | Màn hình: 14" 3K OLED 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-asus-zenbook-duo-ux8407aa-sn439ws</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003vvn</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T05:49:21+00:00</t>
+          <t>2026-09-24T02:46:40+00:00</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Aspire 7 A715 59G 53GZ</t>
+          <t>Laptop Gaming Lenovo LOQ Essential LOQ 15IRH11E 83Y9003WVN (Core 5 205H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B264" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C264" s="2" t="n">
-        <v>22990000</v>
-      </c>
+        <v>39990000</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr"/>
       <c r="D264" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10656,35 +10678,37 @@
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-aspire-7-a715-59g-53gz</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003wvn</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T07:16:51+00:00</t>
+          <t>2026-09-24T05:03:38+00:00</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Aspire 7 A715-59G-59RD NH.DXUSV.001 (Core 5 210H | RTX 3050 | 16GB | 512GB | 144Hz)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX AI D2XWFKG-036VN (Ultra 7 | RTX 5060 | 16GB | 1TB | 2K)</t>
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="C265" s="2" t="inlineStr"/>
+        <v>48990000</v>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>44990000</v>
+      </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10694,37 +10718,35 @@
       <c r="F265" s="2" t="inlineStr"/>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 4GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-ai-d2xwfkg-036vn</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T03:22:45+00:00</t>
+          <t>2026-09-12T04:38:20+00:00</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Aspire 7 A715 59G 73LB</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WFK-074VN (i7 14650HX | 16GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C266" s="2" t="n">
-        <v>22990000</v>
-      </c>
+        <v>52490000</v>
+      </c>
+      <c r="C266" s="2" t="inlineStr"/>
       <c r="D266" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10734,37 +10756,35 @@
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: i7 12650H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-aspire-7-a715-59g-73lb</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-074vn</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T09:29:29+00:00</t>
+          <t>2026-09-17T09:48:44+00:00</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Aspire 7 A715 59G 78WG</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14VFK-075VN (i9 14900HX | 32GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>25890000</v>
-      </c>
-      <c r="C267" s="2" t="n">
-        <v>22990000</v>
-      </c>
+        <v>60990000</v>
+      </c>
+      <c r="C267" s="2" t="inlineStr"/>
       <c r="D267" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10774,37 +10794,35 @@
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-aspire-7-a715-59g-78wg</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-075vn</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T07:17:39+00:00</t>
+          <t>2026-09-14T10:30:50+00:00</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro 16 AI ProPanel AN16S 61 R5F4</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 076VN (Core i9-14900HX | RTX 5050 | 32GB | 1TB SSD | QHD+)</t>
         </is>
       </c>
       <c r="B268" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="C268" s="2" t="n">
-        <v>30990000</v>
-      </c>
+        <v>56790000</v>
+      </c>
+      <c r="C268" s="2" t="inlineStr"/>
       <c r="D268" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10814,33 +10832,33 @@
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" FHD+ 180Hz</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-16-ai-propanel-an16s-61-r5f4</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-076vn</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T07:45:59+00:00</t>
+          <t>2026-09-09T10:48:15+00:00</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS | RTX 4050 | 16GB | 512GB | 15.6inch FHD)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 077VN (Core i7 14650HX | RTX 5050 | 16GB | 512GB | 16 inch)</t>
         </is>
       </c>
       <c r="B269" s="2" t="n">
-        <v>32990000</v>
+        <v>49990000</v>
       </c>
       <c r="C269" s="2" t="inlineStr"/>
       <c r="D269" s="2" t="inlineStr">
@@ -10852,117 +10870,111 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R5 7640HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-anv15-42-r5ef</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-077vn</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12T02:51:12+00:00</t>
+          <t>2026-09-17T09:44:38+00:00</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV16S-71-58WQ</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WGK</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="C270" s="2" t="n">
-        <v>44990000</v>
-      </c>
+        <v>69990000</v>
+      </c>
+      <c r="C270" s="2" t="inlineStr"/>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr"/>
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 8GB | Màn hình: 16" 2K+ 180Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-anv16s-71-58wq</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wgk</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T10:24:36+00:00</t>
+          <t>2026-08-13T04:42:13+00:00</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV16-72-71T9</t>
+          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-051VN (Ultra 9 290HX Plus | 32GB | 1TB | RTX 5070 12GB | 16 inch)</t>
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C271" s="2" t="n">
-        <v>44990000</v>
-      </c>
+        <v>70990000</v>
+      </c>
+      <c r="C271" s="2" t="inlineStr"/>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16inch FHD+</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ Oled 165Hz</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-anv16s-71-71t9</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-051vn</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T04:23:28+00:00</t>
+          <t>2026-09-17T09:46:40+00:00</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro Lite 16 NL16 71G 56WQ (Intel Core i5-13420H, RTX 3050 6GB, 165Hz)</t>
+          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-052VN  (Ultra 7 251HX | 16GB | 1TB | RTX 5070 12GB | 16 inch OLED 165Hz )</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>24490000</v>
-      </c>
-      <c r="C272" s="2" t="n">
-        <v>22990000</v>
-      </c>
+        <v>60990000</v>
+      </c>
+      <c r="C272" s="2" t="inlineStr"/>
       <c r="D272" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10972,37 +10984,35 @@
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 251HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ OLED 165Hz</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-56wq</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-052vn</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T02:27:35+00:00</t>
+          <t>2026-09-17T09:47:42+00:00</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro Lite 16 NL16-71G 71FN</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C273" s="2" t="n">
-        <v>22990000</v>
-      </c>
+        <v>64990000</v>
+      </c>
+      <c r="C273" s="2" t="inlineStr"/>
       <c r="D273" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -11012,37 +11022,35 @@
       <c r="F273" s="2" t="inlineStr"/>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71fn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T02:47:46+00:00</t>
+          <t>2026-08-01T07:15:48+00:00</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro Lite 16 NL16 71G 71UJ (Core i7 | RTX 3050 | 16GB | 512GB | 16 inch)</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="C274" s="2" t="n">
-        <v>22990000</v>
-      </c>
+        <v>56990000</v>
+      </c>
+      <c r="C274" s="2" t="inlineStr"/>
       <c r="D274" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -11052,33 +11060,33 @@
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 7 8840HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-lite-16-nl16-71g-71uj</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk-1</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T02:40:44+00:00</t>
+          <t>2026-08-01T07:16:04+00:00</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS | RTX 4050 | 16GB | 512GB | 15.6inch)</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WGK-067VN (Ryzen 9 8940HX | RTX 5060 | 16GB | 1TB | 16inch QHD+)</t>
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>34590000</v>
+        <v>59990000</v>
       </c>
       <c r="C275" s="2" t="inlineStr"/>
       <c r="D275" s="2" t="inlineStr">
@@ -11090,33 +11098,33 @@
       <c r="F275" s="2" t="inlineStr"/>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Ryzen 7 7445HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wgk-067vn</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04T10:57:57+00:00</t>
+          <t>2026-08-26T08:26:26+00:00</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro ProPanel ANV15-52-50RB (Intel Core 5 210H | RTX 4050 | 16GB | 512GB | 15.6 inch)</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WGK-093VN (Ryzen 9 8940HX | RTX 5070 | 16GB | 1TB | 16inch QHD+)</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>33490000</v>
+        <v>65990000</v>
       </c>
       <c r="C276" s="2" t="inlineStr"/>
       <c r="D276" s="2" t="inlineStr">
@@ -11128,33 +11136,33 @@
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-propanel-anv15-52-50rb</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wgk-093vn</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05T04:22:14+00:00</t>
+          <t>2026-08-26T08:28:22+00:00</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro ProPanel ANV15-52-74UM (Intel Core 7 240H | RTX 3050 | 16GB | 512Gb | 15.6inch)</t>
+          <t>Laptop Gaming MSI Cyborg 15 A13VEK 2089VN</t>
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>30890000</v>
+        <v>30990000</v>
       </c>
       <c r="C277" s="2" t="inlineStr"/>
       <c r="D277" s="2" t="inlineStr">
@@ -11166,35 +11174,37 @@
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-propanel-anv15-52-74um</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-a13vek-2089vn</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T10:53:25+00:00</t>
+          <t>2026-07-12T09:35:09+00:00</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV15-41-R0FE</t>
+          <t>Laptop Gaming MSI Cyborg 15 B13WEKG 676VN</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>27490000</v>
-      </c>
-      <c r="C278" s="2" t="inlineStr"/>
+        <v>32490000</v>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>26990000</v>
+      </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -11204,113 +11214,111 @@
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: ryzen 7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 180Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r0fe</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wekg-676vn</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T03:33:20+00:00</t>
+          <t>2026-06-26T01:56:26+00:00</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro V 15 ProPanel ANV15 41 R0Y4</t>
+          <t>Laptop Gaming MSI Cyborg 15 B13WFKG 658VN</t>
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C279" s="2" t="n">
-        <v>30990000</v>
-      </c>
+        <v>34490000</v>
+      </c>
+      <c r="C279" s="2" t="inlineStr"/>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr"/>
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R7 7735HS | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r0y4</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wfkg-658vn</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T03:06:17+00:00</t>
+          <t>2026-06-26T01:55:59+00:00</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV15-41-R7CR</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VE-2410VN (Core i5-13420H | RTX 4050 | 16GB | 512GB | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>26790000</v>
+        <v>27490000</v>
       </c>
       <c r="C280" s="2" t="n">
-        <v>26990000</v>
+        <v>18990000</v>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr"/>
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R5 7535HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-41-r7cr</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13ve-2410vn</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T03:12:05+00:00</t>
+          <t>2026-08-12T11:27:02+00:00</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro V 15 ProPanel ANV15-51-534U</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2608VN (i7 13620H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz )</t>
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>23990000</v>
+        <v>28490000</v>
       </c>
       <c r="C281" s="2" t="inlineStr"/>
       <c r="D281" s="2" t="inlineStr">
@@ -11322,73 +11330,71 @@
       <c r="F281" s="2" t="inlineStr"/>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-51-534u</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T03:04:28+00:00</t>
+          <t>2026-09-19T03:57:02+00:00</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV15-52-50VA</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2610VN (i5 13420H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C282" s="2" t="n">
-        <v>30990000</v>
-      </c>
+        <v>26490000</v>
+      </c>
+      <c r="C282" s="2" t="inlineStr"/>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr"/>
       <c r="F282" s="2" t="inlineStr"/>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 5 210H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T03:32:27+00:00</t>
+          <t>2026-09-25T11:25:28+00:00</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro V 15 ProPanel ANV15-52-59RR (Core 5 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming MSI Cyborg 15 Max C13WE-422VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5050 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>34990000</v>
+        <v>35990000</v>
       </c>
       <c r="C283" s="2" t="inlineStr"/>
       <c r="D283" s="2" t="inlineStr">
@@ -11400,37 +11406,35 @@
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 5-210H | RAM: 16GB DDR4 | Ổ cứng: 512GB SSD | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-59rr</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25T06:58:32+00:00</t>
+          <t>2026-09-18T05:23:03+00:00</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV15-52-73Z8</t>
+          <t>Laptop Gaming MSI Cyborg 15 Max C13WF-421VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5060 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C284" s="2" t="n">
-        <v>30990000</v>
-      </c>
+        <v>41990000</v>
+      </c>
+      <c r="C284" s="2" t="inlineStr"/>
       <c r="D284" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -11440,76 +11444,76 @@
       <c r="F284" s="2" t="inlineStr"/>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13wf-421vn</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T03:35:55+00:00</t>
+          <t>2026-09-19T07:56:42+00:00</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel AN16S-61-R193</t>
+          <t>Laptop Gaming MSI Katana 15 B13UDXK 2412VN (Core i5-13420H | RTX 3050 | 8GB | 1TB | 15.6 inch FHD)</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>56490000</v>
+        <v>22890000</v>
       </c>
       <c r="C285" s="2" t="n">
-        <v>51990000</v>
+        <v>25990000</v>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr"/>
       <c r="F285" s="2" t="inlineStr"/>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Ryzen Ai 9 365 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5070 8GB | Màn hình: 16" 2K 180Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-an16s-61-r193</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13udxk-2412vn</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T04:33:53+00:00</t>
+          <t>2026-09-18T15:11:58+00:00</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV16S-41-R337</t>
+          <t>Laptop Gaming MSI Katana 15 B13VEK-2440VN (Core i7 | RTX 4050 | 16GB | 1TB | 144Hz)</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>40990000</v>
+        <v>32990000</v>
       </c>
       <c r="C286" s="2" t="n">
-        <v>38990000</v>
+        <v>29990000</v>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
@@ -11520,36 +11524,36 @@
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R7 260 | RAM: 16GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5050 8GB | Màn hình: 16" FHD+ 180Hz 100%sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7-13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-41-r337</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T04:26:40+00:00</t>
+          <t>2026-09-26T03:23:34+00:00</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV16S-61-R0B8</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WEK 027VN (Core i7 | RTX 5050 | 32GB | 512GB | 2K)</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>41990000</v>
+        <v>39990000</v>
       </c>
       <c r="C287" s="2" t="n">
-        <v>34990000</v>
+        <v>37990000</v>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
@@ -11560,36 +11564,36 @@
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Ryzen AI 5 340 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 8GB | Màn hình: 16" FHD+ 180Hz 100%sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-61-r0b8</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T03:39:00+00:00</t>
+          <t>2026-09-18T15:12:31+00:00</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV16S-61-R7KQ</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WEK 286VN (Core i5 | RTX 5050 | 16GB | 512GB | 2K)</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>43990000</v>
+        <v>35990000</v>
       </c>
       <c r="C288" s="2" t="n">
-        <v>38990000</v>
+        <v>34990000</v>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
@@ -11600,36 +11604,36 @@
       <c r="F288" s="2" t="inlineStr"/>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Ryzen AI 5 340 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" FHD+ 180Hz 100%sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i5 14450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-61-r7kq</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-286vn</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T11:10:46+00:00</t>
+          <t>2026-08-01T08:10:25+00:00</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Nitro ProPanel ANV16S-61-R9ZV</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WFK 025VN (Core i7 14650HX | RTX 5060 | 16GB | 512GB | 15.6inch 165Hz)</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>53990000</v>
+        <v>42990000</v>
       </c>
       <c r="C289" s="2" t="n">
-        <v>44990000</v>
+        <v>38990000</v>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
@@ -11640,36 +11644,36 @@
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Ryzen AI 7 350 | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5060 8GB | Màn hình: 16" 2K 180Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-61-r9zv</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-025vn</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T03:48:35+00:00</t>
+          <t>2026-09-18T15:22:23+00:00</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro V 16S AI ProPanel ANV16S 71 75LR</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WFK 267VN (Core i7 14650HX | RTX 5060 | 32GB | 512GB | 15.6inch 165Hz)</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>39990000</v>
+        <v>48990000</v>
       </c>
       <c r="C290" s="2" t="n">
-        <v>38990000</v>
+        <v>40990000</v>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
@@ -11680,117 +11684,113 @@
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: Core 7 240H | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" FHD 180Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-16s-ai-propanel-anv16s-71-75lr</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-267vn</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T10:03:08+00:00</t>
+          <t>2026-09-18T15:21:55+00:00</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro V ANV15-41-R1JY</t>
+          <t>Laptop Gaming MSI Pulse 16 AI C1VGKG 061VN</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>20990000</v>
+        <v>39990000</v>
       </c>
       <c r="C291" s="2" t="n">
-        <v>30990000</v>
+        <v>52990000</v>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr"/>
       <c r="F291" s="2" t="inlineStr"/>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R5 6600H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 185H | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-anv15-41-r1jy</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-pulse-16-ai-c1vgkg-061vn</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:27:19+00:00</t>
+          <t>2026-05-23T06:44:58+00:00</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro V ANV15-41-R732</t>
+          <t>Laptop Gaming MSI Raider 16 HX B2WH 258VN (Ultra 9 275HX | 32GB | 1TB | RTX 5070 Ti | 16inch)</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>26290000</v>
-      </c>
-      <c r="C292" s="2" t="n">
-        <v>30990000</v>
-      </c>
+        <v>78990000</v>
+      </c>
+      <c r="C292" s="2" t="inlineStr"/>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr"/>
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R5 6600H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-anv15-41-r732</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wh-258vn</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T02:57:39+00:00</t>
+          <t>2026-09-09T03:42:50+00:00</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro V ANV15 41 R9M1</t>
+          <t>Laptop Gaming MSI Raider 16 HX B2WI-257VN</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="C293" s="2" t="n">
-        <v>22990000</v>
-      </c>
+        <v>92990000</v>
+      </c>
+      <c r="C293" s="2" t="inlineStr"/>
       <c r="D293" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -11800,33 +11800,33 @@
       <c r="F293" s="2" t="inlineStr"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R5 7535HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 180Hz 100%SRGB</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5080 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-anv15-41-r9m1</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wi-257vn</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T03:06:44+00:00</t>
+          <t>2026-09-17T10:01:54+00:00</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Acer Nitro V ANV16 41 R36Y</t>
+          <t>Laptop Gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX | RTX5070Ti | 32GB | 1TB | 16inch)</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>29490000</v>
+        <v>75990000</v>
       </c>
       <c r="C294" s="2" t="inlineStr"/>
       <c r="D294" s="2" t="inlineStr">
@@ -11838,22 +11838,22 @@
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Acer | CPU: R7 8845HS | RAM: 16GB DDR5 | VGA: RTX 4050 6GB | Màn hình: 16.1"F 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070Ti | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-acer-nitro-v-anv16-41-r36y-nh-qp1sv-004</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b8wh-031vn</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T02:51:23+00:00</t>
+          <t>2026-09-17T09:58:01+00:00</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 11:57:58</t>
+          <t>2026-09-27 12:18:43</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" 2.5K 240Hz</t>
+          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 16" 2.5K 300Hz</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T03:19:15+00:00</t>
+          <t>2026-10-14T03:11:08+00:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:05:08+00:00</t>
+          <t>2026-10-14T03:11:25+00:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:03</t>
+          <t>2026-10-14 10:55:41</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -5086,14 +5086,14 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>24990000</v>
+        <v>29990000</v>
       </c>
       <c r="C120" s="2" t="n">
         <v>26990000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -5110,12 +5110,12 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:58:10+00:00</t>
+          <t>2026-10-13T08:01:40+00:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:00</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T03:22:59+00:00</t>
+          <t>2026-10-13T11:38:13+00:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>32990000</v>
+        <v>33990000</v>
       </c>
       <c r="C128" s="2" t="inlineStr"/>
       <c r="D128" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T07:28:17+00:00</t>
+          <t>2026-10-13T08:04:18+00:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>47990000</v>
+        <v>48990000</v>
       </c>
       <c r="C141" s="2" t="inlineStr"/>
       <c r="D141" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T05:55:51+00:00</t>
+          <t>2026-10-13T09:08:55+00:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>44990000</v>
+        <v>46990000</v>
       </c>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T08:26:25+00:00</t>
+          <t>2026-10-13T09:03:59+00:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:13:58</t>
+          <t>2026-10-14 10:55:29</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T07:57:05+00:00</t>
+          <t>2026-10-13T07:58:22+00:00</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:43</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10312,12 +10312,12 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:43:44+00:00</t>
+          <t>2026-10-13T07:18:28+00:00</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10907,7 +10907,9 @@
           <t>Laptop Lenovo Yoga Pro 7 15IPH11 83SN0059VN (Ultra 7 356H | RTX 5050 | 24GB | 512GB | OLED 2.5K 100%sRGB)</t>
         </is>
       </c>
-      <c r="B270" s="2" t="inlineStr"/>
+      <c r="B270" s="2" t="n">
+        <v>76990000</v>
+      </c>
       <c r="C270" s="2" t="inlineStr"/>
       <c r="D270" s="2" t="inlineStr">
         <is>
@@ -10928,12 +10930,12 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T02:52:20+00:00</t>
+          <t>2026-10-13T08:06:29+00:00</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -10971,7 +10973,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11009,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11047,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11087,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11125,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11163,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11201,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11241,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11281,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11319,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11357,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11390,12 +11392,12 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T11:22:59+00:00</t>
+          <t>2026-10-13T07:19:46+00:00</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11432,12 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09T02:14:46+00:00</t>
+          <t>2026-10-13T07:19:14+00:00</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11473,7 +11475,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11513,7 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11551,7 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11589,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11627,7 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11665,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11705,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11743,7 +11745,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11781,7 +11783,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11821,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11859,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11897,7 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11935,7 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -11966,12 +11968,12 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16T14:41:19+00:00</t>
+          <t>2026-10-13T12:18:18+00:00</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12011,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -12047,7 +12049,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -12085,7 +12087,7 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>
@@ -12123,7 +12125,7 @@
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:14:06</t>
+          <t>2026-10-14 10:55:45</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -540,14 +540,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>26990000</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>22990000</v>
-      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -656,14 +656,14 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
+        <v>16990000</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>18990000</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>16990000</v>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1616,14 +1616,14 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="C31" s="2" t="n">
         <v>24990000</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>22990000</v>
-      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1734,14 +1734,14 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="C34" s="2" t="n">
         <v>25890000</v>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>22990000</v>
-      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1774,14 +1774,14 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="C35" s="2" t="n">
         <v>45990000</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>30990000</v>
-      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-33%</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="C39" s="2" t="n">
         <v>24490000</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>22990000</v>
-      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -1972,14 +1972,14 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="C40" s="2" t="n">
         <v>29990000</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>22990000</v>
-      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2012,14 +2012,14 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="C41" s="2" t="n">
         <v>27990000</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>22990000</v>
-      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2322,14 +2322,14 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="C49" s="2" t="n">
         <v>31490000</v>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>30990000</v>
-      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2400,14 +2400,14 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="C51" s="2" t="n">
         <v>34990000</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>30990000</v>
-      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2440,14 +2440,14 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
+        <v>51990000</v>
+      </c>
+      <c r="C52" s="2" t="n">
         <v>56490000</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>51990000</v>
-      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2480,14 +2480,14 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="C53" s="2" t="n">
         <v>40990000</v>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>38990000</v>
-      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2520,14 +2520,14 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
+        <v>34990000</v>
+      </c>
+      <c r="C54" s="2" t="n">
         <v>41990000</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>34990000</v>
-      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2560,14 +2560,14 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="C55" s="2" t="n">
         <v>43990000</v>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>38990000</v>
-      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2600,14 +2600,14 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
+        <v>44990000</v>
+      </c>
+      <c r="C56" s="2" t="n">
         <v>53990000</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>44990000</v>
-      </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2640,14 +2640,14 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="C57" s="2" t="n">
         <v>39990000</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>38990000</v>
-      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2760,14 +2760,14 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="C60" s="2" t="n">
         <v>23990000</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>22990000</v>
-      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:41</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -2878,14 +2878,14 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
+        <v>28790000</v>
+      </c>
+      <c r="C63" s="2" t="n">
         <v>28990000</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>28790000</v>
-      </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3034,14 +3034,14 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
+        <v>32990000</v>
+      </c>
+      <c r="C67" s="2" t="n">
         <v>33990000</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>32990000</v>
-      </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3150,14 +3150,14 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
+        <v>104990000</v>
+      </c>
+      <c r="C70" s="2" t="n">
         <v>125990000</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>104990000</v>
-      </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3190,14 +3190,14 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
+        <v>149990000</v>
+      </c>
+      <c r="C71" s="2" t="n">
         <v>165990000</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>149990000</v>
-      </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3270,14 +3270,14 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
+        <v>54990000</v>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>56990000</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>54990000</v>
-      </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3310,14 +3310,14 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
+        <v>61990000</v>
+      </c>
+      <c r="C74" s="2" t="n">
         <v>63890000</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>61990000</v>
-      </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3660,14 +3660,14 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
+        <v>27990000</v>
+      </c>
+      <c r="C83" s="2" t="n">
         <v>31990000</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>27990000</v>
-      </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3700,14 +3700,14 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
+        <v>30490000</v>
+      </c>
+      <c r="C84" s="2" t="n">
         <v>31990000</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>30490000</v>
-      </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3740,14 +3740,14 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
+        <v>28490000</v>
+      </c>
+      <c r="C85" s="2" t="n">
         <v>30990000</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>28490000</v>
-      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3894,14 +3894,14 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
+        <v>27490000</v>
+      </c>
+      <c r="C89" s="2" t="n">
         <v>29990000</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>27490000</v>
-      </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3934,14 +3934,14 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
+        <v>25490000</v>
+      </c>
+      <c r="C90" s="2" t="n">
         <v>25790000</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>25490000</v>
-      </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -5086,14 +5086,14 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="C120" s="2" t="n">
         <v>29990000</v>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>26990000</v>
-      </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -5126,14 +5126,14 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
+        <v>27290000</v>
+      </c>
+      <c r="C121" s="2" t="n">
         <v>30990000</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>27290000</v>
-      </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:06</t>
         </is>
       </c>
     </row>
@@ -5166,14 +5166,14 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
+        <v>30490000</v>
+      </c>
+      <c r="C122" s="2" t="n">
         <v>30990000</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>30490000</v>
-      </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6626,14 +6626,14 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
+        <v>53990000</v>
+      </c>
+      <c r="C160" s="2" t="n">
         <v>57990000</v>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>53990000</v>
-      </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6666,14 +6666,14 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
+        <v>48990000</v>
+      </c>
+      <c r="C161" s="2" t="n">
         <v>52590000</v>
       </c>
-      <c r="C161" s="2" t="n">
-        <v>48990000</v>
-      </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6820,14 +6820,14 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
+        <v>57990000</v>
+      </c>
+      <c r="C165" s="2" t="n">
         <v>59990000</v>
       </c>
-      <c r="C165" s="2" t="n">
-        <v>57990000</v>
-      </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="C169" s="2" t="n">
         <v>44990000</v>
       </c>
-      <c r="C169" s="2" t="n">
-        <v>38990000</v>
-      </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7016,14 +7016,14 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="C170" s="2" t="n">
         <v>47590000</v>
       </c>
-      <c r="C170" s="2" t="n">
-        <v>39990000</v>
-      </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7056,14 +7056,14 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
+        <v>36990000</v>
+      </c>
+      <c r="C171" s="2" t="n">
         <v>42990000</v>
       </c>
-      <c r="C171" s="2" t="n">
-        <v>36990000</v>
-      </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7096,14 +7096,14 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
+        <v>44990000</v>
+      </c>
+      <c r="C172" s="2" t="n">
         <v>53390000</v>
       </c>
-      <c r="C172" s="2" t="n">
-        <v>44990000</v>
-      </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7136,14 +7136,14 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="C173" s="2" t="n">
         <v>42990000</v>
       </c>
-      <c r="C173" s="2" t="n">
-        <v>39990000</v>
-      </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7176,14 +7176,14 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
+        <v>63990000</v>
+      </c>
+      <c r="C174" s="2" t="n">
         <v>75990000</v>
       </c>
-      <c r="C174" s="2" t="n">
-        <v>63990000</v>
-      </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7216,14 +7216,14 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
+        <v>69990000</v>
+      </c>
+      <c r="C175" s="2" t="n">
         <v>83990000</v>
       </c>
-      <c r="C175" s="2" t="n">
-        <v>69990000</v>
-      </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7256,14 +7256,14 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
+        <v>59990000</v>
+      </c>
+      <c r="C176" s="2" t="n">
         <v>76990000</v>
       </c>
-      <c r="C176" s="2" t="n">
-        <v>59990000</v>
-      </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7296,14 +7296,14 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
+        <v>54990000</v>
+      </c>
+      <c r="C177" s="2" t="n">
         <v>72390000</v>
       </c>
-      <c r="C177" s="2" t="n">
-        <v>54990000</v>
-      </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-24%</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7374,14 +7374,14 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
+        <v>81990000</v>
+      </c>
+      <c r="C179" s="2" t="n">
         <v>119990000</v>
       </c>
-      <c r="C179" s="2" t="n">
-        <v>81990000</v>
-      </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-32%</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7414,14 +7414,14 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
+        <v>96990000</v>
+      </c>
+      <c r="C180" s="2" t="n">
         <v>118990000</v>
       </c>
-      <c r="C180" s="2" t="n">
-        <v>96990000</v>
-      </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7454,14 +7454,14 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
+        <v>81990000</v>
+      </c>
+      <c r="C181" s="2" t="n">
         <v>156990000</v>
       </c>
-      <c r="C181" s="2" t="n">
-        <v>81990000</v>
-      </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-48%</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:29</t>
+          <t>2026-10-15 00:14:13</t>
         </is>
       </c>
     </row>
@@ -7494,14 +7494,14 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
+        <v>83990000</v>
+      </c>
+      <c r="C182" s="2" t="n">
         <v>109790000</v>
       </c>
-      <c r="C182" s="2" t="n">
-        <v>83990000</v>
-      </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7534,14 +7534,14 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
+        <v>32490000</v>
+      </c>
+      <c r="C183" s="2" t="n">
         <v>32990000</v>
       </c>
-      <c r="C183" s="2" t="n">
-        <v>32490000</v>
-      </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -7962,14 +7962,14 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
+        <v>25490000</v>
+      </c>
+      <c r="C194" s="2" t="n">
         <v>31490000</v>
       </c>
-      <c r="C194" s="2" t="n">
-        <v>25490000</v>
-      </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8002,14 +8002,14 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="C195" s="2" t="n">
         <v>34990000</v>
       </c>
-      <c r="C195" s="2" t="n">
-        <v>29990000</v>
-      </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8156,14 +8156,14 @@
         </is>
       </c>
       <c r="B199" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="C199" s="2" t="n">
         <v>25490000</v>
       </c>
-      <c r="C199" s="2" t="n">
-        <v>23990000</v>
-      </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr"/>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8196,14 +8196,14 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="C200" s="2" t="n">
         <v>35990000</v>
       </c>
-      <c r="C200" s="2" t="n">
-        <v>26990000</v>
-      </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr"/>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>34490000</v>
+        <v>33990000</v>
       </c>
       <c r="C204" s="2" t="inlineStr"/>
       <c r="D204" s="2" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T16:01:26+00:00</t>
+          <t>2026-10-14T11:18:39+00:00</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>29999000</v>
+        <v>28990000</v>
       </c>
       <c r="C205" s="2" t="inlineStr"/>
       <c r="D205" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T16:04:35+00:00</t>
+          <t>2026-10-14T11:28:08+00:00</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8428,14 +8428,14 @@
         </is>
       </c>
       <c r="B206" s="2" t="n">
+        <v>28490000</v>
+      </c>
+      <c r="C206" s="2" t="n">
         <v>38990000</v>
       </c>
-      <c r="C206" s="2" t="n">
-        <v>28490000</v>
-      </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>28490000</v>
+        <v>26990000</v>
       </c>
       <c r="C207" s="2" t="inlineStr"/>
       <c r="D207" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T07:06:05+00:00</t>
+          <t>2026-10-14T11:40:52+00:00</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>32990000</v>
+        <v>32690000</v>
       </c>
       <c r="C208" s="2" t="inlineStr"/>
       <c r="D208" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T15:55:11+00:00</t>
+          <t>2026-10-14T11:49:00+00:00</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8544,14 +8544,14 @@
         </is>
       </c>
       <c r="B209" s="2" t="n">
+        <v>44990000</v>
+      </c>
+      <c r="C209" s="2" t="n">
         <v>49990000</v>
       </c>
-      <c r="C209" s="2" t="n">
-        <v>44990000</v>
-      </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr"/>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9040,14 +9040,14 @@
         </is>
       </c>
       <c r="B222" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="C222" s="2" t="n">
         <v>32490000</v>
       </c>
-      <c r="C222" s="2" t="n">
-        <v>26990000</v>
-      </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr"/>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9118,14 +9118,14 @@
         </is>
       </c>
       <c r="B224" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="C224" s="2" t="n">
         <v>27490000</v>
       </c>
-      <c r="C224" s="2" t="n">
-        <v>18990000</v>
-      </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-31%</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9350,14 +9350,14 @@
         </is>
       </c>
       <c r="B230" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="C230" s="2" t="n">
         <v>32590000</v>
       </c>
-      <c r="C230" s="2" t="n">
-        <v>29990000</v>
-      </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9390,14 +9390,14 @@
         </is>
       </c>
       <c r="B231" s="2" t="n">
+        <v>37990000</v>
+      </c>
+      <c r="C231" s="2" t="n">
         <v>39990000</v>
       </c>
-      <c r="C231" s="2" t="n">
-        <v>37990000</v>
-      </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9430,14 +9430,14 @@
         </is>
       </c>
       <c r="B232" s="2" t="n">
+        <v>34990000</v>
+      </c>
+      <c r="C232" s="2" t="n">
         <v>35990000</v>
       </c>
-      <c r="C232" s="2" t="n">
-        <v>34990000</v>
-      </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9470,14 +9470,14 @@
         </is>
       </c>
       <c r="B233" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="C233" s="2" t="n">
         <v>42990000</v>
       </c>
-      <c r="C233" s="2" t="n">
-        <v>38990000</v>
-      </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9510,14 +9510,14 @@
         </is>
       </c>
       <c r="B234" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="C234" s="2" t="n">
         <v>48990000</v>
       </c>
-      <c r="C234" s="2" t="n">
-        <v>40990000</v>
-      </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:43</t>
+          <t>2026-10-15 00:14:01</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T05:10:11+00:00</t>
+          <t>2026-10-14T14:59:40+00:00</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10090,14 +10090,14 @@
         </is>
       </c>
       <c r="B249" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="C249" s="2" t="n">
         <v>24590000</v>
       </c>
-      <c r="C249" s="2" t="n">
-        <v>21990000</v>
-      </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T09:14:05+00:00</t>
+          <t>2026-10-14T04:41:05+00:00</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10602,14 +10602,14 @@
         </is>
       </c>
       <c r="B262" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="C262" s="2" t="n">
         <v>51990000</v>
       </c>
-      <c r="C262" s="2" t="n">
-        <v>39990000</v>
-      </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:02</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11212,14 +11212,14 @@
         </is>
       </c>
       <c r="B278" s="2" t="n">
+        <v>33790000</v>
+      </c>
+      <c r="C278" s="2" t="n">
         <v>34390000</v>
       </c>
-      <c r="C278" s="2" t="n">
-        <v>33790000</v>
-      </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr"/>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11252,14 +11252,14 @@
         </is>
       </c>
       <c r="B279" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="C279" s="2" t="n">
         <v>40990000</v>
       </c>
-      <c r="C279" s="2" t="n">
-        <v>39990000</v>
-      </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr"/>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11716,14 +11716,14 @@
         </is>
       </c>
       <c r="B291" s="2" t="n">
+        <v>32990000</v>
+      </c>
+      <c r="C291" s="2" t="n">
         <v>38990000</v>
       </c>
-      <c r="C291" s="2" t="n">
-        <v>32990000</v>
-      </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr"/>
@@ -11745,7 +11745,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 10:55:45</t>
+          <t>2026-10-15 00:14:03</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1006,14 +1006,14 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>112590000</v>
+        <v>114990000</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>125990000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T04:28:17+00:00</t>
+          <t>2026-10-15T04:08:28+00:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>51990000</v>
+        <v>51290000</v>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T03:11:08+00:00</t>
+          <t>2026-10-15T04:33:48+00:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>130990000</v>
+        <v>128990000</v>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T16:11:32+00:00</t>
+          <t>2026-10-15T04:05:46+00:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>25990000</v>
+        <v>25490000</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T15:03:00+00:00</t>
+          <t>2026-10-15T04:43:16+00:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>33990000</v>
+        <v>31490000</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T05:54:35+00:00</t>
+          <t>2026-10-15T04:53:42+00:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:42</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>156490000</v>
+        <v>155990000</v>
       </c>
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T11:18:02+00:00</t>
+          <t>2026-10-15T04:02:40+00:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:06</t>
+          <t>2026-10-16 00:07:41</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:13</t>
+          <t>2026-10-16 00:07:52</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:01</t>
+          <t>2026-10-16 00:07:48</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10130,14 +10130,14 @@
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>195990000</v>
+        <v>199000000</v>
       </c>
       <c r="C250" s="2" t="n">
-        <v>199000000</v>
+        <v>199990000</v>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr"/>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T09:01:38+00:00</t>
+          <t>2026-10-15T03:25:58+00:00</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -10968,12 +10968,12 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T06:42:49+00:00</t>
+          <t>2026-10-15T03:53:27+00:00</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:02</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>53990000</v>
+        <v>54990000</v>
       </c>
       <c r="C286" s="2" t="inlineStr"/>
       <c r="D286" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T04:50:16+00:00</t>
+          <t>2026-10-15T04:41:17+00:00</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>222990000</v>
+        <v>220990000</v>
       </c>
       <c r="C287" s="2" t="inlineStr"/>
       <c r="D287" s="2" t="inlineStr">
@@ -11584,12 +11584,12 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T09:04:38+00:00</t>
+          <t>2026-10-15T03:48:30+00:00</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>139990000</v>
+        <v>135990000</v>
       </c>
       <c r="C288" s="2" t="inlineStr"/>
       <c r="D288" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T09:05:41+00:00</t>
+          <t>2026-10-15T03:50:10+00:00</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11745,7 +11745,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 00:14:03</t>
+          <t>2026-10-16 00:07:56</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J304"/>
+  <dimension ref="A1:J297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PW-TS051W</t>
+          <t>Laptop ASUS ROG Strix G16 G614PW-TS051W (Ryzen 9 8940HX | RTX 5080 | 16GB | 512GB)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -524,12 +524,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:45:45+00:00</t>
+          <t>2026-10-18T05:09:51+00:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -881,14 +881,14 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt P16 H7606WP SR335W (Ryzen AI 9 HX 370 | RTX 5070 | 64GB | 2TB | 16inch OLED)</t>
+          <t>Laptop ASUS ProArt P16 H7606WP-SR335W (Ryzen AI 9 HX 370 | RTX 5070 | 64GB | 2TB | 16inch OLED)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -914,12 +914,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T03:23:50+00:00</t>
+          <t>2026-10-18T05:32:01+00:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:11:03+00:00</t>
+          <t>2026-10-18T04:20:47+00:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:10:03+00:00</t>
+          <t>2026-10-18T04:20:27+00:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1028,19 +1028,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:12:29+00:00</t>
+          <t>2026-10-18T05:10:11+00:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt PX13 HN7306EA LX050W (Ryzen AI MAX+ 395 | Radeon Graphics | 32GB | 1TB | 3K OLED)</t>
+          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI MAX+ 395 | Radeon Graphics | 32GB | 1TB | 3K OLED)</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T03:25:31+00:00</t>
+          <t>2026-10-18T05:01:14+00:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1104,19 +1104,19 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T20:58:18+00:00</t>
+          <t>2026-10-18T04:53:41+00:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS ROG Zephyrus G16 GU606AW TB121W (Ultra 9 386H | RTX 5080 | 32GB | 1TB | 16.0 WQXGA OLED 240Hz)</t>
+          <t>Laptop Gaming ASUS ROG Zephyrus G16 GU606AW-TB121W (Ultra 9 386H | RTX 5080 | 32GB | 1TB | 16.0 WQXGA OLED 240Hz)</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1144,19 +1144,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:08:28+00:00</t>
+          <t>2026-10-18T04:57:49+00:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PH-TS118W ( Ryzen 9 8940HX | 16GB  | 512GB | RTX 5050 )</t>
+          <t>Laptop ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9 8940HX | 16GB | 512GB | RTX 5050)</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T03:40:01+00:00</t>
+          <t>2026-10-18T05:04:06+00:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1220,19 +1220,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:33:48+00:00</t>
+          <t>2026-10-18T05:04:46+00:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PP-TS112W</t>
+          <t>Laptop ASUS ROG Strix G16 G614PP-TS112W (Ryzen 9 8940HX | RTX 5070 | 16GB | 512GB)</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1258,19 +1258,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T03:11:25+00:00</t>
+          <t>2026-10-18T05:07:31+00:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ROG Strix G16 G614PR TS103W (Ryzen 9 8940HX | RTX 5070Ti | 16GB | 512GB | 16 inch 2.5K 100% sRGB)</t>
+          <t>Laptop ASUS ROG Strix G16 G614PR-TS103W (Ryzen 9 8940HX | RTX 5070 Ti | 16GB | 512GB | 16 inch 2.5K 100% sRGB)</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T02:05:12+00:00</t>
+          <t>2026-10-18T05:00:56+00:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1334,19 +1334,19 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T11:14:33+00:00</t>
+          <t>2026-10-18T05:49:06+00:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS ROG Zephyrus G16 GU606AW TB052WS (Ultra 9 386H | RTX 5080 | 64GB | 1TB | 16.0 inch OLED 240Hz)</t>
+          <t>Laptop Gaming ASUS ROG Zephyrus G16 GU606AW-TB052WS (Ultra 9 386H | RTX 5080 | 64GB | 1TB | 16.0 inch OLED 240Hz)</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1372,19 +1372,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:05:46+00:00</t>
+          <t>2026-10-18T05:55:18+00:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus TUF F16 FX608JHI-TU210W (Intel Core i5-14450HX | RTX  5050 | 16GB | 512GB | 16 inch WUXGA)</t>
+          <t>Laptop Asus TUF F16 FX608JHI-TU210W (Intel Core i5-14450HX | RTX 5050 | 16GB | 512GB | 16 inch WUXGA)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -1410,19 +1410,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11T05:16:27+00:00</t>
+          <t>2026-10-18T05:02:51+00:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS TUF A16 FA608UHI TU121W (Ryzen 7 260 | 16GB | 512GB | RTX 5050 | 16 inch)</t>
+          <t>Laptop Gaming ASUS TUF A16 FA608UHI-TU121W (Ryzen 7 260 | 16GB | 512GB | RTX 5050 | 16 inch)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11T04:08:55+00:00</t>
+          <t>2026-10-18T05:03:15+00:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T05:05:13+00:00</t>
+          <t>2026-10-18T04:14:10+00:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T13:45:19+00:00</t>
+          <t>2026-10-18T05:07:13+00:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1562,19 +1562,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T05:12:06+00:00</t>
+          <t>2026-10-18T04:49:34+00:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS TUF A16 FA608UMI TU162W (Ryzen 7 260 | 16GB| 512GB| RTX 5060 | 16 inch)</t>
+          <t>Laptop Gaming ASUS TUF A16 FA608UMI-TU162W (Ryzen 7 260 | 16GB | 512GB | RTX 5060 | 16 inch)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1600,19 +1600,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T06:46:47+00:00</t>
+          <t>2026-10-18T05:04:26+00:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS TUF A14 FA401EA RG041W (Ryzen AI MAX+ 392 | Radeon 8060S| 32GB | 512GB | 14 inch)</t>
+          <t>Laptop Gaming ASUS TUF A14 FA401EA-RG041W (Ryzen AI MAX+ 392 | Radeon 8060S | 32GB | 512GB | 14 inch)</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T04:32:49+00:00</t>
+          <t>2026-10-18T05:05:18+00:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T11:17:45+00:00</t>
+          <t>2026-10-18T04:19:48+00:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:36</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T09:30:15+00:00</t>
+          <t>2026-10-17T17:44:38+00:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3921,14 +3921,14 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus AI V16 V3607VJ-TK189W (Core 5 | RTX 3050 | 16GB | 512GB | 144Hz)</t>
+          <t>Laptop Gaming Asus AI V16 V3607VJ-TK189W (Core 5 210H | RTX 3050 | 16GB | 512GB | 144Hz)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T01:04:36+00:00</t>
+          <t>2026-10-18T05:00:35+00:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4072,19 +4072,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:43:50+00:00</t>
+          <t>2026-10-17T17:44:18+00:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus AI V16 V3607VU-TK416W (Core 5 | RTX 4050 | 16GB | 512GB | 144Hz)</t>
+          <t>Laptop Gaming Asus AI V16 V3607VU-TK416W (Core 5 210H | RTX 4050 | 16GB | 512GB | 144Hz)</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -4110,19 +4110,19 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T08:22:21+00:00</t>
+          <t>2026-10-18T05:02:08+00:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS ROG Flow Z13 GZ302EA-RU145WS (Ryzen AI MAX | AMD Radeon | 128GB | 1TB | 2.5K)</t>
+          <t>Laptop Gaming ASUS ROG Flow Z13 GZ302EA-RU145WS (Ryzen AI MAX+ 395 | AMD Radeon | 128GB | 1TB | 2.5K)</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -4150,19 +4150,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T02:45:01+00:00</t>
+          <t>2026-10-18T05:08:28+00:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming ASUS ROG Flow Z13 GZ302EA-RU232WS (Ryzen AI MAX | AMD Radeon | 64GB | 1TB | 2.5K)</t>
+          <t>Laptop Gaming ASUS ROG Flow Z13 GZ302EA-RU232WS (Ryzen AI MAX+ 395 | AMD Radeon | 64GB | 1TB | 2.5K)</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T02:33:50+00:00</t>
+          <t>2026-10-18T05:47:13+00:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22T10:59:22+00:00</t>
+          <t>2026-10-18T05:08:10+00:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4271,14 +4271,14 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus ROG Strix G16 G614PH-RV176W ( Ryzen 9 8940HX | 16GB  | 512GB | RTX 5050 | 165Hz )</t>
+          <t>Laptop Gaming Asus ROG Strix G16 G614PH-RV176W (Ryzen 9 8940HX | 16GB | 512GB | RTX 5050 | 165Hz)</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -4304,19 +4304,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T03:34:34+00:00</t>
+          <t>2026-10-18T05:03:48+00:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus ROG Strix G16 G614PP RV262W (Ryen 9 8940HX | RTX 5070 |16GB | 512GB | 16 inch WUXGA 165Hz)</t>
+          <t>Laptop Gaming Asus ROG Strix G16 G614PP-RV262W (Ryzen 9 8940HX | RTX 5070 | 16GB | 512GB | 16 inch WUXGA 165Hz)</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4332,7 +4332,7 @@
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5070 | Màn hình: 16" 2.5K 165Hz</t>
+          <t>Thương hiệu: Asus | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5070 | Màn hình: 16" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -4342,19 +4342,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:30:24+00:00</t>
+          <t>2026-10-18T06:08:54+00:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus ROG Strix G16 G614PR RV060W (Ryen 9 8940HX | 16GB | 1TB | 16 inch WUXGA 165Hz | RTX 5070 Ti)</t>
+          <t>Laptop Gaming Asus ROG Strix G16 G614PR-RV060W (Ryzen 9 8940HX | RTX 5070 Ti | 16GB | 1TB | 16 inch WUXGA 165Hz)</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T03:03:59+00:00</t>
+          <t>2026-10-18T05:59:25+00:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T11:13:09+00:00</t>
+          <t>2026-10-18T05:23:58+00:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:26:18+00:00</t>
+          <t>2026-10-18T05:17:24+00:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T12:11:39+00:00</t>
+          <t>2026-10-18T04:55:39+00:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4532,19 +4532,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T07:34:01+00:00</t>
+          <t>2026-10-18T07:24:46+00:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus ROG Zephyrus G14 GU405AR SY016W (Ultra 9 386H | RTX 5070 Ti | 32GB | 1TB | 14 inch)</t>
+          <t>Laptop Gaming Asus ROG Zephyrus G14 GU405AR-SY016W (Ultra 9 386H | RTX 5070 Ti | 32GB | 1TB | 14 inch)</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -4570,19 +4570,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T03:25:58+00:00</t>
+          <t>2026-10-18T05:02:38+00:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus ROG Zephyrus G16 GU606AM-TB032W (Ultra 9 386H | RTX 5060 |  32GB | 1TB | 16 inch)</t>
+          <t>Laptop Gaming Asus ROG Zephyrus G16 GU606AM-TB032W (Ultra 9 386H | RTX 5060 | 32GB | 1TB | 16 inch)</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -4608,19 +4608,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T16:47:40+00:00</t>
+          <t>2026-10-18T05:01:32+00:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus ROG Zephyrus G16 GU606AR-TB027W (Core Ultra 9 386H | RTX 5070Ti | 32GB | 1TB | 16 inch 2.5K OLED)</t>
+          <t>Laptop Gaming Asus ROG Zephyrus G16 GU606AR-TB027W (Core Ultra 9 386H | RTX 5070 Ti | 32GB | 1TB | 16 inch 2.5K OLED)</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T10:07:52+00:00</t>
+          <t>2026-10-18T05:02:58+00:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4684,12 +4684,12 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:02:40+00:00</t>
+          <t>2026-10-18T05:58:50+00:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4804,19 +4804,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T04:57:00+00:00</t>
+          <t>2026-10-17T18:09:13+00:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus TUF A16 FA607NUQ RL007W (Ryzen 7 170 | RTX 4050 | 16GB | 512 GB | 16 inch)</t>
+          <t>Laptop Gaming Asus TUF A16 FA607NUQ-RL007W (Ryzen 7 170 | RTX 4050 | 16GB | 512GB | 16 inch)</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T06:32:40+00:00</t>
+          <t>2026-10-18T05:02:30+00:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4918,12 +4918,12 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T09:57:41+00:00</t>
+          <t>2026-10-18T04:52:43+00:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T03:03:38+00:00</t>
+          <t>2026-10-18T04:16:54+00:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T14:25:14+00:00</t>
+          <t>2026-10-18T05:27:47+00:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5146,12 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:32:16+00:00</t>
+          <t>2026-10-18T05:29:46+00:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:52</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:52:59+00:00</t>
+          <t>2026-10-18T05:34:37+00:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T04:14:58+00:00</t>
+          <t>2026-10-18T05:31:49+00:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:13:16+00:00</t>
+          <t>2026-10-18T06:18:11+00:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:02:20+00:00</t>
+          <t>2026-10-18T06:18:22+00:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5464,12 +5464,12 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:12:09+00:00</t>
+          <t>2026-10-18T06:18:46+00:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T16:10:06+00:00</t>
+          <t>2026-10-18T05:34:50+00:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T11:29:51+00:00</t>
+          <t>2026-10-18T05:32:37+00:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:01:14+00:00</t>
+          <t>2026-10-18T06:17:57+00:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T05:22:27+00:00</t>
+          <t>2026-10-18T05:32:26+00:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
@@ -5694,259 +5694,253 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:53:40+00:00</t>
+          <t>2026-10-18T06:18:57+00:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte AORUS 16X 9KG 43VNC54SH (i7-13650HX | RTX 4060 | 16GB | 1TB | 100% sRGB)</t>
+          <t>Laptop Gaming Gigabyte Aorus Master 16 BYH-C5VNE64SH</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>27990000</v>
+        <v>94890000</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>36990000</v>
+        <v>109990000</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>-24%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4060 | Màn hình: 16" WQXGA 165Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 16GB | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-gigabyte-aorus-16x-9kg-43vnc54sh</t>
+          <t>https://xgear.net/products/laptop-gaming-gigabyte-aorus-master-16-byh-c5vne64sh</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:47:27+00:00</t>
+          <t>2026-10-18T06:19:20+00:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte AORUS 16X ASG 53VNC54SH</t>
+          <t>Laptop Gaming HP HyperX Omen 15-ga0091TX D72D7PA (Core i5-14450HX | RTX 5060 | 16GB | 512GB | QHD)</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>43990000</v>
-      </c>
+        <v>48990000</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr"/>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4070 | Màn hình: 16" WQXGA 165Hz</t>
+          <t>Thương hiệu: HP | CPU: i5-14450HX | RAM: 16GB DDR5 | Ổ cứng: 512TB SSD | VGA: RTX 5060 | Màn hình: 15.3" 2K 165Hz</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-gigabyte-aorus-16x-asg-53vnc54sh</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-hyperx-omen-15-ga0091tx-d72d7pa</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:56:43+00:00</t>
+          <t>2026-10-13T09:08:55+00:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte AORUS 16X ASG 53VNC94SH</t>
+          <t>Laptop Gaming HP HyperX Omen 15-ga0091TX D72D8PA (Core i5-14450HX | RTX 5050 | 16GB | 512GB | QHD)</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>41990000</v>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr"/>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4070 | Màn hình: 16" QHD+ 165Hz</t>
+          <t>Thương hiệu: HP | CPU: i5-14450HX | RAM: 16GB DDR5 | Ổ cứng: 512TB SSD | VGA: RTX 5050 | Màn hình: 15.3" 2K 165Hz</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-gigabyte-aorus-16x-asg-53vnc94sh</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-hyperx-omen-15-ga0091tx-d72d8pa</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:57:01+00:00</t>
+          <t>2026-10-13T09:03:59+00:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte Aorus Master 16 BYH-C5VNE64SH</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="n">
-        <v>94890000</v>
-      </c>
+          <t>Laptop Gaming HP VICTUS 15 fa2731TX - B85LNPA</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr"/>
       <c r="C139" s="2" t="n">
-        <v>109990000</v>
+        <v>33990000</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-100%</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 16GB | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: HP | CPU: i5 13420H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-gigabyte-aorus-master-16-byh-c5vne64sh</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-15-fa2731tx-b85lnpa</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T04:03:28+00:00</t>
+          <t>2026-07-29T10:27:04+00:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte G6X 9KG 43VN853SH</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="n">
-        <v>27590000</v>
-      </c>
-      <c r="C140" s="2" t="inlineStr"/>
+          <t>Laptop Gaming HP VICTUS 15-fa2732TX B85LPPA</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="n">
+        <v>33990000</v>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-100%</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4060 | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: HP | CPU: i5 13420H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-gigabyte-g6x-9kg-43vn853sh</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-15-fa2732tx-b85lppa</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:58:31+00:00</t>
+          <t>2026-07-29T10:34:04+00:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte G6X 9KG 43VN854SH</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="n">
-        <v>28290000</v>
-      </c>
-      <c r="C141" s="2" t="inlineStr"/>
+          <t>Laptop Gaming HP VICTUS 16-r0228TX 9Q979PA</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr"/>
+      <c r="C141" s="2" t="n">
+        <v>35990000</v>
+      </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-100%</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4060 | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: HP | CPU: i5 13500H | RAM: 32GB DDR5 | Ổ cứng: 512GB M.2 NVMe™ PCIe® 4.0 SSD | VGA: RTX 4050 6GB | Màn hình: 16.1" inch</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-gigabyte-g6x-9kg-43vn854sh</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-r0228tx-9q979pa</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:14:47+00:00</t>
+          <t>2026-07-29T10:36:25+00:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte G6X 9MG 42VN853SH</t>
+          <t>Laptop Gaming HP Victus 16-r0298TX AE0N5PA</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>25690000</v>
+        <v>34990000</v>
       </c>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr">
@@ -5958,34 +5952,32 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: HP | CPU: i5 13500HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4060 8GB | Màn hình: 16.1" FHD 144Hz</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-gigabyte-g6x-9mg-42vn853sh</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-r0298tx-ae0n5pa</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:57:53+00:00</t>
+          <t>2026-10-04T15:26:09+00:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte G6X 9MG 42VN854SH</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="n">
-        <v>26290000</v>
-      </c>
+          <t>Laptop Gaming HP Victus 16-r1178TX A2NN2PA</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr"/>
       <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr">
         <is>
@@ -5996,34 +5988,32 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4050 | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: HP | CPU: i5 14450HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4060 8GB | Màn hình: 16.1" FHD 144Hz</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-gigabyte-g6x-9mg-42vn854sh</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-r1178tx-a2nn2pa</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:57:36+00:00</t>
+          <t>2026-07-29T10:40:21+00:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP HyperX Omen 15-ga0091TX D72D7PA (Core i5-14450HX | RTX 5060 | 16GB | 512GB | QHD)</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="n">
-        <v>48990000</v>
-      </c>
+          <t>Laptop Gaming HP Victus 16-r1182TX A2NN6PA</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="2" t="inlineStr">
         <is>
@@ -6034,34 +6024,32 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: i5-14450HX | RAM: 16GB DDR5 | Ổ cứng: 512TB SSD | VGA: RTX 5060 | Màn hình: 15.3" 2K 165Hz</t>
+          <t>Thương hiệu: HP | CPU: i5 14450HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4050 6GB | Màn hình: 16.1" FHD 144Hz</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-hyperx-omen-15-ga0091tx-d72d7pa</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-r1182tx-a2nn6pa</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:08:55+00:00</t>
+          <t>2026-07-29T10:32:56+00:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP HyperX Omen 15-ga0091TX D72D8PA (Core i5-14450HX | RTX 5050 | 16GB | 512GB | QHD)</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="n">
-        <v>46990000</v>
-      </c>
+          <t>Laptop Gaming HP Victus 16-s0138AX 9Q985PA</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr"/>
       <c r="C145" s="2" t="inlineStr"/>
       <c r="D145" s="2" t="inlineStr">
         <is>
@@ -6072,148 +6060,142 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: i5-14450HX | RAM: 16GB DDR5 | Ổ cứng: 512TB SSD | VGA: RTX 5050 | Màn hình: 15.3" 2K 165Hz</t>
+          <t>Thương hiệu: HP | CPU: R7 7840HS | RAM: 32GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4070 8GB | Màn hình: 16.1" FHD 144Hz</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-hyperx-omen-15-ga0091tx-d72d8pa</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s0138ax-9q985pa</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:03:59+00:00</t>
+          <t>2026-07-29T10:31:26+00:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP VICTUS 15 fa2731TX - B85LNPA</t>
+          <t>Laptop Gaming HP Victus 16-s1141AX AZ0C6PA</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr"/>
-      <c r="C146" s="2" t="n">
-        <v>33990000</v>
-      </c>
+      <c r="C146" s="2" t="inlineStr"/>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>-100%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: i5 13420H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: HP | CPU: R5 8460H | RAM: 16GB DDR5 | Ổ cứng: 512SSD | VGA: RTX 4050 8GB</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-15-fa2731tx-b85lnpa</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s1141ax-az0c6pa</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:27:04+00:00</t>
+          <t>2026-07-29T10:28:13+00:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP VICTUS 15-fa2732TX B85LPPA</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr"/>
-      <c r="C147" s="2" t="n">
-        <v>33990000</v>
-      </c>
+          <t>Laptop Gaming HP Victus 16-s1142AX AZ0C7PA (R7-8845HS | RTX 4060 | 16G | 512SSD | 16.1inch FHD 165Hz)</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>36990000</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr"/>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>-100%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: i5 13420H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: HP | CPU: R7 8845HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4060 8GB | Màn hình: 16.1" FHD 165Hz  100% sRGB</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-15-fa2732tx-b85lppa</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s1142ax-az0c7pa</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:34:04+00:00</t>
+          <t>2026-09-17T07:20:37+00:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP VICTUS 16-r0228TX 9Q979PA</t>
+          <t>Laptop Gaming HP Victus 16-s1143AX AZ0C8PA</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr"/>
-      <c r="C148" s="2" t="n">
-        <v>35990000</v>
-      </c>
+      <c r="C148" s="2" t="inlineStr"/>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>-100%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: i5 13500H | RAM: 32GB DDR5 | Ổ cứng: 512GB M.2 NVMe™ PCIe® 4.0 SSD | VGA: RTX 4050 6GB | Màn hình: 16.1" inch</t>
+          <t>Thương hiệu: HP | CPU: R7 8845HS | RAM: 32GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 16.1" FHD 165Hz  100% sRGB</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-r0228tx-9q979pa</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s1143ax-az0c8pa</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:36:25+00:00</t>
+          <t>2026-07-29T10:38:37+00:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-r0298TX AE0N5PA</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="n">
-        <v>34990000</v>
-      </c>
+          <t>Laptop Gaming HP Victus 16-s1145AX AZ0D0PA</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr"/>
       <c r="C149" s="2" t="inlineStr"/>
       <c r="D149" s="2" t="inlineStr">
         <is>
@@ -6224,69 +6206,77 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: i5 13500HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4060 8GB | Màn hình: 16.1" FHD 144Hz</t>
+          <t>Thương hiệu: HP | CPU: R7 8845HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 16.1" FHD 165Hz  100% sRGB</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-r0298tx-ae0n5pa</t>
+          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s1145ax-az0d0pa</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T15:26:09+00:00</t>
+          <t>2026-07-29T10:35:52+00:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-r1178TX A2NN2PA</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr"/>
-      <c r="C150" s="2" t="inlineStr"/>
+          <t>Laptop Gaming Lenovo Legion 5 15AHP10 83M0002XVN (Ryzen 7 | RTX 5050 | 24GB | 512GB | 165 Hz)</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>37590000</v>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>38990000</v>
+      </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: i5 14450HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4060 8GB | Màn hình: 16.1" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 260 | RAM: 24GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.1 2K 165Hz</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-r1178tx-a2nn2pa</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp10-83m0002xvn</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:40:21+00:00</t>
+          <t>2026-09-18T15:03:25+00:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-r1182TX A2NN6PA</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr"/>
-      <c r="C151" s="2" t="inlineStr"/>
+          <t>Laptop Gaming Lenovo Legion 5 15AHP10 83M0002YVN</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>36990000</v>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>36990000</v>
+      </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -6296,69 +6286,77 @@
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: i5 14450HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4050 6GB | Màn hình: 16.1" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 260 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.1 2K 165Hz</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-r1182tx-a2nn6pa</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp10-83m0002yvn</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:32:56+00:00</t>
+          <t>2026-07-05T11:50:59+00:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-s0138AX 9Q985PA</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr"/>
-      <c r="C152" s="2" t="inlineStr"/>
+          <t>Laptop Gaming LENOVO Legion 5 15AHP10 83M00030VN (AMD Ryzen 7 260 | RTX 5060 | 24GB | 1TB | 15.1 inch WQXGA OLED 165Hz)</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>42990000</v>
+      </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: R7 7840HS | RAM: 32GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4070 8GB | Màn hình: 16.1" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 260 | RAM: 24GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5060 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s0138ax-9q985pa</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp10-83m00030vn</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:31:26+00:00</t>
+          <t>2026-09-18T14:37:37+00:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-s1141AX AZ0C6PA</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr"/>
-      <c r="C153" s="2" t="inlineStr"/>
+          <t>Laptop Gaming Lenovo Legion 5 15AHP10 83M0005FVN (Ryzen 7 | RTX 5060 | 16GB | 32GB | OLED)</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>45990000</v>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>45990000</v>
+      </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -6368,33 +6366,33 @@
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: R5 8460H | RAM: 16GB DDR5 | Ổ cứng: 512SSD | VGA: RTX 4050 8GB</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 260 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 15.1 2K 165Hz</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s1141ax-az0c6pa</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp10-83m0005fvn</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:28:13+00:00</t>
+          <t>2026-06-17T08:59:56+00:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-s1142AX AZ0C7PA (R7-8845HS | RTX 4060 | 16G | 512SSD | 16.1inch FHD 165Hz)</t>
+          <t>Laptop Gaming Lenovo Legion 5 15AHP11 83Q7001HVN (R7 250 | RTX 5050 | 16GB | 512GB | OLED)</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>36990000</v>
+        <v>51490000</v>
       </c>
       <c r="C154" s="2" t="inlineStr"/>
       <c r="D154" s="2" t="inlineStr">
@@ -6406,32 +6404,34 @@
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: R7 8845HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4060 8GB | Màn hình: 16.1" FHD 165Hz  100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.3" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s1142ax-az0c7pa</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp11-83q7001hvn</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T07:20:37+00:00</t>
+          <t>2026-10-08T15:15:12+00:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-s1143AX AZ0C8PA</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr"/>
+          <t>Laptop Gaming Lenovo Legion 5 15AHP11-83Q7001JVN (Ryzen 7 250 | RTX 5060 | 16GB | 512GB | OLED)</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>52990000</v>
+      </c>
       <c r="C155" s="2" t="inlineStr"/>
       <c r="D155" s="2" t="inlineStr">
         <is>
@@ -6442,113 +6442,115 @@
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: R7 8845HS | RAM: 32GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 16.1" FHD 165Hz  100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.3" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s1143ax-az0c8pa</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp11-83q7001jvn</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:38:37+00:00</t>
+          <t>2026-10-08T15:15:02+00:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-s1145AX AZ0D0PA</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr"/>
-      <c r="C156" s="2" t="inlineStr"/>
+          <t>Laptop Gaming Lenovo Legion 5 15IAX10 83F0003BVN</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>53990000</v>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>57990000</v>
+      </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: R7 8845HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 16.1" FHD 165Hz  100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 255HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 | Màn hình: 15.1" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-hp-victus-16-s1145ax-az0d0pa</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iax10-83f0003bvn</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:35:52+00:00</t>
+          <t>2026-09-18T15:04:19+00:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion 5 15AHP10 83M0002XVN (Ryzen 7 | RTX 5050 | 24GB | 512GB | 165 Hz)</t>
+          <t>Laptop Gaming Lenovo Legion 5 15IAX10 83F0003CVN</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>37590000</v>
+        <v>48990000</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>38990000</v>
+        <v>52590000</v>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 260 | RAM: 24GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.1 2K 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 255HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 15.1" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp10-83m0002xvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iax10-83f0003cvn</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:03:25+00:00</t>
+          <t>2026-09-18T15:00:08+00:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion 5 15AHP10 83M0002YVN</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IAX11 83VK00A2VN (Ultra 7 251HX | RTX 5060 | 24GB | 512GB | OLED)</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>36990000</v>
-      </c>
+        <v>61990000</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr"/>
       <c r="D158" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -6558,77 +6560,73 @@
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 260 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.1 2K 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 251HX | RAM: 24GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5060 | Màn hình: 15.3" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp10-83m0002yvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iax11-83vk00a2vn</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T11:50:59+00:00</t>
+          <t>2026-10-18T03:46:04+00:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15AHP10 83M00030VN (AMD Ryzen 7 260 | RTX 5060 | 24GB | 1TB | 15.1 inch WQXGA OLED 165Hz)</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IAX11 83VK00A3VN (Ultra 7 251HX | RTX 5060 | 24GB | 512GB | OLED)</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>42990000</v>
-      </c>
+        <v>61990000</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr"/>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 260 | RAM: 24GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5060 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 251HX | RAM: 24GB DDR5 | VGA: RTX 5060 | Màn hình: 15.3" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp10-83m00030vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iax11-83vk00a3vn</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:37:37+00:00</t>
+          <t>2026-10-18T03:45:36+00:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion 5 15AHP10 83M0005FVN (Ryzen 7 | RTX 5060 | 16GB | 32GB | OLED)</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IPH11 83RW0023VN (Ultra 7 356H | RTX 5060 | 16GB | 512GB | OLED)</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>45990000</v>
-      </c>
+        <v>56990000</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr"/>
       <c r="D160" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -6638,1057 +6636,1059 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 260 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 15.1 2K 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5060 | Màn hình: 15.3" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp10-83m0005fvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iph11-83rw0023vn</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17T08:59:56+00:00</t>
+          <t>2026-10-18T03:47:29+00:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion 5 15AHP11 83Q7001HVN (R7 250 | RTX 5050 | 16GB | 512GB | OLED)</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY004GVN</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>51490000</v>
-      </c>
-      <c r="C161" s="2" t="inlineStr"/>
+        <v>57990000</v>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>59990000</v>
+      </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.3" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 24GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5070 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp11-83q7001hvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly004gvn</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:15:12+00:00</t>
+          <t>2026-10-08T15:12:56+00:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion 5 15AHP11-83Q7001JVN (Ryzen 7 250 | RTX 5060 | 16GB | 512GB | OLED)</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY004JVN</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>52990000</v>
-      </c>
-      <c r="C162" s="2" t="inlineStr"/>
+        <v>40490000</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>44990000</v>
+      </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.3" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 24GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 8GB | Màn hình: 15.1" 2.5K OLED 165Hz</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15ahp11-83q7001jvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly004jvn</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:15:02+00:00</t>
+          <t>2026-09-18T15:01:03+00:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion 5 15IAX10 83F0003BVN</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY004VVN</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>53990000</v>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>57990000</v>
-      </c>
+        <v>43890000</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr"/>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 255HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 | Màn hình: 15.1" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5060 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iax10-83f0003bvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly004vvn</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:04:19+00:00</t>
+          <t>2026-09-18T15:01:25+00:00</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion 5 15IAX10 83F0003CVN</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY00A6VN</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>52590000</v>
-      </c>
+        <v>38290000</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr"/>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 255HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 15.1" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iax10-83f0003cvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00a6vn</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:00:08+00:00</t>
+          <t>2026-06-27T09:04:49+00:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IAX11 83VK00A2VN (Ultra 7 251HX | RTX 5060 | 24GB | 512GB | OLED)</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY00A7VN (Core i7-14700HX | RTX 5050 | 16GB | 512GB | 15,1 inch)</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>61990000</v>
-      </c>
-      <c r="C165" s="2" t="inlineStr"/>
+        <v>38990000</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>44990000</v>
+      </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 251HX | RAM: 24GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5060 | Màn hình: 15.3" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iax11-83vk00a2vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00a7vn</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T02:59:50+00:00</t>
+          <t>2026-09-18T15:05:02+00:00</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IAX11 83VK00A3VN (Ultra 7 251HX | RTX 5060 | 24GB | 512GB | OLED)</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY00HQVN (Core i7 13650HX | RTX 5060 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>61990000</v>
-      </c>
-      <c r="C166" s="2" t="inlineStr"/>
+        <v>39990000</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>47590000</v>
+      </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 251HX | RAM: 24GB DDR5 | VGA: RTX 5060 | Màn hình: 15.3" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5060 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iax11-83vk00a3vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T03:00:45+00:00</t>
+          <t>2026-10-08T15:09:40+00:00</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IPH11 83RW0023VN (Ultra 7 356H | RTX 5060 | 16GB | 512GB | OLED)</t>
+          <t>Lenovo Legion 5 15IRX10 83LY00HRVN ( Core i7 13650HX | RTX 5050 | 16GB DDR5 | 512GB | 15.3″ WUXGA )</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>56990000</v>
-      </c>
-      <c r="C167" s="2" t="inlineStr"/>
+        <v>36990000</v>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>42990000</v>
+      </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5060 | Màn hình: 15.1" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15iph11-83rw0023vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hrvn</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T10:29:50+00:00</t>
+          <t>2026-10-08T15:09:58+00:00</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY004GVN</t>
+          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HWVN (Core i7 | RTX 5060 | 16GB | 512GB | OLED)</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>57990000</v>
+        <v>44990000</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>59990000</v>
+        <v>53390000</v>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 24GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5070 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 8GB | Màn hình: 15.1" 2.5K OLED 165Hz</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly004gvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hwvn</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:12:56+00:00</t>
+          <t>2026-10-10T09:39:59+00:00</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY004JVN</t>
+          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY00HYVN (Core i7 | RTX 5050 | 16GB | 1TB | OLED)</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>40490000</v>
+        <v>39990000</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>44990000</v>
+        <v>42990000</v>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 24GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 8GB | Màn hình: 15.1" 2.5K OLED 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.1" 2.5K OLED 165Hz</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly004jvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hyvn</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:01:03+00:00</t>
+          <t>2026-10-18T02:43:29+00:00</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY004VVN</t>
+          <t>Laptop Gaming LENOVO Legion 7 16IAX10 83KY001UVN (Ultra 9 275HX | RTX 5060 | 32GB | 1TB | 16 inch WQXGA OLED 240Hz)</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>43890000</v>
-      </c>
-      <c r="C170" s="2" t="inlineStr"/>
+        <v>63990000</v>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>75990000</v>
+      </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5060 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5060 8GB | Màn hình: 16" WQXGA 240Hz</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly004vvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-7-16iax10-83ky001uvn</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:01:25+00:00</t>
+          <t>2026-07-20T06:15:22+00:00</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY00A6VN</t>
+          <t>Laptop Gaming LENOVO Legion 7 16IAX10 83KY001VVN (Intel Core Ultra 9 275HX | RTX 5070 | 32GB | 1TB | 16 inch WQXGA OLED 240Hz)</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>38290000</v>
-      </c>
-      <c r="C171" s="2" t="inlineStr"/>
+        <v>69990000</v>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>83990000</v>
+      </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5070 8GB | Màn hình: 16" WQXGA 240Hz</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00a6vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-7-16iax10-83ky001vvn</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T09:04:49+00:00</t>
+          <t>2026-10-01T06:38:19+00:00</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY00A7VN (Core i7-14700HX | RTX 5050 | 16GB | 512GB | 15,1 inch)</t>
+          <t>Laptop Gaming Lenovo Legion Pro 5 16IAX10 83F3002GVN</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>38990000</v>
+        <v>59990000</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>44990000</v>
+        <v>76990000</v>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.1" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 | Màn hình: 16" 2.5K OLED 165Hz</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00a7vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-5-16iax10-83f3002gvn</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:05:02+00:00</t>
+          <t>2026-10-08T15:11:47+00:00</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY00HQVN (Core i7 13650HX | RTX 5060 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo Legion Pro 5 16IAX10 83F3003VVN</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>39990000</v>
+        <v>54990000</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>47590000</v>
+        <v>72390000</v>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-24%</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5060 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" 2.5K OLED 165Hz</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hqvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-5-16iax10-83f3003vvn</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:09:40+00:00</t>
+          <t>2026-10-18T02:56:13+00:00</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Lenovo Legion 5 15IRX10 83LY00HRVN ( Core i7 13650HX | RTX 5050 | 16GB DDR5 | 512GB | 15.3″ WUXGA )</t>
+          <t>Laptop Gaming Lenovo Legion Pro 5 16IAX10 83F300CWVN (Ultra 7-251HX | RTX 5060 | 24GB | 1TB |16inch WQXGA OLED)</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>42990000</v>
-      </c>
+        <v>66990000</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr"/>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 251HX | RAM: 24GB DDR5 | Ổ cứng: 1TB SSD Gen 4 | VGA: RTX 5060</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hrvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-5-16iax10-83f300cwvn</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:09:58+00:00</t>
+          <t>2026-08-03T08:32:54+00:00</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion 5 15IRX10 83LY00HWVN (Core i7 | RTX 5060 | 16GB | 512GB | OLED)</t>
+          <t>Laptop Gaming LENOVO Legion Pro 7 16IAX10H 83F5008VVN</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>44990000</v>
+        <v>81990000</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>53390000</v>
+        <v>119990000</v>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-32%</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 8GB | Màn hình: 15.1" 2.5K OLED 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti 12GB | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hwvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f5008vvn</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T09:39:59+00:00</t>
+          <t>2026-07-20T04:26:41+00:00</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 5 15IRX10 83LY00HYVN (Core i7 | RTX 5050 | 16GB | 1TB | OLED)</t>
+          <t>Laptop Gaming Lenovo Legion Pro 7 16IAX10H 83F5008WVN</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>39990000</v>
+        <v>96990000</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>42990000</v>
+        <v>118990000</v>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14700HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 16 WQXGA 240Hz</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-5-15irx10-83ly00hyvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f5008wvn</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:04:40+00:00</t>
+          <t>2026-10-08T15:19:41+00:00</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 7 16IAX10 83KY001UVN (Ultra 9 275HX | RTX 5060 | 32GB | 1TB | 16 inch WQXGA OLED 240Hz)</t>
+          <t>Laptop Gaming LENOVO Legion Pro 7 16IAX10H 83F500ANVN (Ultra 9 275HX | RTX 5080 | 64GB | 1TB | 16 inch OLED)</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>63990000</v>
+        <v>81990000</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>75990000</v>
+        <v>156990000</v>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-48%</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5060 8GB | Màn hình: 16" WQXGA 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 16GB | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-7-16iax10-83ky001uvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500anvn</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T06:15:22+00:00</t>
+          <t>2026-10-18T02:54:28+00:00</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion 7 16IAX10 83KY001VVN (Intel Core Ultra 9 275HX | RTX 5070 | 32GB | 1TB | 16 inch WQXGA OLED 240Hz)</t>
+          <t>Laptop Gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Legion Pro 7i FIFA World Cup 26™ Edition)</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>69990000</v>
+        <v>83990000</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>83990000</v>
+        <v>109790000</v>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-23%</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5070 8GB | Màn hình: 16" WQXGA 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti | Màn hình: 16" WQXGA 240Hz</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-7-16iax10-83ky001vvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T06:38:19+00:00</t>
+          <t>2026-10-08T15:18:52+00:00</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion Pro 5 16IAX10 83F3002GVN</t>
+          <t>Laptop Gaming Lenovo LOQ 15AHP10 83JG0047VN (Ryzen 7 250 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>59990000</v>
+        <v>32490000</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>76990000</v>
+        <v>32990000</v>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 | Màn hình: 16" 2.5K OLED 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-5-16iax10-83f3002gvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15ahp10-83jg0047vn</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:11:47+00:00</t>
+          <t>2026-10-01T06:38:55+00:00</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion Pro 5 16IAX10 83F3003VVN</t>
+          <t>Laptop Gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7 250 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>54990000</v>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>72390000</v>
-      </c>
+        <v>40790000</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr"/>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>-24%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" 2.5K OLED 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.3" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-5-16iax10-83f3003vvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:10:35+00:00</t>
+          <t>2026-10-18T03:46:57+00:00</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion Pro 5 16IAX10 83F300CWVN (Ultra 7-251HX | RTX 5060 | 24GB | 1TB |16inch WQXGA OLED)</t>
+          <t>Laptop Gaming Lenovo LOQ 15APH8 82XT00BTVN</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>66990000</v>
-      </c>
-      <c r="C181" s="2" t="inlineStr"/>
+        <v>21890000</v>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>27362500</v>
+      </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 251HX | RAM: 24GB DDR5 | Ổ cứng: 1TB SSD Gen 4 | VGA: RTX 5060</t>
+          <t>Thương hiệu: Lenovo | CPU: R5 7640HS | RAM: 16GB DDR5 | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-5-16iax10-83f300cwvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15aph8-82xt00btvn</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T08:32:54+00:00</t>
+          <t>2026-05-18T15:56:06+00:00</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:35</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion Pro 7 16IAX10H 83F5008VVN</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0000GVN (R5 7535HS | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>81990000</v>
-      </c>
-      <c r="C182" s="2" t="n">
-        <v>119990000</v>
-      </c>
+        <v>37990000</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr"/>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>-32%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti 12GB | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 5 7535HS | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f5008vvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp10e-83s0000gvn</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T04:26:41+00:00</t>
+          <t>2026-10-08T14:47:16+00:00</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion Pro 7 16IAX10H 83F5008WVN</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000G7VN (Ryzen 5 150 | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>96990000</v>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>118990000</v>
-      </c>
+        <v>35990000</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr"/>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 16 WQXGA 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 5 150 | RAM: 16GB DDR5 | Ổ cứng: 512GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f5008wvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp10e-83s000g7vn</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:19:41+00:00</t>
+          <t>2026-08-01T10:08:14+00:00</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming LENOVO Legion Pro 7 16IAX10H 83F500ANVN (Ultra 9 275HX | RTX 5080 | 64GB | 1TB | 16 inch OLED)</t>
+          <t>Laptop Gaming Lenovo LOQ 15ARP9 83JC00HXVN (Ryzen 5 7235HS, RTX 3050 6GB, 100% sRGB)</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>81990000</v>
+        <v>21990000</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>156990000</v>
+        <v>27990000</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>-48%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 16GB | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R5 7235HS | RAM: 12GB DDR5 | Ổ cứng: 512GB | VGA: Geforce RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500anvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp9-83jc00hxvn</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T07:48:39+00:00</t>
+          <t>2026-09-18T13:38:48+00:00</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:35</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Legion Pro 7i FIFA World Cup 26™ Edition)</t>
+          <t>Laptop Gaming Lenovo LOQ 15ARP9 83JC00LVVN (Ryzen 5 7235HS, RTX 3050 6GB, 100% sRGB)</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>83990000</v>
+        <v>27990000</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>109790000</v>
+        <v>27990000</v>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>-23%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti | Màn hình: 16" WQXGA 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R5 7235HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: Geforce RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp9-83jc00lvvn</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:18:52+00:00</t>
+          <t>2026-10-10T13:57:36+00:00</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15AHP10 83JG0047VN (Ryzen 7 250 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IPH11 83SL000LVN (Ultra 7-356H | RTX 5060 | 16GB | 512 GB | 15.3 inch)</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>32490000</v>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>32990000</v>
-      </c>
+        <v>47290000</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr"/>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7-356H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15ahp10-83jg0047vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15iph11-83sl000lvn</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T06:38:55+00:00</t>
+          <t>2026-10-18T03:47:54+00:00</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7 250 | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IPH11E 83Y8000MVN (Ultra X7-358H | ARC B390 | 16GB | 512 GB | 15.3 inch WUXGA)</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>40790000</v>
+        <v>45990000</v>
       </c>
       <c r="C187" s="2" t="inlineStr"/>
       <c r="D187" s="2" t="inlineStr">
@@ -7700,36 +7700,36 @@
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 250 | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra X7-358H | RAM: 16GB LPDDR5X-9600 | Ổ cứng: 512GB | VGA: Intel ARC B390 | Màn hình: 15.3" WUXGA 165Hz</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15iph11e-83y8000mvn</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T03:43:24+00:00</t>
+          <t>2026-10-18T02:46:07+00:00</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15APH8 82XT00BTVN</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRH8 82XV00QQVN</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>21890000</v>
+        <v>15990000</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>27362500</v>
+        <v>19987500</v>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
@@ -7740,33 +7740,33 @@
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R5 7640HS | RAM: 16GB DDR5 | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 12450H | RAM: 8GB DDR5 | VGA: RTX 2050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15aph8-82xt00btvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irh8-82xv00qqvn</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18T15:56:06+00:00</t>
+          <t>2026-05-17T15:58:24+00:00</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0000GVN (R5 7535HS | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX10 83JE01N4VN (Core  i7-14650HX | RTX 5050 | 16GB | 512GB | 15.6 inch)</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>37990000</v>
+        <v>53990000</v>
       </c>
       <c r="C189" s="2" t="inlineStr"/>
       <c r="D189" s="2" t="inlineStr">
@@ -7778,115 +7778,115 @@
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 5 7535HS | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: i7-14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp10e-83s0000gvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx10-83je01n4vn</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:47:16+00:00</t>
+          <t>2026-08-01T10:15:20+00:00</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000G7VN (Ryzen 5 150 | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV003CVN (Core i5 | RTX 3050 |16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C190" s="2" t="inlineStr"/>
+        <v>25490000</v>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>31490000</v>
+      </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-19%</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 5 150 | RAM: 16GB DDR5 | Ổ cứng: 512GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp10e-83s000g7vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv003cvn</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T10:08:14+00:00</t>
+          <t>2026-10-18T02:08:54+00:00</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15ARP9 83JC00HXVN (Ryzen 5 7235HS, RTX 3050 6GB, 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01ALVN (Core i7-13650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>21990000</v>
+        <v>29990000</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>27990000</v>
+        <v>34990000</v>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R5 7235HS | RAM: 12GB DDR5 | Ổ cứng: 512GB | VGA: Geforce RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp9-83jc00hxvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:38:48+00:00</t>
+          <t>2026-10-18T02:55:07+00:00</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15ARP9 83JC00LVVN (Ryzen 5 7235HS, RTX 3050 6GB, 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01H2VN (Core i7-13650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="C192" s="2" t="n">
-        <v>27990000</v>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr"/>
       <c r="D192" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -7896,33 +7896,33 @@
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R5 7235HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: Geforce RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15arp9-83jc00lvvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01h2vn</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T13:57:36+00:00</t>
+          <t>2026-10-08T14:47:54+00:00</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IPH11 83SL000LVN (Ultra 7-356H | RTX 5060 | 16GB | 512 GB | 15.3 inch)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01H3VN (Core i7-13645HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>47290000</v>
+        <v>34590000</v>
       </c>
       <c r="C193" s="2" t="inlineStr"/>
       <c r="D193" s="2" t="inlineStr">
@@ -7934,33 +7934,33 @@
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7-356H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 8GB | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13645HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 100% sRGB</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15iph11-83sl000lvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01h3vn</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T03:41:17+00:00</t>
+          <t>2026-10-08T15:04:24+00:00</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IPH11E 83Y8000MVN (Ultra X7-358H | ARC B390 | 16GB | 512 GB | 15.3 inch WUXGA)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01MCVN (Core i7-14650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>45990000</v>
+        <v>44990000</v>
       </c>
       <c r="C194" s="2" t="inlineStr"/>
       <c r="D194" s="2" t="inlineStr">
@@ -7972,154 +7972,154 @@
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra X7-358H | RAM: 16GB LPDDR5X-9600 | Ổ cứng: 512GB | VGA: Intel ARC B390 | Màn hình: 15.3" WUXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15iph11e-83y8000mvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01mcvn</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T07:13:36+00:00</t>
+          <t>2026-10-18T02:55:37+00:00</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRH8 82XV00QQVN</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0006QVN (Ryzen 7 | RTX 3050 | 16GB | 512GB | 144Hz)</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>15990000</v>
+        <v>23990000</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>19987500</v>
+        <v>25490000</v>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 12450H | RAM: 8GB DDR5 | VGA: RTX 2050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irh8-82xv00qqvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10-83s0006qvn</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17T15:58:24+00:00</t>
+          <t>2026-10-01T06:37:19+00:00</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX10 83JE01N4VN (Core  i7-14650HX | RTX 5050 | 16GB | 512GB | 15.6 inch)</t>
+          <t>Laptop Lenovo LOQ 15ARP10E 83S0004FVN ( Ryzen 7 7735HS | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>53990000</v>
-      </c>
-      <c r="C196" s="2" t="inlineStr"/>
+        <v>26990000</v>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>35990000</v>
+      </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7-14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx10-83je01n4vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T10:15:20+00:00</t>
+          <t>2026-10-18T02:01:08+00:00</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV003CVN (Core i5 | RTX 3050 |16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0006RVN</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>25490000</v>
-      </c>
-      <c r="C197" s="2" t="n">
-        <v>31490000</v>
-      </c>
+        <v>28990000</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr"/>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv003cvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0006rvn</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T13:58:58+00:00</t>
+          <t>2026-10-16T05:23:14+00:00</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01ALVN (Core i7-13650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0007AVN</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>29990000</v>
+        <v>26990000</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>34990000</v>
+        <v>31490000</v>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
@@ -8130,33 +8130,33 @@
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0007avn</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:58:13+00:00</t>
+          <t>2026-09-18T13:38:09+00:00</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01H2VN (Core i7-13650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S000DCVN ( Ryzen 7 - 170 | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>33990000</v>
+        <v>29990000</v>
       </c>
       <c r="C199" s="2" t="inlineStr"/>
       <c r="D199" s="2" t="inlineStr">
@@ -8168,33 +8168,33 @@
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 170 | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01h2vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s000dcvn</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T14:47:54+00:00</t>
+          <t>2026-10-18T02:41:11+00:00</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01H3VN (Core i7-13645HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003XVN (Core 7 230H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>34590000</v>
+        <v>33990000</v>
       </c>
       <c r="C200" s="2" t="inlineStr"/>
       <c r="D200" s="2" t="inlineStr">
@@ -8206,33 +8206,33 @@
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13645HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01h3vn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003xvn</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:04:24+00:00</t>
+          <t>2026-10-18T03:48:23+00:00</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX9 83DV01MCVN (Core i7-14650HX | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003YVN (Core 7 230H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>44990000</v>
+        <v>28990000</v>
       </c>
       <c r="C201" s="2" t="inlineStr"/>
       <c r="D201" s="2" t="inlineStr">
@@ -8244,113 +8244,111 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 4050 6GB | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-15irx9-83dv01mcvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003yvn</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T08:17:42+00:00</t>
+          <t>2026-10-18T03:48:51+00:00</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0006QVN (Ryzen 7 | RTX 3050 | 16GB | 512GB | 144Hz)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRX11 83SC003RVN (i5-13450HX | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>23990000</v>
+        <v>28490000</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>25490000</v>
+        <v>38990000</v>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr"/>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10-83s0006qvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irx11-83sc003rvn</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T06:37:19+00:00</t>
+          <t>2026-07-01T05:38:36+00:00</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo LOQ 15ARP10E 83S0004FVN ( Ryzen 7 7735HS | RTX 4050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003VVN (Core 5 205H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
         <v>26990000</v>
       </c>
-      <c r="C203" s="2" t="n">
-        <v>35990000</v>
-      </c>
+      <c r="C203" s="2" t="inlineStr"/>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0004fvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003vvn</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03T03:23:57+00:00</t>
+          <t>2026-10-18T03:49:20+00:00</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0006RVN</t>
+          <t>Laptop Gaming Lenovo LOQ Essential LOQ 15IRH11E 83Y9003WVN (Core 5 205H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>28990000</v>
+        <v>32690000</v>
       </c>
       <c r="C204" s="2" t="inlineStr"/>
       <c r="D204" s="2" t="inlineStr">
@@ -8362,73 +8360,73 @@
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0006rvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003wvn</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T05:23:14+00:00</t>
+          <t>2026-10-18T03:49:47+00:00</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S0007AVN</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX AI D2XWFKG-036VN (Ultra 7 | RTX 5060 | 16GB | 1TB | 2K)</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>26990000</v>
+        <v>44990000</v>
       </c>
       <c r="C205" s="2" t="n">
-        <v>31490000</v>
+        <v>49990000</v>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: R7 7735HS | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0007avn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-ai-d2xwfkg-036vn</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:38:09+00:00</t>
+          <t>2026-10-18T07:15:43+00:00</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S000DCVN ( Ryzen 7 - 170 | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WFK-074VN (i7 14650HX | 16GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>29990000</v>
+        <v>55990000</v>
       </c>
       <c r="C206" s="2" t="inlineStr"/>
       <c r="D206" s="2" t="inlineStr">
@@ -8440,33 +8438,33 @@
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 170 | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s000dcvn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-074vn</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T02:11:59+00:00</t>
+          <t>2026-10-18T07:13:02+00:00</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003XVN (Core 7 230H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14VFK-075VN (i9 14900HX | 32GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>33990000</v>
+        <v>64990000</v>
       </c>
       <c r="C207" s="2" t="inlineStr"/>
       <c r="D207" s="2" t="inlineStr">
@@ -8478,33 +8476,33 @@
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003xvn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-075vn</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T11:18:39+00:00</t>
+          <t>2026-10-05T06:34:58+00:00</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003YVN (Core 7 230H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 076VN (Core i9-14900HX | RTX 5050 | 32GB | 1TB SSD | QHD+)</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>28990000</v>
+        <v>58990000</v>
       </c>
       <c r="C208" s="2" t="inlineStr"/>
       <c r="D208" s="2" t="inlineStr">
@@ -8516,73 +8514,71 @@
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003yvn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-076vn</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T11:28:08+00:00</t>
+          <t>2026-10-18T07:29:36+00:00</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRX11 83SC003RVN (i5-13450HX | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 077VN (Core i7 14650HX | RTX 5050 | 16GB | 512GB | 16 inch)</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>28490000</v>
-      </c>
-      <c r="C209" s="2" t="n">
-        <v>38990000</v>
-      </c>
+        <v>49990000</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr"/>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr"/>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irx11-83sc003rvn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-077vn</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T05:38:36+00:00</t>
+          <t>2026-09-17T09:44:38+00:00</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003VVN (Core 5 205H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WGK</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>26990000</v>
+        <v>69990000</v>
       </c>
       <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="inlineStr">
@@ -8594,33 +8590,33 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003vvn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wgk</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T11:40:52+00:00</t>
+          <t>2026-08-13T04:42:13+00:00</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential LOQ 15IRH11E 83Y9003WVN (Core 5 205H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-051VN (Ultra 9 290HX Plus | 32GB | 1TB | RTX 5070 12GB | 16 inch)</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>32690000</v>
+        <v>74990000</v>
       </c>
       <c r="C211" s="2" t="inlineStr"/>
       <c r="D211" s="2" t="inlineStr">
@@ -8632,73 +8628,71 @@
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.6" FHD 165Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ Oled 165Hz</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003wvn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-051vn</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T11:49:00+00:00</t>
+          <t>2026-10-18T07:10:50+00:00</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX AI D2XWFKG-036VN (Ultra 7 | RTX 5060 | 16GB | 1TB | 2K)</t>
+          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-052VN  (Ultra 7 251HX | 16GB | 1TB | RTX 5070 12GB | 16 inch OLED 165Hz )</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="C212" s="2" t="n">
-        <v>49990000</v>
-      </c>
+        <v>63990000</v>
+      </c>
+      <c r="C212" s="2" t="inlineStr"/>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 251HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ OLED 165Hz</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-ai-d2xwfkg-036vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-052vn</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:58:22+00:00</t>
+          <t>2026-10-18T07:10:37+00:00</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WFK-074VN (i7 14650HX | 16GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>55990000</v>
+        <v>64990000</v>
       </c>
       <c r="C213" s="2" t="inlineStr"/>
       <c r="D213" s="2" t="inlineStr">
@@ -8710,33 +8704,33 @@
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-074vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T06:36:03+00:00</t>
+          <t>2026-10-18T07:12:50+00:00</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14VFK-075VN (i9 14900HX | 32GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>64990000</v>
+        <v>56990000</v>
       </c>
       <c r="C214" s="2" t="inlineStr"/>
       <c r="D214" s="2" t="inlineStr">
@@ -8748,33 +8742,33 @@
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 7 8840HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-075vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk-1</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T06:34:58+00:00</t>
+          <t>2026-10-18T07:12:37+00:00</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 076VN (Core i9-14900HX | RTX 5050 | 32GB | 1TB SSD | QHD+)</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WFK-067VN (Ryzen 9 8940HX | RTX 5060 | 16GB | 1TB | 16inch QHD+)</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>58990000</v>
+        <v>59990000</v>
       </c>
       <c r="C215" s="2" t="inlineStr"/>
       <c r="D215" s="2" t="inlineStr">
@@ -8786,33 +8780,33 @@
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-076vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wfk-067vn</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T07:29:48+00:00</t>
+          <t>2026-10-18T08:12:52+00:00</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 077VN (Core i7 14650HX | RTX 5050 | 16GB | 512GB | 16 inch)</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WGK-093VN (Ryzen 9 8940HX | RTX 5070 | 16GB | 1TB | 16inch QHD+)</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>49990000</v>
+        <v>65990000</v>
       </c>
       <c r="C216" s="2" t="inlineStr"/>
       <c r="D216" s="2" t="inlineStr">
@@ -8824,33 +8818,33 @@
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-077vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wgk-093vn</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T09:44:38+00:00</t>
+          <t>2026-10-12T04:33:12+00:00</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WGK</t>
+          <t>Laptop Gaming MSI Cyborg 15 A13VEK 2089VN</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>69990000</v>
+        <v>30990000</v>
       </c>
       <c r="C217" s="2" t="inlineStr"/>
       <c r="D217" s="2" t="inlineStr">
@@ -8862,71 +8856,73 @@
       <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wgk</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-a13vek-2089vn</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T04:42:13+00:00</t>
+          <t>2026-07-12T09:35:09+00:00</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-051VN (Ultra 9 290HX Plus | 32GB | 1TB | RTX 5070 12GB | 16 inch)</t>
+          <t>Laptop Gaming MSI Cyborg 15 B13WEKG-676VN</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
-        <v>74990000</v>
-      </c>
-      <c r="C218" s="2" t="inlineStr"/>
+        <v>26990000</v>
+      </c>
+      <c r="C218" s="2" t="n">
+        <v>32490000</v>
+      </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr"/>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ Oled 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-051vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wekg-676vn</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T09:41:30+00:00</t>
+          <t>2026-10-12T08:19:31+00:00</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-052VN  (Ultra 7 251HX | 16GB | 1TB | RTX 5070 12GB | 16 inch OLED 165Hz )</t>
+          <t>Laptop Gaming MSI Cyborg 15 B13WFKG 658VN</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>63990000</v>
+        <v>34490000</v>
       </c>
       <c r="C219" s="2" t="inlineStr"/>
       <c r="D219" s="2" t="inlineStr">
@@ -8938,71 +8934,73 @@
       <c r="F219" s="2" t="inlineStr"/>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 251HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ OLED 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-052vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wfkg-658vn</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T06:19:52+00:00</t>
+          <t>2026-06-26T01:55:59+00:00</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VE-2410VN (Core i5-13420H | RTX 4050 | 16GB | 512GB | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>64990000</v>
-      </c>
-      <c r="C220" s="2" t="inlineStr"/>
+        <v>18990000</v>
+      </c>
+      <c r="C220" s="2" t="n">
+        <v>27490000</v>
+      </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-31%</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13ve-2410vn</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T07:15:48+00:00</t>
+          <t>2026-10-18T07:12:25+00:00</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2608VN (i7 13620H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz )</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>56990000</v>
+        <v>28990000</v>
       </c>
       <c r="C221" s="2" t="inlineStr"/>
       <c r="D221" s="2" t="inlineStr">
@@ -9014,33 +9012,33 @@
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 7 8840HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk-1</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T07:16:04+00:00</t>
+          <t>2026-10-18T07:11:21+00:00</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WFK-067VN (Ryzen 9 8940HX | RTX 5060 | 16GB | 1TB | 16inch QHD+)</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2610VN (i5 13420H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>59990000</v>
+        <v>26490000</v>
       </c>
       <c r="C222" s="2" t="inlineStr"/>
       <c r="D222" s="2" t="inlineStr">
@@ -9052,33 +9050,33 @@
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wfk-067vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T04:31:12+00:00</t>
+          <t>2026-10-18T07:11:04+00:00</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WGK-093VN (Ryzen 9 8940HX | RTX 5070 | 16GB | 1TB | 16inch QHD+)</t>
+          <t>Laptop Gaming MSI Cyborg 15 Max C13WE-422VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5050 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>65990000</v>
+        <v>36990000</v>
       </c>
       <c r="C223" s="2" t="inlineStr"/>
       <c r="D223" s="2" t="inlineStr">
@@ -9090,33 +9088,33 @@
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wgk-093vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T04:33:12+00:00</t>
+          <t>2026-10-05T06:42:06+00:00</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 A13VEK 2089VN</t>
+          <t>Laptop Gaming MSI Cyborg 15 Max C13WF-421VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5060 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>30990000</v>
+        <v>41990000</v>
       </c>
       <c r="C224" s="2" t="inlineStr"/>
       <c r="D224" s="2" t="inlineStr">
@@ -9128,583 +9126,579 @@
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-a13vek-2089vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13wf-421vn</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12T09:35:09+00:00</t>
+          <t>2026-10-18T07:10:23+00:00</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 B13WEKG-676VN</t>
+          <t>Laptop Gaming MSI Katana 15 B13UDXK 2412VN (Core i5-13420H | RTX 3050 | 8GB | 1TB | 15.6 inch FHD)</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>26990000</v>
+        <v>22890000</v>
       </c>
       <c r="C225" s="2" t="n">
-        <v>32490000</v>
+        <v>25990000</v>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr"/>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wekg-676vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13udxk-2412vn</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T08:19:31+00:00</t>
+          <t>2026-10-18T07:35:06+00:00</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 B13WFKG 658VN</t>
+          <t>Laptop Gaming MSI Katana 15 B13VEK-2440VN (Core i7 | RTX 4050 | 16GB | 1TB | 144Hz)</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>34490000</v>
-      </c>
-      <c r="C226" s="2" t="inlineStr"/>
+        <v>29990000</v>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>32590000</v>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7-13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wfkg-658vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T01:55:59+00:00</t>
+          <t>2026-09-28T12:06:54+00:00</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VE-2410VN (Core i5-13420H | RTX 4050 | 16GB | 512GB | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WEK 027VN (Core i7 | RTX 5050 | 32GB | 512GB | 2K)</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>18990000</v>
+        <v>37990000</v>
       </c>
       <c r="C227" s="2" t="n">
-        <v>27490000</v>
+        <v>39990000</v>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>-31%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr"/>
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13ve-2410vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T11:27:02+00:00</t>
+          <t>2026-09-18T15:12:31+00:00</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2608VN (i7 13620H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz )</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WEK 286VN (Core i5 | RTX 5050 | 16GB | 512GB | 2K)</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C228" s="2" t="inlineStr"/>
+        <v>34990000</v>
+      </c>
+      <c r="C228" s="2" t="n">
+        <v>35990000</v>
+      </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr"/>
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 14450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-286vn</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T11:05:31+00:00</t>
+          <t>2026-10-18T07:32:04+00:00</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2610VN (i5 13420H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WFK 025VN (Core i7 14650HX | RTX 5060 | 16GB | 512GB | 15.6inch 165Hz)</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>26490000</v>
-      </c>
-      <c r="C229" s="2" t="inlineStr"/>
+        <v>38990000</v>
+      </c>
+      <c r="C229" s="2" t="n">
+        <v>42990000</v>
+      </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr"/>
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-025vn</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T11:25:28+00:00</t>
+          <t>2026-10-18T07:35:29+00:00</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Max C13WE-422VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5050 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WFK 267VN (Core i7 14650HX | RTX 5060 | 32GB | 512GB | 15.6inch 165Hz)</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C230" s="2" t="inlineStr"/>
+        <v>40990000</v>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>48990000</v>
+      </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-267vn</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T06:42:06+00:00</t>
+          <t>2026-10-18T07:31:54+00:00</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Max C13WF-421VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5060 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming MSI Pulse 16 AI C1VGKG 061VN</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="C231" s="2" t="inlineStr"/>
+        <v>39990000</v>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>52990000</v>
+      </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 185H | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13wf-421vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-pulse-16-ai-c1vgkg-061vn</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T07:56:42+00:00</t>
+          <t>2026-10-18T07:32:38+00:00</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 B13UDXK 2412VN (Core i5-13420H | RTX 3050 | 8GB | 1TB | 15.6 inch FHD)</t>
+          <t>Laptop Gaming MSI Raider 16 HX B2WH 258VN (Ultra 9 275HX | 32GB | 1TB | RTX 5070 Ti | 16inch)</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>22890000</v>
-      </c>
-      <c r="C232" s="2" t="n">
-        <v>25990000</v>
-      </c>
+        <v>81990000</v>
+      </c>
+      <c r="C232" s="2" t="inlineStr"/>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13udxk-2412vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wh-258vn</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:11:58+00:00</t>
+          <t>2026-10-12T10:46:21+00:00</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 B13VEK-2440VN (Core i7 | RTX 4050 | 16GB | 1TB | 144Hz)</t>
+          <t>Laptop Gaming MSI Raider 16 HX B2WI-257VN</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C233" s="2" t="n">
-        <v>32590000</v>
-      </c>
+        <v>92990000</v>
+      </c>
+      <c r="C233" s="2" t="inlineStr"/>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr"/>
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7-13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5080 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wi-257vn</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T12:06:54+00:00</t>
+          <t>2026-10-18T07:13:26+00:00</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WEK 027VN (Core i7 | RTX 5050 | 32GB | 512GB | 2K)</t>
+          <t>Laptop Gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX | RTX5070Ti | 32GB | 1TB | 16inch)</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>37990000</v>
-      </c>
-      <c r="C234" s="2" t="n">
-        <v>39990000</v>
-      </c>
+        <v>79490000</v>
+      </c>
+      <c r="C234" s="2" t="inlineStr"/>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr"/>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070Ti | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b8wh-031vn</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:12:31+00:00</t>
+          <t>2026-10-18T07:12:14+00:00</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WEK 286VN (Core i5 | RTX 5050 | 16GB | 512GB | 2K)</t>
+          <t>Laptop Gaming MSI Raider 16 Max HX B2WI-095VN (Ultra 9 290HX Plus | RTX 5080 | 64GB | 2TB | 16 inch OLED QHD+)</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C235" s="2" t="n">
-        <v>35990000</v>
-      </c>
+        <v>128990000</v>
+      </c>
+      <c r="C235" s="2" t="inlineStr"/>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 14450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5080 | Màn hình: 16" UHD+ MiniLED 240Hz</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-286vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-max-hx-b2wi-095vn</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T08:30:43+00:00</t>
+          <t>2026-10-18T10:29:36+00:00</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WFK 025VN (Core i7 14650HX | RTX 5060 | 16GB | 512GB | 15.6inch 165Hz)</t>
+          <t>Laptop Gaming MSI Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="C236" s="2" t="n">
-        <v>42990000</v>
-      </c>
+        <v>139990000</v>
+      </c>
+      <c r="C236" s="2" t="inlineStr"/>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr"/>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 16" UHD+ MiniLED 240Hz</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-025vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-max-hx-b2wj</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:22:23+00:00</t>
+          <t>2026-10-18T08:06:02+00:00</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WFK 267VN (Core i7 14650HX | RTX 5060 | 32GB | 512GB | 15.6inch 165Hz)</t>
+          <t>Laptop Gaming MSI Raider 18 Max HX A2WI 1285VN (Ultra 9 290HX | RTX 5080 | 64GB | 2TB | 18inch)</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C237" s="2" t="n">
-        <v>48990000</v>
-      </c>
+        <v>139990000</v>
+      </c>
+      <c r="C237" s="2" t="inlineStr"/>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr"/>
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5080 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-267vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-18-max-hx-a2wi-1285vn</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:21:55+00:00</t>
+          <t>2026-10-18T07:13:51+00:00</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Pulse 16 AI C1VGKG 061VN</t>
+          <t>Laptop Gaming MSI Raider 18 Max HX A2WJ</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C238" s="2" t="n">
-        <v>52990000</v>
-      </c>
+        <v>149990000</v>
+      </c>
+      <c r="C238" s="2" t="inlineStr"/>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr"/>
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 185H | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-pulse-16-ai-c1vgkg-061vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-18-max-hx-a2wj</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23T06:44:58+00:00</t>
+          <t>2026-10-18T08:06:25+00:00</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 HX B2WH 258VN (Ultra 9 275HX | 32GB | 1TB | RTX 5070 Ti | 16inch)</t>
+          <t>Laptop Gaming MSI Stealth 16 AI+ B3WF 007VN (Ultra 9 386H | RTX 5060 | 32GB | 1TB | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>81990000</v>
+        <v>74490000</v>
       </c>
       <c r="C239" s="2" t="inlineStr"/>
       <c r="D239" s="2" t="inlineStr">
@@ -9716,33 +9710,33 @@
       <c r="F239" s="2" t="inlineStr"/>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ OLED 240Hz</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wh-258vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wf-007vn</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T10:46:21+00:00</t>
+          <t>2026-10-10T07:28:24+00:00</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 HX B2WI-257VN</t>
+          <t>Laptop Gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9 386H | RTX 5070 | 32GB | 1TB | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>92990000</v>
+        <v>80590000</v>
       </c>
       <c r="C240" s="2" t="inlineStr"/>
       <c r="D240" s="2" t="inlineStr">
@@ -9754,33 +9748,33 @@
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5080 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ OLED 240Hz</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wi-257vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T10:36:24+00:00</t>
+          <t>2026-10-18T07:13:15+00:00</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX | RTX5070Ti | 32GB | 1TB | 16inch)</t>
+          <t>Laptop Gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9 386H | RTX 5070 12GB | 32GB | 1TB | 16 inch)</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>79490000</v>
+        <v>81490000</v>
       </c>
       <c r="C241" s="2" t="inlineStr"/>
       <c r="D241" s="2" t="inlineStr">
@@ -9792,35 +9786,37 @@
       <c r="F241" s="2" t="inlineStr"/>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070Ti | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ OLED 240Hz</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b8wh-031vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wgx-051vn</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T10:47:13+00:00</t>
+          <t>2026-10-18T07:11:49+00:00</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:50</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 Max HX B2WI-095VN (Ultra 9 290HX Plus | RTX 5080 | 64GB | 2TB | 16 inch OLED QHD+)</t>
+          <t>Laptop Gaming MSI Stealth 18 HX AI A2XWJG 073VN</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>129990000</v>
-      </c>
-      <c r="C242" s="2" t="inlineStr"/>
+        <v>140990000</v>
+      </c>
+      <c r="C242" s="2" t="n">
+        <v>140990000</v>
+      </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9830,185 +9826,193 @@
       <c r="F242" s="2" t="inlineStr"/>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5080 | Màn hình: 16" UHD+ MiniLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 24GB | Màn hình: 18" UHD+ MiniLED 120Hz</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-max-hx-b2wi-095vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-18-hx-ai-a2xwjg-073vn</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T06:31:39+00:00</t>
+          <t>2026-10-18T07:15:18+00:00</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 Max HX B2WJ</t>
+          <t>Laptop Gaming MSI Stealth A16 Mercedes AMG AI+ A3XWGGG 032VN (AMD Ryzen AI 9 HX 370 | RTX 5070 | 32GB | 2TB | 16 inch QHD+ OLED 240Hz)</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>139990000</v>
-      </c>
-      <c r="C243" s="2" t="inlineStr"/>
+        <v>77890000</v>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>79990000</v>
+      </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr"/>
       <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 16" UHD+ MiniLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen AI 9 HX370 | RAM: 32GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-max-hx-b2wj</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-a16-mercedes-amg-ai-a3xwggg-032vn</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08T06:47:33+00:00</t>
+          <t>2026-10-18T07:15:31+00:00</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 18 Max HX A2WI 1285VN (Ultra 9 290HX | RTX 5080 | 64GB | 2TB | 18inch)</t>
+          <t>Laptop Gaming MSI Sword 16 HX B14VGKG 466VN (20th Edition)</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>139990000</v>
-      </c>
-      <c r="C244" s="2" t="inlineStr"/>
+        <v>37890000</v>
+      </c>
+      <c r="C244" s="2" t="n">
+        <v>43990000</v>
+      </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr"/>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5080 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-18-max-hx-a2wi-1285vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-sword-16-hx-b14vgkg-466vn-20th-edition</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T06:30:28+00:00</t>
+          <t>2026-10-18T07:37:12+00:00</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 18 Max HX A2WJ</t>
+          <t>Laptop Gaming MSI Thin 15 B13UC 3247VN</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>149990000</v>
-      </c>
-      <c r="C245" s="2" t="inlineStr"/>
+        <v>21990000</v>
+      </c>
+      <c r="C245" s="2" t="n">
+        <v>24590000</v>
+      </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr"/>
       <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR4 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-18-max-hx-a2wj</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-thin-15-b13uc-3247vn</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08T06:47:45+00:00</t>
+          <t>2026-10-18T07:33:51+00:00</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:25</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth 16 AI+ B3WF 007VN (Ultra 9 386H | RTX 5060 | 32GB | 1TB | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming MSI Titan 18 HX A2WJ 1200VN (Ultra 9 290HX Plus | RTX 5090 | 96GB | 2TB | UHD)</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>74490000</v>
-      </c>
-      <c r="C246" s="2" t="inlineStr"/>
+        <v>192990000</v>
+      </c>
+      <c r="C246" s="2" t="n">
+        <v>199000000</v>
+      </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr"/>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ OLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 96GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 240Hz</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wf-007vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-titan-18-hx-a2wj-1200vn</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T07:28:24+00:00</t>
+          <t>2026-10-18T07:31:08+00:00</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9 386H | RTX 5070 | 32GB | 1TB | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming MSI Titan 18 HX Dragon Edition Draco Epic A2W 1245VN</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>80590000</v>
+        <v>212990000</v>
       </c>
       <c r="C247" s="2" t="inlineStr"/>
       <c r="D247" s="2" t="inlineStr">
@@ -10020,271 +10024,269 @@
       <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ OLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 96GB DDR5 | Ổ cứng: 4TB SSD | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 240Hz</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-titan-18-hx-dragon-edition-draco-epic-a2w-1245vn</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T07:24:55+00:00</t>
+          <t>2026-10-18T07:14:40+00:00</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9 386H | RTX 5070 12GB | 32GB | 1TB | 16 inch)</t>
+          <t>Laptop Gaming MSI Titan 18 HX AI A2XWJG 034VN Dragon Edition Norse Myth</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>81490000</v>
-      </c>
-      <c r="C248" s="2" t="inlineStr"/>
+        <v>174990000</v>
+      </c>
+      <c r="C248" s="2" t="n">
+        <v>184990000</v>
+      </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr"/>
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ OLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 285HX | RAM: 96GB DDR5 | Ổ cứng: 6TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wgx-051vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-titan-18hx-ai-a2xwjg-034vn-dragon-edition-norse-myth</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T07:23:23+00:00</t>
+          <t>2026-10-18T07:15:55+00:00</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth 18 HX AI A2XWJG 073VN</t>
+          <t>Laptop Gaming MSI Vector 16 HX AI A2XWHG 010VN</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>140990000</v>
+        <v>63490000</v>
       </c>
       <c r="C249" s="2" t="n">
-        <v>140990000</v>
+        <v>69990000</v>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr"/>
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 24GB | Màn hình: 18" UHD+ MiniLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-18-hx-ai-a2xwjg-073vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-vector-16-hx-ai-a2xwhg-010vn</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T10:44:56+00:00</t>
+          <t>2026-08-03T04:28:37+00:00</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth A16 Mercedes AMG AI+ A3XWGGG 032VN (AMD Ryzen AI 9 HX 370 | RTX 5070 | 32GB | 2TB | 16 inch QHD+ OLED 240Hz)</t>
+          <t>Laptop Gaming MSI Vector 16 HX AI A2XWJG 470VN (Ultra 9 | RTX 5090 | 32GB | 1TB | QHD)</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>77890000</v>
+        <v>108990000</v>
       </c>
       <c r="C250" s="2" t="n">
-        <v>79990000</v>
+        <v>119990000</v>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr"/>
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen AI 9 HX370 | RAM: 32GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5090 24GB | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-a16-mercedes-amg-ai-a3xwggg-032vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-vector-16-hx-ai-a2xwjg-470vn</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T14:59:40+00:00</t>
+          <t>2026-10-18T07:36:56+00:00</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Sword 16 HX B14VGKG 466VN (20th Edition)</t>
+          <t>Laptop Gaming MSI Vector GP68 HX 12VH 070VN</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>37890000</v>
-      </c>
-      <c r="C251" s="2" t="n">
-        <v>43990000</v>
-      </c>
+        <v>61990000</v>
+      </c>
+      <c r="C251" s="2" t="inlineStr"/>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr"/>
       <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i9 12900HX | RAM: 16GB DDR5 | VGA: RTX 4080 | Màn hình: 16" FHD+ 144Hz</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-sword-16-hx-b14vgkg-466vn-20th-edition</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-vector-gp68-hx-12vh-070vn</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>2026-03-24T04:54:58+00:00</t>
+          <t>2026-10-18T07:33:33+00:00</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Thin 15 B13UC 3247VN</t>
+          <t>Laptop Gaming OMEN MAX 16 16-ah0186TX</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C252" s="2" t="n">
-        <v>24590000</v>
-      </c>
+        <v>94990000</v>
+      </c>
+      <c r="C252" s="2" t="inlineStr"/>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr"/>
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR4 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: HP | CPU: Ultra 7 255HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-thin-15-b13uc-3247vn</t>
+          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0186tx</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T18:10:16+00:00</t>
+          <t>2026-06-02T13:15:28+00:00</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Titan 18 HX A2WJ 1200VN (Ultra 9 290HX Plus | RTX 5090 | 96GB | 2TB | UHD)</t>
+          <t>Laptop Gaming OMEN MAX 16 16-ah0212TX C1WR1PA</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>192990000</v>
+        <v>137990000</v>
       </c>
       <c r="C253" s="2" t="n">
-        <v>199000000</v>
+        <v>139000000</v>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr"/>
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 96GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 240Hz</t>
+          <t>Thương hiệu: HP | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5090 | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-titan-18-hx-a2wj-1200vn</t>
+          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0212tx</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T04:58:49+00:00</t>
+          <t>2026-10-17T11:07:39+00:00</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Titan 18 HX Dragon Edition Draco Epic A2W 1245VN</t>
+          <t>Laptop Gaming OMEN MAX 16 16-ah0213TX C1WR2PA</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>212990000</v>
+        <v>129990000</v>
       </c>
       <c r="C254" s="2" t="inlineStr"/>
       <c r="D254" s="2" t="inlineStr">
@@ -10296,191 +10298,193 @@
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 96GB DDR5 | Ổ cứng: 4TB SSD | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 240Hz</t>
+          <t>Thương hiệu: HP | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5080 | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-titan-18-hx-dragon-edition-draco-epic-a2w-1245vn</t>
+          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0213tx</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T04:41:05+00:00</t>
+          <t>2026-09-02T14:51:19+00:00</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Titan 18 HX AI A2XWJG 034VN Dragon Edition Norse Myth</t>
+          <t>Laptop Gaming Gigabyte A5 K1 AVN1030SB</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>174990000</v>
+        <v>17290000</v>
       </c>
       <c r="C255" s="2" t="n">
-        <v>184990000</v>
+        <v>23490000</v>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr"/>
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 285HX | RAM: 96GB DDR5 | Ổ cứng: 6TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: R5 5600H | RAM: 8GB DDR4 | VGA: RTX 3060 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-titan-18hx-ai-a2xwjg-034vn-dragon-edition-norse-myth</t>
+          <t>https://xgear.net/products/laptop-gigabyte-a5-k1-avn1030sb</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26T06:43:42+00:00</t>
+          <t>2026-04-08T03:48:41+00:00</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Vector 16 HX AI A2XWHG 010VN</t>
+          <t>Laptop Gigabyte AERO X16 1VH93VNC64AH (Ryzen AI 7 | RTX 5060 | 32GB | 1TB | sRGB 100%)</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>63490000</v>
+        <v>37990000</v>
       </c>
       <c r="C256" s="2" t="n">
-        <v>69990000</v>
+        <v>39990000</v>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr"/>
       <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen Ai 7 350 | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-vector-16-hx-ai-a2xwhg-010vn</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-1vh93vnc64ah</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T04:28:37+00:00</t>
+          <t>2026-09-18T14:12:38+00:00</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Vector 16 HX AI A2XWJG 470VN (Ultra 9 | RTX 5090 | 32GB | 1TB | QHD)</t>
+          <t>Laptop Gigabyte AERO X16 1VH93VNC94DH (Ryzen AI 7 350 | RTX 5060 | 16GB | 1TB | sRGB 100%)</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>108990000</v>
+        <v>39990000</v>
       </c>
       <c r="C257" s="2" t="n">
-        <v>119990000</v>
+        <v>39990000</v>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr"/>
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5090 24GB | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen Ai 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-vector-16-hx-ai-a2xwjg-470vn</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-1vh93vnc94dh</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:18:28+00:00</t>
+          <t>2026-10-18T06:19:08+00:00</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Vector GP68 HX 12VH 070VN</t>
+          <t>Laptop Gigabyte AERO X16 4WHN3VNC93AH (R9 AI 465 | RTX 5070 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>61990000</v>
-      </c>
-      <c r="C258" s="2" t="inlineStr"/>
+        <v>39990000</v>
+      </c>
+      <c r="C258" s="2" t="n">
+        <v>49990000</v>
+      </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr"/>
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 12900HX | RAM: 16GB DDR5 | VGA: RTX 4080 | Màn hình: 16" FHD+ 144Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 9 465 | RAM: 16GB DDR5 | Ổ cứng: 512 GB SSD | VGA: RTX 5070 | Màn hình: 16" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-vector-gp68-hx-12vh-070vn</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-4whn3vnc93ah</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20T06:33:52+00:00</t>
+          <t>2026-10-18T05:35:12+00:00</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 16-ah0186TX</t>
+          <t>Laptop Gigabyte AERO X16 EG61H-1VH93MY894AH  (Ryzen AI 7 350 | RTX 5060 | 16GB | 1TB | sRGB 100%)</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>94990000</v>
+        <v>38990000</v>
       </c>
       <c r="C259" s="2" t="inlineStr"/>
       <c r="D259" s="2" t="inlineStr">
@@ -10492,73 +10496,71 @@
       <c r="F259" s="2" t="inlineStr"/>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: Ultra 7 255HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" FHD+ 165Hz</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0186tx</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-eg61h-1vh93my894ah</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02T13:15:28+00:00</t>
+          <t>2026-09-19T12:56:52+00:00</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 16-ah0212TX C1WR1PA</t>
+          <t>Laptop Gigabyte AERO X16 EG61H-1VH93VNC94AH (Ryzen AI 7 | RTX 5060 | 16GB | 1TB | QHD+| sRGB 100%)</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>137990000</v>
-      </c>
-      <c r="C260" s="2" t="n">
-        <v>139000000</v>
-      </c>
+        <v>40590000</v>
+      </c>
+      <c r="C260" s="2" t="inlineStr"/>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr"/>
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5090 | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16"QHD+ 165Hz</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0212tx</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-eg61h-1vh93vnc94ah</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T11:07:39+00:00</t>
+          <t>2026-10-18T05:33:01+00:00</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 16-ah0213TX C1WR2PA</t>
+          <t>Laptop Gigabyte Aorus Master 16 6XJM4VNE64SH (R9 9955HX3D | RTX 5070 Ti | 32GB | 1TB | OLED)</t>
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>129990000</v>
+        <v>79990000</v>
       </c>
       <c r="C261" s="2" t="inlineStr"/>
       <c r="D261" s="2" t="inlineStr">
@@ -10570,117 +10572,111 @@
       <c r="F261" s="2" t="inlineStr"/>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5080 | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: R9 9955HX3D | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0213tx</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:51:19+00:00</t>
+          <t>2026-10-18T10:19:03+00:00</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte A5 K1 AVN1030SB</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="n">
-        <v>17290000</v>
-      </c>
-      <c r="C262" s="2" t="n">
-        <v>23490000</v>
-      </c>
+          <t>Laptop Gaming HP Victus 16-s1146AX AZ0D1PA</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr"/>
+      <c r="C262" s="2" t="inlineStr"/>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr"/>
       <c r="F262" s="2" t="inlineStr"/>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: R5 5600H | RAM: 8GB DDR4 | VGA: RTX 3060 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: HP | CPU: R5 8460H | RAM: 16GB DDR5 | Ổ cứng: 512SSD | VGA: RTX 4050 8GB</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-a5-k1-avn1030sb</t>
+          <t>https://xgear.net/products/laptop-hp-victus-16-s1146ax-az0d1pa</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08T03:48:41+00:00</t>
+          <t>2026-07-29T10:26:36+00:00</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 1VH93VNC64AH (Ryzen AI 7 | RTX 5060 | 32GB | 1TB | sRGB 100%)</t>
+          <t>Laptop Lenovo LOQ Essential 15IAX9E 83LK0079VN (i5-12450HX, RTX 3050 6GB, 100% sRGB)</t>
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>37990000</v>
+        <v>22990000</v>
       </c>
       <c r="C263" s="2" t="n">
-        <v>39990000</v>
+        <v>23990000</v>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr"/>
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen Ai 7 350 | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 12450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-1vh93vnc64ah</t>
+          <t>https://xgear.net/products/laptop-lenovo-loq-essential-15iax9e-83lk0079vn</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:12:38+00:00</t>
+          <t>2026-09-18T13:40:37+00:00</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 1VH93VNC94DH (Ryzen AI 7 350 | RTX 5060 | 16GB | 1TB | sRGB 100%)</t>
+          <t>Laptop LENOVO Yoga Pro 7 15ASH11 83W5000SVN (Ryzen AI Max+ 388 | AMD Radeon 8060S | 32GB | 512 GB | OLED)</t>
         </is>
       </c>
       <c r="B264" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C264" s="2" t="n">
-        <v>39990000</v>
-      </c>
+        <v>62990000</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr"/>
       <c r="D264" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -10690,73 +10686,71 @@
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen Ai 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen AI Max+ 388 | RAM: 32GB | Ổ cứng: 512GB SSD | VGA: RTX 5050 8GB | Màn hình: 15.3" WQXGA</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-1vh93vnc94dh</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15ash11-83w5000svn</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:13:47+00:00</t>
+          <t>2026-07-13T06:30:42+00:00</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 4WHN3VNC93AH (R9 AI 465 | RTX 5070 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop LENOVO Yoga Pro 7 15IPH11 83SN000BVN (Ultra 7 356H | RTX 5050 | 32GB | 1TB | 2.5K)</t>
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C265" s="2" t="n">
-        <v>49990000</v>
-      </c>
+        <v>73990000</v>
+      </c>
+      <c r="C265" s="2" t="inlineStr"/>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr"/>
       <c r="F265" s="2" t="inlineStr"/>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 9 465 | RAM: 16GB DDR5 | Ổ cứng: 512 GB SSD | VGA: RTX 5070 | Màn hình: 16" WQXGA 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 32GB | Ổ cứng: 1TB SSD | VGA: RTX 5050 8GB | Màn hình: 15.3" WUXGA 2.5K</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-4whn3vnc93ah</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15iph11-83sn000bvn</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:38:11+00:00</t>
+          <t>2026-10-01T02:30:34+00:00</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 EG61H-1VH93MY894AH  (Ryzen AI 7 350 | RTX 5060 | 16GB | 1TB | sRGB 100%)</t>
+          <t>Laptop Lenovo Yoga Pro 7 15IPH11 83SN0059VN (Ultra 7 356H | RTX 5050 | 24GB | 512GB | OLED 2.5K 100%sRGB)</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>38990000</v>
+        <v>76990000</v>
       </c>
       <c r="C266" s="2" t="inlineStr"/>
       <c r="D266" s="2" t="inlineStr">
@@ -10768,33 +10762,33 @@
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 24GB LPDDR5X | Ổ cứng: 512GB | VGA: RTX 5050 8GB | Màn hình: 15.3" 2.5K</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-eg61h-1vh93my894ah</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15iph11-83sn0059vn</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:56:52+00:00</t>
+          <t>2026-10-13T08:06:29+00:00</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 EG61H-1VH93VNC94AH (Ryzen AI 7 | RTX 5060 | 16GB | 1TB | QHD+| sRGB 100%)</t>
+          <t>Laptop Lenovo Yoga Pro 9 15N1X11 83SR001HVN (Spark N1X | 64GB RAM | 1TB SSD | RTX Blackwell | 15.3 inch 2.8K OLED 165Hz)</t>
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>40590000</v>
+        <v>126990000</v>
       </c>
       <c r="C267" s="2" t="inlineStr"/>
       <c r="D267" s="2" t="inlineStr">
@@ -10806,34 +10800,32 @@
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16"QHD+ 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Nvidia N1x | RAM: 64GB DDR5 | Ổ cứng: 1TB | VGA: RTX Blackwell | Màn hình: 15.3" 2.8K 165Hz</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-eg61h-1vh93vnc94ah</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-9-15n1x11-83sr001hvn</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:57:19+00:00</t>
+          <t>2026-10-17T13:13:43+00:00</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aorus Master 16 6XJM4VNE64SH (R9 9955HX3D | RTX 5070 Ti | 32GB | 1TB | OLED)</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="n">
-        <v>78990000</v>
-      </c>
+          <t>Laptop Lenovo Yoga Slim 7x Snapdragon X Elite/16GB/512GB/14.5 3K 90Hz/Touch/Win11</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr"/>
       <c r="C268" s="2" t="inlineStr"/>
       <c r="D268" s="2" t="inlineStr">
         <is>
@@ -10844,32 +10836,34 @@
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: R9 9955HX3D | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Snapdragon X Elite | RAM: 16GB DDR5 | Ổ cứng: 512GB NVMe | VGA: Qualcomm Adreno | Màn hình: 14.5" 3K OLED</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-slim-7x-snapdragon-x-elite</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T11:06:17+00:00</t>
+          <t>2026-05-28T08:56:37+00:00</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-s1146AX AZ0D1PA</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="inlineStr"/>
+          <t>Laptop Gaming MSI Cyborg 15 C13WEO-417VN</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>32990000</v>
+      </c>
       <c r="C269" s="2" t="inlineStr"/>
       <c r="D269" s="2" t="inlineStr">
         <is>
@@ -10880,73 +10874,73 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: R5 8460H | RAM: 16GB DDR5 | Ổ cứng: 512SSD | VGA: RTX 4050 8GB</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-hp-victus-16-s1146ax-az0d1pa</t>
+          <t>https://xgear.net/products/laptop-msi-cyborg-15-c13weo-417vn</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:26:36+00:00</t>
+          <t>2026-10-18T07:11:37+00:00</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo LOQ Essential 15IAX9E 83LK0079VN (i5-12450HX, RTX 3050 6GB, 100% sRGB)</t>
+          <t>Laptop MSI Gaming GF63 Thin 11UC 1228VN i7 11800H/8GB/512GB/15.6"F 144Hz/RTX3050MaxQ 4GB/Win11</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
-        <v>22990000</v>
+        <v>16490000</v>
       </c>
       <c r="C270" s="2" t="n">
-        <v>23990000</v>
+        <v>20490000</v>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr"/>
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 12450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 11800H | RAM: 8GB DDR4 | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-loq-essential-15iax9e-83lk0079vn</t>
+          <t>https://xgear.net/products/laptop-msi-gaming-gf63-thin-11uc-1228vn</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:40:37+00:00</t>
+          <t>2026-10-18T07:33:24+00:00</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Laptop LENOVO Yoga Pro 7 15ASH11 83W5000SVN (Ryzen AI Max+ 388 | AMD Radeon 8060S | 32GB | 512 GB | OLED)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Ultra 7 355 | 32GB | 1TB | Intel® Arc™ graphics | 16 inch)</t>
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>62990000</v>
+        <v>43990000</v>
       </c>
       <c r="C271" s="2" t="inlineStr"/>
       <c r="D271" s="2" t="inlineStr">
@@ -10958,33 +10952,33 @@
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen AI Max+ 388 | RAM: 32GB | Ổ cứng: 512GB SSD | VGA: RTX 5050 8GB | Màn hình: 15.3" WQXGA</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 355H | RAM: 32GB DDR5 | Ổ cứng: 1TB | Màn hình: 16" FHD+ OLED 120Hz</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15ash11-83w5000svn</t>
+          <t>https://xgear.net/products/laptop-msi-modern-16s-ai-g3mg-058vn</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T06:30:42+00:00</t>
+          <t>2026-10-18T07:40:24+00:00</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Laptop LENOVO Yoga Pro 7 15IPH11 83SN000BVN (Ultra 7 356H | RTX 5050 | 32GB | 1TB | 2.5K)</t>
+          <t>Laptop  MSI Modern 16S G3MG-016VN  (Core 7 350 | 16GB | 1TB | Intel® Arc™ graphics | 16inch)</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>73990000</v>
+        <v>32990000</v>
       </c>
       <c r="C272" s="2" t="inlineStr"/>
       <c r="D272" s="2" t="inlineStr">
@@ -10996,33 +10990,33 @@
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 32GB | Ổ cứng: 1TB SSD | VGA: RTX 5050 8GB | Màn hình: 15.3" WUXGA 2.5K</t>
+          <t>Thương hiệu: MSI | CPU: Core 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | Màn hình: 16" FHD+ 120Hz</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15iph11-83sn000bvn</t>
+          <t>https://xgear.net/products/laptop-msi-modern-16s-g3mg-016vn</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T02:30:34+00:00</t>
+          <t>2026-10-18T07:40:15+00:00</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Pro 7 15IPH11 83SN0059VN (Ultra 7 356H | RTX 5050 | 24GB | 512GB | OLED 2.5K 100%sRGB)</t>
+          <t>Laptop MSI Prestige 13 AI+ A3MG-036VN (Ultra 9-386H | Arc Graphics | 32GB | 1TB | 13.3 inch)</t>
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>76990000</v>
+        <v>50990000</v>
       </c>
       <c r="C273" s="2" t="inlineStr"/>
       <c r="D273" s="2" t="inlineStr">
@@ -11034,107 +11028,113 @@
       <c r="F273" s="2" t="inlineStr"/>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 24GB LPDDR5X | Ổ cứng: 512GB | VGA: RTX 5050 8GB | Màn hình: 15.3" 2.5K</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9-386H | RAM: 32GB LPDDR5x | VGA: Intel® Arc™ Graphics | Màn hình: 13.3" 2.8K OLED</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15iph11-83sn0059vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-a3mg-036vn</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:06:29+00:00</t>
+          <t>2026-10-18T07:30:59+00:00</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Pro 9 15N1X11 83SR001HVN (Spark N1X | 64GB RAM | 1TB SSD | RTX Blackwell | 15.3 inch 2.8K OLED 165Hz)</t>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>126990000</v>
-      </c>
-      <c r="C274" s="2" t="inlineStr"/>
+        <v>33790000</v>
+      </c>
+      <c r="C274" s="2" t="n">
+        <v>34390000</v>
+      </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr"/>
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Nvidia N1x | RAM: 64GB DDR5 | Ổ cứng: 1TB | VGA: RTX Blackwell | Màn hình: 15.3" 2.8K 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 155H | RAM: 32GB DDR5 | VGA: Intel Arc 16GB | Màn hình: 13.3" 2.8K OLED</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-9-15n1x11-83sr001hvn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:13:43+00:00</t>
+          <t>2026-10-18T07:33:15+00:00</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7x Snapdragon X Elite/16GB/512GB/14.5 3K 90Hz/Touch/Win11</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr"/>
-      <c r="C275" s="2" t="inlineStr"/>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 062VN</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="C275" s="2" t="n">
+        <v>40990000</v>
+      </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr"/>
       <c r="F275" s="2" t="inlineStr"/>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Snapdragon X Elite | RAM: 16GB DDR5 | Ổ cứng: 512GB NVMe | VGA: Qualcomm Adreno | Màn hình: 14.5" 3K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 288V | RAM: 32GB DDR5 | VGA: Intel® Arc™ Graphics | Màn hình: 13.3" 2.8K OLED</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-slim-7x-snapdragon-x-elite</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-evo-a2vmg-062vn</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28T08:56:37+00:00</t>
+          <t>2026-05-09T07:28:55+00:00</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 C13WEO-417VN</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7 355 | Arc Graphics | 32GB | 1TB | 14 inch)</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>32990000</v>
+        <v>44990000</v>
       </c>
       <c r="C276" s="2" t="inlineStr"/>
       <c r="D276" s="2" t="inlineStr">
@@ -11146,75 +11146,75 @@
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 355 | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-cyborg-15-c13weo-417vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T02:54:36+00:00</t>
+          <t>2026-10-18T07:34:56+00:00</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming GF63 Thin 11UC 1228VN i7 11800H/8GB/512GB/15.6"F 144Hz/RTX3050MaxQ 4GB/Win11</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ D3MTG-021VN (Ultra 9 386H | Arc Graphics | 32 GB | 1TB | 14 inch)</t>
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>16490000</v>
-      </c>
-      <c r="C277" s="2" t="n">
-        <v>20490000</v>
-      </c>
+        <v>52990000</v>
+      </c>
+      <c r="C277" s="2" t="inlineStr"/>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 11800H | RAM: 8GB DDR4 | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-gaming-gf63-thin-11uc-1228vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-d3mtg-021vn</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08T03:48:13+00:00</t>
+          <t>2026-10-18T07:34:46+00:00</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Ultra 7 355 | 32GB | 1TB | Intel® Arc™ graphics | 16 inch)</t>
+          <t>Laptop MSI Prestige 14 AI Evo C1MG 080VN</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C278" s="2" t="inlineStr"/>
+        <v>32990000</v>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>32990000</v>
+      </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -11224,71 +11224,73 @@
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 355H | RAM: 32GB DDR5 | Ổ cứng: 1TB | Màn hình: 16" FHD+ OLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 5 125H | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-modern-16s-ai-g3mg-058vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-evo-c1mg-080vn</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T04:58:00+00:00</t>
+          <t>2026-10-18T07:32:51+00:00</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Laptop  MSI Modern 16S G3MG-016VN  (Core 7 350 | 16GB | 1TB | Intel® Arc™ graphics | 16inch)</t>
+          <t>Laptop MSI Prestige 14 AI Evo C1MG 081VN</t>
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C279" s="2" t="inlineStr"/>
+        <v>28990000</v>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>30990000</v>
+      </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr"/>
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Core 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | Màn hình: 16" FHD+ 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 5 125H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: Intel Arc Graphics | Màn hình: 14" FHD+ 144Hz</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-modern-16s-g3mg-016vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-evo-c1mg-081vn</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T04:43:39+00:00</t>
+          <t>2026-10-13T07:19:14+00:00</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ A3MG-036VN (Ultra 9-386H | Arc Graphics | 32GB | 1TB | 13.3 inch)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent Van Gogh Edition Starry Night Over the Rhone - 260VN (Ultra X9 378H | Intel Arc B390 | 32GB | 1TB | 14 inch FHD+ OLED)</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>50990000</v>
+        <v>57490000</v>
       </c>
       <c r="C280" s="2" t="inlineStr"/>
       <c r="D280" s="2" t="inlineStr">
@@ -11300,113 +11302,109 @@
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9-386H | RAM: 32GB LPDDR5x | VGA: Intel® Arc™ Graphics | Màn hình: 13.3" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 378H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-a3mg-036vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T10:48:33+00:00</t>
+          <t>2026-10-18T07:36:20+00:00</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent Van Gogh Edition The Starry Night - 259VN (Ultra X9 378H | Intel Arc B390 | 32GB | 1TB | 14 inch FHD+ OLED)</t>
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>33790000</v>
-      </c>
-      <c r="C281" s="2" t="n">
-        <v>34390000</v>
-      </c>
+        <v>57490000</v>
+      </c>
+      <c r="C281" s="2" t="inlineStr"/>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr"/>
       <c r="F281" s="2" t="inlineStr"/>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 155H | RAM: 32GB DDR5 | VGA: Intel Arc 16GB | Màn hình: 13.3" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 378H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-295vn</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T06:18:36+00:00</t>
+          <t>2026-10-18T07:36:37+00:00</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 062VN</t>
+          <t>Laptop MSI Prestige 16 AI+ C3MG-024VN (Ultra X9-388H | Intel Arc B390| 32GB | 1TB | 16 inch 2.8K OLED)</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C282" s="2" t="n">
-        <v>40990000</v>
-      </c>
+        <v>54990000</v>
+      </c>
+      <c r="C282" s="2" t="inlineStr"/>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr"/>
       <c r="F282" s="2" t="inlineStr"/>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 288V | RAM: 32GB DDR5 | VGA: Intel® Arc™ Graphics | Màn hình: 13.3" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra X9 388H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: Intel Arc B90 | Màn hình: 16" 2.8K OLED 120Hz</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-evo-a2vmg-062vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-16-ai-c3mg-024vn</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09T07:28:55+00:00</t>
+          <t>2026-10-15T04:41:17+00:00</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7 355 | Arc Graphics | 32GB | 1TB | 14 inch)</t>
+          <t>Laptop MSI Prestige N16 Flip AI+ C1XMT-016VN (Spark N1x | 128GB RAM | 2TB SSD | RTX Black Well | 16 inch OLED 120Hz)</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>44990000</v>
+        <v>220990000</v>
       </c>
       <c r="C283" s="2" t="inlineStr"/>
       <c r="D283" s="2" t="inlineStr">
@@ -11418,33 +11416,33 @@
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 355 | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Nvidia N1x | RAM: 128GB DDR5 | Ổ cứng: 2TB | VGA: RTX Blackwell | Màn hình: 16" UHD+ 120Hz</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-n16-flip-ai-c1xmt-016vn</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:23:28+00:00</t>
+          <t>2026-10-18T07:29:27+00:00</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ D3MTG-021VN (Ultra 9 386H | Arc Graphics | 32 GB | 1TB | 14 inch)</t>
+          <t>Laptop MSI Prestige N16 Flip AI+ C1XMT-017VN (Spark N1X | 64GB RAM | 2TB SSD | RTX Black Well | 16 inch 2.8K OLED 120Hz)</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>52990000</v>
+        <v>135990000</v>
       </c>
       <c r="C284" s="2" t="inlineStr"/>
       <c r="D284" s="2" t="inlineStr">
@@ -11456,37 +11454,35 @@
       <c r="F284" s="2" t="inlineStr"/>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Nvidia N1x | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX Blackwell | Màn hình: 16" 2.8K OLED 120Hz</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-d3mtg-021vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-n16-flip-ai-c1xmt-017vn</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T07:46:18+00:00</t>
+          <t>2026-10-18T07:29:18+00:00</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI Evo C1MG 080VN</t>
+          <t>Laptop MSI Venture 15 AI+ B3M-007VN (Ultra X7 358H | Intel Arc B390 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C285" s="2" t="n">
-        <v>32990000</v>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C285" s="2" t="inlineStr"/>
       <c r="D285" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -11496,111 +11492,113 @@
       <c r="F285" s="2" t="inlineStr"/>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 5 125H | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra X7 358H | RAM: 16 GB | Ổ cứng: 512 GB SSD | VGA: Intel ARC B390 | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-evo-c1mg-080vn</t>
+          <t>https://xgear.net/products/laptop-msi-venture-15-ai-b3m-007vn</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:19:46+00:00</t>
+          <t>2026-10-07T05:13:43+00:00</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI Evo C1MG 081VN</t>
+          <t>Laptop MSI Venture A14 AI+ A3HMG 004VN</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>28990000</v>
+        <v>24990000</v>
       </c>
       <c r="C286" s="2" t="n">
-        <v>30990000</v>
+        <v>25990000</v>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr"/>
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 5 125H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: Intel Arc Graphics | Màn hình: 14" FHD+ 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen AI 5 340 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | Màn hình: 14" OLED 2.8K 120Hz</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-evo-c1mg-081vn</t>
+          <t>https://xgear.net/products/laptop-msi-venture-a14-ai-a3hmg-004vn</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:19:14+00:00</t>
+          <t>2026-10-18T08:03:56+00:00</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent Van Gogh Edition Starry Night Over the Rhone - 260VN (Ultra X9 378H | Intel Arc B390 | 32GB | 1TB | 14 inch FHD+ OLED)</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX10 83JE00PEVN (Core i7-13650HX | RTX 5050 | 16GB | 512GB | 15.6 inch)</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>57490000</v>
-      </c>
-      <c r="C287" s="2" t="inlineStr"/>
+        <v>32990000</v>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>37990000</v>
+      </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr"/>
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 378H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn</t>
+          <t>https://xgear.net/products/lenovo-loq-15irx10-83je00pevn-core-i7-13650hx</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:23:13+00:00</t>
+          <t>2026-10-18T09:11:13+00:00</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent Van Gogh Edition The Starry Night - 259VN (Ultra X9 378H | Intel Arc B390 | 32GB | 1TB | 14 inch FHD+ OLED)</t>
+          <t>MacBook Air M5 13 inch 2026 10CPU 10GPU 16GB 1TB</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>57490000</v>
+        <v>42690000</v>
       </c>
       <c r="C288" s="2" t="inlineStr"/>
       <c r="D288" s="2" t="inlineStr">
@@ -11612,33 +11610,33 @@
       <c r="F288" s="2" t="inlineStr"/>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 378H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 16GB | Ổ cứng: 1TB | Màn hình: 13.6 inch</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-295vn</t>
+          <t>https://xgear.net/products/macbook-air-m5-13-inch-2026-10cpu-10gpu-16gb-1tb</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:23:51+00:00</t>
+          <t>2026-06-26T12:03:05+00:00</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 16 AI+ C3MG-024VN (Ultra X9-388H | Intel Arc B390| 32GB | 1TB | 16 inch 2.8K OLED)</t>
+          <t>MacBook Air M5 13 inch 2026 10CPU 10GPU 24GB 1TB</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>54990000</v>
+        <v>45990000</v>
       </c>
       <c r="C289" s="2" t="inlineStr"/>
       <c r="D289" s="2" t="inlineStr">
@@ -11650,33 +11648,33 @@
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra X9 388H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: Intel Arc B90 | Màn hình: 16" 2.8K OLED 120Hz</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 13.6 inch</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-16-ai-c3mg-024vn</t>
+          <t>https://xgear.net/products/macbook-air-m5-13-inch-2026-10cpu-10gpu-24gb-1tb</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:41:17+00:00</t>
+          <t>2026-10-18T09:26:38+00:00</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige N16 Flip AI+ C1XMT-016VN (Spark N1x | 128GB RAM | 2TB SSD | RTX Black Well | 16 inch OLED 120Hz)</t>
+          <t>MacBook Air M5 15 inch 2026 10CPU 10GPU 16GB 1TB</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>220990000</v>
+        <v>47990000</v>
       </c>
       <c r="C290" s="2" t="inlineStr"/>
       <c r="D290" s="2" t="inlineStr">
@@ -11688,33 +11686,33 @@
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Nvidia N1x | RAM: 128GB DDR5 | Ổ cứng: 2TB | VGA: RTX Blackwell | Màn hình: 16" UHD+ 120Hz</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 16GB | Ổ cứng: 1TB | Màn hình: 15.3 inches</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-n16-flip-ai-c1xmt-016vn</t>
+          <t>https://xgear.net/products/macbook-air-m5-15-inch-2026-10cpu-10gpu-16gb-1tb</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T14:13:29+00:00</t>
+          <t>2026-06-26T12:09:01+00:00</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige N16 Flip AI+ C1XMT-017VN (Spark N1X | 64GB RAM | 2TB SSD | RTX Black Well | 16 inch 2.8K OLED 120Hz)</t>
+          <t>MacBook Air M5 15 inch 2026 10CPU 10GPU 24GB 1TB</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>135990000</v>
+        <v>52990000</v>
       </c>
       <c r="C291" s="2" t="inlineStr"/>
       <c r="D291" s="2" t="inlineStr">
@@ -11726,33 +11724,33 @@
       <c r="F291" s="2" t="inlineStr"/>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Nvidia N1x | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX Blackwell | Màn hình: 16" 2.8K OLED 120Hz</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 15.3 inches</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-n16-flip-ai-c1xmt-017vn</t>
+          <t>https://xgear.net/products/macbook-air-m5-15-inch-2026-10cpu-10gpu-24gb-1tb</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T14:57:30+00:00</t>
+          <t>2026-06-26T12:31:23+00:00</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Venture 15 AI+ B3M-007VN (Ultra X7 358H | Intel Arc B390 | 16GB | 512GB | 100% sRGB)</t>
+          <t>MacBook Neo 13 inch A18 Pro 8GB-256GB</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>34990000</v>
+        <v>17490000</v>
       </c>
       <c r="C292" s="2" t="inlineStr"/>
       <c r="D292" s="2" t="inlineStr">
@@ -11764,113 +11762,109 @@
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra X7 358H | RAM: 16 GB | Ổ cứng: 512 GB SSD | VGA: Intel ARC B390 | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Apple | CPU: Apple A18 Pro | RAM: 8GB | Ổ cứng: 256TB | Màn hình: 13 inch</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-venture-15-ai-b3m-007vn</t>
+          <t>https://xgear.net/products/macbook-neo-13-inch-a18-pro-2026-6cpu-5gpu-8gb-256gb</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T05:13:43+00:00</t>
+          <t>2026-10-18T09:19:17+00:00</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Venture A14 AI+ A3HMG 004VN</t>
+          <t>MacBook Neo 13 inch A18 Pro 8GB-512GB</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C293" s="2" t="n">
-        <v>25990000</v>
-      </c>
+        <v>20890000</v>
+      </c>
+      <c r="C293" s="2" t="inlineStr"/>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr"/>
       <c r="F293" s="2" t="inlineStr"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen AI 5 340 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | Màn hình: 14" OLED 2.8K 120Hz</t>
+          <t>Thương hiệu: Apple</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-venture-a14-ai-a3hmg-004vn</t>
+          <t>https://xgear.net/products/macbook-neo-13-inch-a18-pro-8gb-512gb</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T18:09:26+00:00</t>
+          <t>2026-10-13T12:18:18+00:00</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX10 83JE00PEVN (Core i7-13650HX | RTX 5050 | 16GB | 512GB | 15.6 inch)</t>
+          <t>MacBook Pro M5 Max 16 inch 2026 18CPU 32GPU 36GB 2TB</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C294" s="2" t="n">
-        <v>38990000</v>
-      </c>
+        <v>118690000</v>
+      </c>
+      <c r="C294" s="2" t="inlineStr"/>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr"/>
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 36GB | Ổ cứng: 2TB | Màn hình: 16.2 inch</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/lenovo-loq-15irx10-83je00pevn-core-i7-13650hx</t>
+          <t>https://xgear.net/products/macbook-pro-m5-max-16-inch-18cpu-32gpu-36gb-2tb</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T11:00:52+00:00</t>
+          <t>2026-06-26T12:42:59+00:00</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>MacBook Air M5 13 inch 2026 10CPU 10GPU 16GB 1TB</t>
+          <t>MacBook Pro M5 Pro 14 inch 2026 15CPU 16GPU 24GB 1TB</t>
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>42690000</v>
+        <v>65990000</v>
       </c>
       <c r="C295" s="2" t="inlineStr"/>
       <c r="D295" s="2" t="inlineStr">
@@ -11882,33 +11876,33 @@
       <c r="F295" s="2" t="inlineStr"/>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 16GB | Ổ cứng: 1TB | Màn hình: 13.6 inch</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 36GB | Ổ cứng: 2TB | Màn hình: 14.2 inch</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-air-m5-13-inch-2026-10cpu-10gpu-16gb-1tb</t>
+          <t>https://xgear.net/products/macbook-pro-m5-pro-14-inch-15cpu-16gpu-24gb-1tb</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T12:03:05+00:00</t>
+          <t>2026-10-18T11:06:01+00:00</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>MacBook Air M5 13 inch 2026 10CPU 10GPU 24GB 1TB</t>
+          <t>MacBook Pro M5 Pro 14 inch 2026 18CPU 20GPU 24GB 2TB</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>47590000</v>
+        <v>85890000</v>
       </c>
       <c r="C296" s="2" t="inlineStr"/>
       <c r="D296" s="2" t="inlineStr">
@@ -11920,33 +11914,33 @@
       <c r="F296" s="2" t="inlineStr"/>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 13.6 inch</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 24GB | Ổ cứng: 2TB | Màn hình: 16.2 inch</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-air-m5-13-inch-2026-10cpu-10gpu-24gb-1tb</t>
+          <t>https://xgear.net/products/macbook-pro-m5-pro-14-inch-2026-18cpu-20gpu-24gb-2tb</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T13:03:42+00:00</t>
+          <t>2026-10-18T11:16:22+00:00</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>MacBook Air M5 15 inch 2026 10CPU 10GPU 16GB 1TB</t>
+          <t>MacBook Pro M5 Pro 16 inch 2026 18CPU 20GPU 24GB 1TB</t>
         </is>
       </c>
       <c r="B297" s="2" t="n">
-        <v>47990000</v>
+        <v>79390000</v>
       </c>
       <c r="C297" s="2" t="inlineStr"/>
       <c r="D297" s="2" t="inlineStr">
@@ -11958,288 +11952,22 @@
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 16GB | Ổ cứng: 1TB | Màn hình: 15.3 inches</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 16.2 inch</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-air-m5-15-inch-2026-10cpu-10gpu-16gb-1tb</t>
+          <t>https://xgear.net/products/macbook-pro-m5-pro-16-inch-18cpu-20gpu-24gb-1tb</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T12:09:01+00:00</t>
+          <t>2026-06-26T12:42:09+00:00</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 00:09:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>MacBook Air M5 15 inch 2026 10CPU 10GPU 24GB 1TB</t>
-        </is>
-      </c>
-      <c r="B298" s="2" t="n">
-        <v>52990000</v>
-      </c>
-      <c r="C298" s="2" t="inlineStr"/>
-      <c r="D298" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
-      <c r="E298" s="2" t="inlineStr"/>
-      <c r="F298" s="2" t="inlineStr"/>
-      <c r="G298" s="2" t="inlineStr">
-        <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 15.3 inches</t>
-        </is>
-      </c>
-      <c r="H298" s="2" t="inlineStr">
-        <is>
-          <t>https://xgear.net/products/macbook-air-m5-15-inch-2026-10cpu-10gpu-24gb-1tb</t>
-        </is>
-      </c>
-      <c r="I298" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26T12:31:23+00:00</t>
-        </is>
-      </c>
-      <c r="J298" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:09:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>MacBook Neo 13 inch A18 Pro 8GB-256GB</t>
-        </is>
-      </c>
-      <c r="B299" s="2" t="n">
-        <v>16990000</v>
-      </c>
-      <c r="C299" s="2" t="inlineStr"/>
-      <c r="D299" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
-      <c r="E299" s="2" t="inlineStr"/>
-      <c r="F299" s="2" t="inlineStr"/>
-      <c r="G299" s="2" t="inlineStr">
-        <is>
-          <t>Thương hiệu: Apple | CPU: Apple A18 Pro | RAM: 8GB | Ổ cứng: 256TB | Màn hình: 13 inch</t>
-        </is>
-      </c>
-      <c r="H299" s="2" t="inlineStr">
-        <is>
-          <t>https://xgear.net/products/macbook-neo-13-inch-a18-pro-2026-6cpu-5gpu-8gb-256gb</t>
-        </is>
-      </c>
-      <c r="I299" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-09T03:17:53+00:00</t>
-        </is>
-      </c>
-      <c r="J299" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:09:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>MacBook Neo 13 inch A18 Pro 8GB-512GB</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="n">
-        <v>20890000</v>
-      </c>
-      <c r="C300" s="2" t="inlineStr"/>
-      <c r="D300" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
-      <c r="E300" s="2" t="inlineStr"/>
-      <c r="F300" s="2" t="inlineStr"/>
-      <c r="G300" s="2" t="inlineStr">
-        <is>
-          <t>Thương hiệu: Apple</t>
-        </is>
-      </c>
-      <c r="H300" s="2" t="inlineStr">
-        <is>
-          <t>https://xgear.net/products/macbook-neo-13-inch-a18-pro-8gb-512gb</t>
-        </is>
-      </c>
-      <c r="I300" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13T12:18:18+00:00</t>
-        </is>
-      </c>
-      <c r="J300" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:09:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>MacBook Pro M5 Max 16 inch 2026 18CPU 32GPU 36GB 2TB</t>
-        </is>
-      </c>
-      <c r="B301" s="2" t="n">
-        <v>118690000</v>
-      </c>
-      <c r="C301" s="2" t="inlineStr"/>
-      <c r="D301" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr"/>
-      <c r="F301" s="2" t="inlineStr"/>
-      <c r="G301" s="2" t="inlineStr">
-        <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 36GB | Ổ cứng: 2TB | Màn hình: 16.2 inch</t>
-        </is>
-      </c>
-      <c r="H301" s="2" t="inlineStr">
-        <is>
-          <t>https://xgear.net/products/macbook-pro-m5-max-16-inch-18cpu-32gpu-36gb-2tb</t>
-        </is>
-      </c>
-      <c r="I301" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26T12:42:59+00:00</t>
-        </is>
-      </c>
-      <c r="J301" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:09:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>MacBook Pro M5 Pro 14 inch 2026 15CPU 16GPU 24GB 1TB</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="n">
-        <v>66890000</v>
-      </c>
-      <c r="C302" s="2" t="inlineStr"/>
-      <c r="D302" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr"/>
-      <c r="F302" s="2" t="inlineStr"/>
-      <c r="G302" s="2" t="inlineStr">
-        <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 36GB | Ổ cứng: 2TB | Màn hình: 14.2 inch</t>
-        </is>
-      </c>
-      <c r="H302" s="2" t="inlineStr">
-        <is>
-          <t>https://xgear.net/products/macbook-pro-m5-pro-14-inch-15cpu-16gpu-24gb-1tb</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26T12:33:18+00:00</t>
-        </is>
-      </c>
-      <c r="J302" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:09:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>MacBook Pro M5 Pro 14 inch 2026 18CPU 20GPU 24GB 2TB</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="n">
-        <v>94690000</v>
-      </c>
-      <c r="C303" s="2" t="inlineStr"/>
-      <c r="D303" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
-      <c r="E303" s="2" t="inlineStr"/>
-      <c r="F303" s="2" t="inlineStr"/>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 24GB | Ổ cứng: 2TB | Màn hình: 16.2 inch</t>
-        </is>
-      </c>
-      <c r="H303" s="2" t="inlineStr">
-        <is>
-          <t>https://xgear.net/products/macbook-pro-m5-pro-14-inch-2026-18cpu-20gpu-24gb-2tb</t>
-        </is>
-      </c>
-      <c r="I303" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26T12:35:52+00:00</t>
-        </is>
-      </c>
-      <c r="J303" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:09:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>MacBook Pro M5 Pro 16 inch 2026 18CPU 20GPU 24GB 1TB</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="n">
-        <v>79390000</v>
-      </c>
-      <c r="C304" s="2" t="inlineStr"/>
-      <c r="D304" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="inlineStr"/>
-      <c r="F304" s="2" t="inlineStr"/>
-      <c r="G304" s="2" t="inlineStr">
-        <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 16.2 inch</t>
-        </is>
-      </c>
-      <c r="H304" s="2" t="inlineStr">
-        <is>
-          <t>https://xgear.net/products/macbook-pro-m5-pro-16-inch-18cpu-20gpu-24gb-1tb</t>
-        </is>
-      </c>
-      <c r="I304" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26T12:42:09+00:00</t>
-        </is>
-      </c>
-      <c r="J304" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18 00:09:33</t>
+          <t>2026-10-19 00:06:48</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -524,12 +524,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:09:51+00:00</t>
+          <t>2026-10-21T04:39:25+00:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -843,18 +843,18 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt P14 H7407BA-SU304W (RTX Spark N1X | RTX Blackwell | 48GB RAM | 1TB SSD | 14 inch 4K OLED 120Hz)</t>
+          <t>Laptop ASUS ProArt P14 H7407BA-SU304W (RTX Spark N1X | RTX Blackwell | 48GB RAM | 1TB SSD | 14 inch 3K OLED 120Hz)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>114990000</v>
+        <v>113990000</v>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Asus | CPU: Nvidia N1x | RAM: 48GB LPDDR5X | VGA: RTX Blackwell | Màn hình: 14" 4K OLED</t>
+          <t>Thương hiệu: Asus | CPU: Nvidia N1x | RAM: 48GB LPDDR5X | VGA: RTX Blackwell | Màn hình: 14" 3K OLED</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T06:42:07+00:00</t>
+          <t>2026-10-22T10:42:41+00:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>129990000</v>
+        <v>128990000</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T06:49:10+00:00</t>
+          <t>2026-10-22T10:41:26+00:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>119990000</v>
+        <v>118990000</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T10:10:46+00:00</t>
+          <t>2026-10-22T10:43:08+00:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>71990000</v>
+        <v>70990000</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:01:14+00:00</t>
+          <t>2026-10-21T03:28:43+00:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>57890000</v>
+        <v>57490000</v>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:07:31+00:00</t>
+          <t>2026-10-21T04:36:59+00:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,9 @@
           <t>Laptop ASUS TUF Gaming 16 FX610JP-TU073W (Intel Core 7 14650HX | RTX 5070 | 16GB | 512GB | 16inch 144Hz)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="n">
+        <v>54990000</v>
+      </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -1484,12 +1486,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T10:12:54+00:00</t>
+          <t>2026-10-20T03:25:20+00:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1529,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1562,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:07:13+00:00</t>
+          <t>2026-10-20T11:21:21+00:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1605,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1643,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1681,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1719,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1757,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1797,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1835,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1875,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1915,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1955,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1993,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2033,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2073,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2113,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2153,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2231,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2269,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2307,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2345,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2385,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2425,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2463,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2503,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2541,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2581,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2621,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2661,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2701,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2741,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2781,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2821,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:44</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2861,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2901,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2941,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2979,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3019,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3059,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3097,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3135,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3175,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3215,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3253,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3291,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3331,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3371,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3411,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3451,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3491,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3529,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3567,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3605,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3645,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3683,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3723,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3763,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3801,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3841,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3881,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3921,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3959,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3997,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4035,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4075,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4115,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4153,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4193,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4204,7 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>104990000</v>
+        <v>103990000</v>
       </c>
       <c r="C97" s="2" t="inlineStr"/>
       <c r="D97" s="2" t="inlineStr">
@@ -4224,12 +4226,12 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:47:13+00:00</t>
+          <t>2026-10-23T02:49:17+00:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4269,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4309,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4347,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4385,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4423,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4461,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4499,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4510,7 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>189990000</v>
+        <v>188990000</v>
       </c>
       <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="2" t="inlineStr">
@@ -4530,12 +4532,12 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T04:55:39+00:00</t>
+          <t>2026-10-21T04:49:46+00:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4575,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4613,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4651,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4689,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4727,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4767,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4807,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4847,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4923,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4961,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4999,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5037,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5113,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5151,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5189,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5227,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5265,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5300,12 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:34:37+00:00</t>
+          <t>2026-10-22T14:25:19+00:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5345,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5385,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5425,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5465,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5505,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5545,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5585,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5623,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5661,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5699,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5737,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5775,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5815,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5853,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5891,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5929,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5967,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6005,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6043,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6079,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6115,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6151,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6187,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6225,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6261,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6297,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6337,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6377,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6417,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6457,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6495,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6533,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6573,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6613,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6624,7 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>61990000</v>
+        <v>61490000</v>
       </c>
       <c r="C160" s="2" t="inlineStr"/>
       <c r="D160" s="2" t="inlineStr">
@@ -6644,12 +6646,12 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T09:31:33+00:00</t>
+          <t>2026-10-23T02:38:36+00:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6662,7 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>61990000</v>
+        <v>61490000</v>
       </c>
       <c r="C161" s="2" t="inlineStr"/>
       <c r="D161" s="2" t="inlineStr">
@@ -6682,12 +6684,12 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T09:20:43+00:00</t>
+          <t>2026-10-23T02:39:28+00:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6727,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6767,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6807,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6845,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6883,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6923,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6963,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7003,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7043,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7083,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7123,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7163,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7203,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7243,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7281,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7321,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7356,12 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:19:41+00:00</t>
+          <t>2026-10-23T02:18:38+00:00</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7401,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7441,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7481,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:48</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7519,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7559,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7597,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7635,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7675,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7715,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7753,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7791,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7831,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7869,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7909,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7949,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7987,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8025,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8063,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8103,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8143,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8181,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8221,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8259,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8270,7 @@
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>33990000</v>
+        <v>32990000</v>
       </c>
       <c r="C202" s="2" t="inlineStr"/>
       <c r="D202" s="2" t="inlineStr">
@@ -8290,12 +8292,12 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T04:35:56+00:00</t>
+          <t>2026-10-23T02:33:12+00:00</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8308,7 @@
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>28990000</v>
+        <v>27490000</v>
       </c>
       <c r="C203" s="2" t="inlineStr"/>
       <c r="D203" s="2" t="inlineStr">
@@ -8328,12 +8330,12 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T03:48:51+00:00</t>
+          <t>2026-10-23T02:33:56+00:00</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8375,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8413,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8424,7 @@
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>32690000</v>
+        <v>31590000</v>
       </c>
       <c r="C206" s="2" t="inlineStr"/>
       <c r="D206" s="2" t="inlineStr">
@@ -8444,12 +8446,12 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T03:49:47+00:00</t>
+          <t>2026-10-23T02:29:07+00:00</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8491,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8529,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8567,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8605,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8643,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8681,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8719,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8757,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8795,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8833,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8871,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8909,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8945,7 +8947,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8987,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9025,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9065,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9096,12 +9098,12 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:11:21+00:00</t>
+          <t>2026-10-22T15:21:42+00:00</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9134,12 +9136,12 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:11:04+00:00</t>
+          <t>2026-10-22T15:19:36+00:00</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9179,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9217,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9257,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9297,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9337,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9372,12 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:32:04+00:00</t>
+          <t>2026-10-22T15:27:31+00:00</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9417,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9457,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9497,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9535,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9573,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9611,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9649,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9687,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9698,7 @@
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>139990000</v>
+        <v>142990000</v>
       </c>
       <c r="C239" s="2" t="inlineStr"/>
       <c r="D239" s="2" t="inlineStr">
@@ -9718,12 +9720,12 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:13:51+00:00</t>
+          <t>2026-10-20T04:49:17+00:00</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9763,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9801,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:55:30</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9839,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9877,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9917,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9957,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9997,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10030,12 +10032,12 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:33:51+00:00</t>
+          <t>2026-10-20T02:33:47+00:00</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10077,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10115,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10155,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10195,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10233,7 +10235,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10273,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10311,7 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10351,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10389,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10429,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10467,7 +10469,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10509,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10549,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10587,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10625,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10663,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10699,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10739,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10777,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10815,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10853,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10891,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10927,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10965,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11005,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11043,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11081,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11119,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11159,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11197,7 +11199,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11237,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11275,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11315,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11353,7 +11355,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11393,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11431,7 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11469,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11500,12 +11502,12 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:29:27+00:00</t>
+          <t>2026-10-20T04:21:30+00:00</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11538,12 +11540,12 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:29:18+00:00</t>
+          <t>2026-10-20T04:22:20+00:00</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11583,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11623,7 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11635,11 +11637,11 @@
         <v>32990000</v>
       </c>
       <c r="C289" s="2" t="n">
-        <v>37990000</v>
+        <v>38990000</v>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr"/>
@@ -11656,12 +11658,12 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T09:11:13+00:00</t>
+          <t>2026-10-22T07:20:17+00:00</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11701,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11739,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11777,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11815,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11853,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11864,7 @@
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>20890000</v>
+        <v>21890000</v>
       </c>
       <c r="C295" s="2" t="inlineStr"/>
       <c r="D295" s="2" t="inlineStr">
@@ -11884,12 +11886,12 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:18:18+00:00</t>
+          <t>2026-10-20T11:45:35+00:00</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11902,7 @@
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>118690000</v>
+        <v>116890000</v>
       </c>
       <c r="C296" s="2" t="inlineStr"/>
       <c r="D296" s="2" t="inlineStr">
@@ -11922,12 +11924,12 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T12:42:59+00:00</t>
+          <t>2026-10-20T11:57:28+00:00</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -11965,7 +11967,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12005,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12043,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 07:56:12</t>
+          <t>2026-10-23 09:55:18</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:10:03</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:55</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:53</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:54</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10077,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10772,12 +10772,12 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T06:30:42+00:00</t>
+          <t>2026-10-23T05:22:17+00:00</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>73990000</v>
+        <v>71990000</v>
       </c>
       <c r="C267" s="2" t="inlineStr"/>
       <c r="D267" s="2" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T02:30:34+00:00</t>
+          <t>2026-10-23T05:23:17+00:00</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:55:18</t>
+          <t>2026-10-24 00:09:56</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:10:03</t>
+          <t>2026-10-25 00:20:13</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45990000</v>
+        <v>46790000</v>
       </c>
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:03:48+00:00</t>
+          <t>2026-10-24T02:54:28+00:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:55</t>
+          <t>2026-10-25 00:19:51</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:53</t>
+          <t>2026-10-25 00:20:24</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>64990000</v>
+        <v>64490000</v>
       </c>
       <c r="C209" s="2" t="inlineStr"/>
       <c r="D209" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T06:34:58+00:00</t>
+          <t>2026-10-24T09:34:05+00:00</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9020,12 +9020,12 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T01:55:59+00:00</t>
+          <t>2026-10-24T13:32:22+00:00</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:54</t>
+          <t>2026-10-25 00:20:08</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10077,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 00:09:56</t>
+          <t>2026-10-25 00:20:10</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -43,7 +43,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,13 +51,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -529,7 +535,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -569,7 +575,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -607,7 +613,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -645,7 +651,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -685,7 +691,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -725,7 +731,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -765,7 +771,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -803,7 +809,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -843,7 +849,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -881,7 +887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -919,7 +925,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -957,7 +963,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -995,7 +1001,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1039,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1077,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1115,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1155,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1166,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45990000</v>
+        <v>45790000</v>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
@@ -1182,12 +1188,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:04:06+00:00</t>
+          <t>2026-10-25T02:33:19+00:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1204,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>51290000</v>
+        <v>50990000</v>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
@@ -1220,12 +1226,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:04:46+00:00</t>
+          <t>2026-10-25T02:35:10+00:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1269,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1307,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1345,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1383,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1421,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1459,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1497,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1535,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1573,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1611,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1649,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1687,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1725,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1763,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1803,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1814,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>25490000</v>
+        <v>24490000</v>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
@@ -1830,12 +1836,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:43:16+00:00</t>
+          <t>2026-10-25T02:41:08+00:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1881,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1921,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1961,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1999,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2039,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2079,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2119,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2159,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2199,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2237,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2275,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2313,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2351,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2391,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2431,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2469,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2509,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2547,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2587,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2627,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2667,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2707,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2747,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2787,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2827,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:13</t>
+          <t>2026-10-26 00:13:38</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2867,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2907,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2947,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2985,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3025,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3065,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3103,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3141,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3181,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3221,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3259,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3297,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3337,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3377,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3417,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3457,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3497,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3535,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3573,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3611,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3651,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3689,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3729,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3769,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3780,7 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>29990000</v>
+        <v>29490000</v>
       </c>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="inlineStr">
@@ -3796,12 +3802,12 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T05:09:07+00:00</t>
+          <t>2026-10-25T02:44:20+00:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3847,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3887,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3927,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3965,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4003,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4041,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4081,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4121,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4159,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4199,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4237,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4275,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4315,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4353,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4364,7 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>59990000</v>
+        <v>59490000</v>
       </c>
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr">
@@ -4380,12 +4386,12 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T06:08:54+00:00</t>
+          <t>2026-10-25T02:39:30+00:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4429,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4456,12 +4462,12 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:23:58+00:00</t>
+          <t>2026-10-25T12:27:23+00:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4505,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4543,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4581,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4619,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4657,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4695,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4733,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4773,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4813,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4853,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4891,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4929,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4967,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -4999,7 +5005,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5043,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5081,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5119,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5157,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:19:51</t>
+          <t>2026-10-26 00:13:49</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5195,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5233,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5271,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5311,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5351,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5391,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5431,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5471,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5511,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5551,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5591,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5629,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5667,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5705,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5743,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5781,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5821,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5859,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5897,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5935,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5973,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6011,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6049,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6085,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6121,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6157,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6193,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6231,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6267,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6303,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6343,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6383,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6423,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6463,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6501,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6539,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6579,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6619,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6657,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6695,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6733,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6773,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6813,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6851,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6889,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6929,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6969,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7009,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7049,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7089,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7129,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7169,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7209,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7249,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7287,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7327,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7367,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7407,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7447,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7487,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:24</t>
+          <t>2026-10-26 00:13:43</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7525,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7565,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7603,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7641,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7681,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7721,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7759,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7797,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7837,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7875,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7915,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7955,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7993,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8031,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8069,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8109,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8149,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8187,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8227,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8265,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8303,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8341,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8381,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8419,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8457,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8497,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8535,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8573,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8611,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8649,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8687,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8725,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8763,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8801,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8839,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8877,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8915,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8953,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8993,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9031,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9071,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9103,7 +9109,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9147,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9185,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9223,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9263,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9303,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9343,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9377,7 +9383,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9423,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9463,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9503,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9535,7 +9541,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9579,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9617,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9655,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9693,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9731,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9769,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9807,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:08</t>
+          <t>2026-10-26 00:13:50</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9845,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -9877,7 +9883,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9923,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -9957,7 +9963,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -9997,7 +10003,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10043,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10083,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10121,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10161,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10201,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10241,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10279,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10317,7 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10357,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10395,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10435,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10475,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10515,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10555,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10593,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10631,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10669,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10705,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10739,7 +10745,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10777,7 +10783,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10821,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10853,7 +10859,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10897,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10933,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10944,7 @@
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>32990000</v>
+        <v>31990000</v>
       </c>
       <c r="C271" s="2" t="inlineStr"/>
       <c r="D271" s="2" t="inlineStr">
@@ -10960,12 +10966,12 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:11:37+00:00</t>
+          <t>2026-10-25T02:30:57+00:00</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11011,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11049,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11087,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11125,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11165,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11205,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11243,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11281,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11321,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11361,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11399,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11437,7 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11475,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11513,7 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11551,7 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11589,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11629,7 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11669,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11707,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11745,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11783,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11821,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11859,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11897,7 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11935,7 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -11967,7 +11973,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12011,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12049,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 00:20:10</t>
+          <t>2026-10-26 00:13:58</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -43,7 +43,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,19 +51,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -535,7 +529,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -575,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -613,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -651,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -691,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -731,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -771,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -809,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -849,7 +843,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -887,7 +881,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -925,7 +919,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -963,7 +957,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1001,7 +995,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1033,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1071,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1109,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1149,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1187,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1225,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1263,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1301,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1339,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1377,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1415,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1453,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1491,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1529,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1567,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1605,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1643,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1681,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1719,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1757,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1797,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1835,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1875,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1915,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1955,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1993,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2033,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2073,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2113,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2153,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2231,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2269,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2307,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2345,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2385,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2425,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2463,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2503,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2541,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2581,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2621,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2661,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2701,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2741,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2781,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2821,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:38</t>
+          <t>2026-10-26 08:20:17</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2861,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2901,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2941,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2979,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3019,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3059,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3097,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3135,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3175,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3215,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3253,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3291,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3331,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3371,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3411,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3451,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3491,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3529,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3567,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3605,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3645,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3683,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3723,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3763,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3801,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3841,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3881,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3921,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3959,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4003,7 +3997,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4035,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4075,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4115,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4153,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4193,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4231,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4269,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4309,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4347,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4385,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4423,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4461,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4499,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4537,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4575,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4613,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4651,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4689,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4727,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4767,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4807,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4847,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4923,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4961,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -5005,7 +4999,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5037,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5113,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5151,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:49</t>
+          <t>2026-10-26 08:19:46</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5189,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5227,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5265,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5305,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5345,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5385,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5425,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5465,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5505,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5545,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5585,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5623,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5661,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5699,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5737,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5775,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5815,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5853,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5891,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5929,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5967,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6005,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6043,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6079,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6115,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6151,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6187,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6225,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6261,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6297,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6337,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6377,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6417,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6457,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6495,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6533,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6573,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6613,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6651,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6689,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6727,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6767,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6807,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6845,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6883,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6923,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6963,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7003,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7043,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7083,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7123,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7163,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7203,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7243,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7281,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7321,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7361,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7401,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7441,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7481,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:43</t>
+          <t>2026-10-26 08:19:55</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7519,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7559,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7597,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7635,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7675,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7715,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7753,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7791,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7831,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7869,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7909,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7955,7 +7949,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7987,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8025,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8063,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8103,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8143,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8181,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8221,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8259,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8297,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8335,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8375,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8413,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8451,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8491,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8529,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8567,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8605,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8643,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8681,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8719,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8757,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8795,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8833,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8871,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8909,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8947,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -8993,7 +8987,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9025,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9065,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9103,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9141,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9179,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9217,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9257,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9297,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9337,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9377,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9417,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9457,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9497,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9535,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9573,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9611,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9649,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9687,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9725,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9763,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9801,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:50</t>
+          <t>2026-10-26 08:20:13</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9839,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 12:34:48</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9877,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9917,7 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9957,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10003,7 +9997,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10037,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10083,7 +10077,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10115,7 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10155,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10195,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10241,7 +10235,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10273,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10311,7 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10351,7 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10389,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10435,7 +10429,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10469,7 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10509,7 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10549,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10587,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10625,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10663,7 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10705,7 +10699,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10739,7 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10777,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10815,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10853,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10897,7 +10891,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10927,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -10971,7 +10965,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11005,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11043,7 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11081,7 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11119,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11165,7 +11159,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11199,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11243,7 +11237,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11275,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11315,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11355,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11393,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11437,7 +11431,7 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11469,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11507,7 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11545,7 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11583,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11623,7 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11663,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11707,7 +11701,7 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11745,7 +11739,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11777,7 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11815,7 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11853,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11891,7 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11929,7 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11967,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12005,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12043,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 00:13:58</t>
+          <t>2026-10-26 08:19:53</t>
         </is>
       </c>
     </row>

--- a/laptop_xgear_all.xlsx
+++ b/laptop_xgear_all.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J299"/>
+  <dimension ref="A1:J298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T10:42:41+00:00</t>
+          <t>2026-10-26T05:03:33+00:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T10:41:26+00:00</t>
+          <t>2026-10-26T05:03:02+00:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T10:43:08+00:00</t>
+          <t>2026-10-26T05:02:34+00:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T06:47:23+00:00</t>
+          <t>2026-10-26T05:00:31+00:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:17</t>
+          <t>2026-10-26 17:20:50</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -4961,18 +4961,18 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Asus TUF F16 FX607VJG-TU458W (Intel Core 5 205H | RTX 3050 | 16Gb | 512GB | 16inch WUXGA)</t>
+          <t>Laptop Gaming Asus TUF F16 FX607VJG-TU458W (Intel Core 5 205H | RTX 3050 | 16GB | 512GB | 16inch WUXGA)</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>32990000</v>
+        <v>30990000</v>
       </c>
       <c r="C117" s="2" t="inlineStr"/>
       <c r="D117" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T06:26:59+00:00</t>
+          <t>2026-10-26T09:43:05+00:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:46</t>
+          <t>2026-10-26 17:20:56</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6722,12 +6722,12 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T03:47:29+00:00</t>
+          <t>2026-10-26T04:37:32+00:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:55</t>
+          <t>2026-10-26 17:20:52</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -8221,18 +8221,18 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15ARP10E 83S000DCVN ( Ryzen 7 - 170 | RTX 3050 | 16GB | 1TB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003XVN (Core 7 230H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>29990000</v>
+        <v>32990000</v>
       </c>
       <c r="C201" s="2" t="inlineStr"/>
       <c r="D201" s="2" t="inlineStr">
@@ -8244,33 +8244,33 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen 7 170 | RAM: 16GB DDR5 | Ổ cứng: 1TB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s000dcvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003xvn</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T02:41:11+00:00</t>
+          <t>2026-10-23T02:33:12+00:00</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003XVN (Core 7 230H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003YVN (Core 7 230H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>32990000</v>
+        <v>27490000</v>
       </c>
       <c r="C202" s="2" t="inlineStr"/>
       <c r="D202" s="2" t="inlineStr">
@@ -8282,111 +8282,111 @@
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003xvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003yvn</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T02:33:12+00:00</t>
+          <t>2026-10-23T02:33:56+00:00</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003YVN (Core 7 230H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRX11 83SC003RVN (i5-13450HX | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>27490000</v>
-      </c>
-      <c r="C203" s="2" t="inlineStr"/>
+        <v>28490000</v>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>38990000</v>
+      </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-27%</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 7 230H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irh11e-83y9003yvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irx11-83sc003rvn</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T02:33:56+00:00</t>
+          <t>2026-07-01T05:38:36+00:00</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRX11 83SC003RVN (i5-13450HX | RTX 5050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003VVN (Core 5 205H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>28490000</v>
-      </c>
-      <c r="C204" s="2" t="n">
-        <v>38990000</v>
-      </c>
+        <v>25990000</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr"/>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>-27%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 13450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 5050 8GB | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-15irx11-83sc003rvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003vvn</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T05:38:36+00:00</t>
+          <t>2026-10-19T06:29:00+00:00</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential 15IRH11E 83Y9003VVN (Core 5 205H | RTX 3050 | 8GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming Lenovo LOQ Essential LOQ 15IRH11E 83Y9003WVN (Core 5 205H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>25990000</v>
+        <v>31590000</v>
       </c>
       <c r="C205" s="2" t="inlineStr"/>
       <c r="D205" s="2" t="inlineStr">
@@ -8398,111 +8398,111 @@
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 8GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
+          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003vvn</t>
+          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003wvn</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T06:29:00+00:00</t>
+          <t>2026-10-23T02:29:07+00:00</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ Essential LOQ 15IRH11E 83Y9003WVN (Core 5 205H | RTX 3050 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX AI D2XWFKG-036VN (Ultra 7 | RTX 5060 | 16GB | 1TB | 2K)</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>31590000</v>
-      </c>
-      <c r="C206" s="2" t="inlineStr"/>
+        <v>44990000</v>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>49990000</v>
+      </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Core 5 205H | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD Gen 4 | VGA: RTX 3050 6GB | Màn hình: 15.3" WUXGA 165Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-lenovo-loq-essential-loq-15irh11e-83y9003wvn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-ai-d2xwfkg-036vn</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T02:29:07+00:00</t>
+          <t>2026-10-18T07:15:43+00:00</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX AI D2XWFKG-036VN (Ultra 7 | RTX 5060 | 16GB | 1TB | 2K)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WFK-074VN (i7 14650HX | 16GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="C207" s="2" t="n">
-        <v>49990000</v>
-      </c>
+        <v>55990000</v>
+      </c>
+      <c r="C207" s="2" t="inlineStr"/>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-ai-d2xwfkg-036vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-074vn</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:15:43+00:00</t>
+          <t>2026-10-18T07:13:02+00:00</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WFK-074VN (i7 14650HX | 16GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14VFK-075VN (i9 14900HX | 32GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>55990000</v>
+        <v>64490000</v>
       </c>
       <c r="C208" s="2" t="inlineStr"/>
       <c r="D208" s="2" t="inlineStr">
@@ -8514,33 +8514,33 @@
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-074vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-075vn</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:13:02+00:00</t>
+          <t>2026-10-24T09:34:05+00:00</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14VFK-075VN (i9 14900HX | 32GB | 1TB | RTX 5060 | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 076VN (Core i9-14900HX | RTX 5050 | 32GB | 1TB SSD | QHD+)</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>64490000</v>
+        <v>58990000</v>
       </c>
       <c r="C209" s="2" t="inlineStr"/>
       <c r="D209" s="2" t="inlineStr">
@@ -8552,33 +8552,33 @@
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14vfk-075vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-076vn</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T09:34:05+00:00</t>
+          <t>2026-10-18T07:29:36+00:00</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 076VN (Core i9-14900HX | RTX 5050 | 32GB | 1TB SSD | QHD+)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 077VN (Core i7 14650HX | RTX 5050 | 16GB | 512GB | 16 inch)</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>58990000</v>
+        <v>49990000</v>
       </c>
       <c r="C210" s="2" t="inlineStr"/>
       <c r="D210" s="2" t="inlineStr">
@@ -8590,33 +8590,33 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-076vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-077vn</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:29:36+00:00</t>
+          <t>2026-09-17T09:44:38+00:00</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WEK 077VN (Core i7 14650HX | RTX 5050 | 16GB | 512GB | 16 inch)</t>
+          <t>Laptop Gaming MSI Crosshair 16 HX E14WGK</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>49990000</v>
+        <v>69990000</v>
       </c>
       <c r="C211" s="2" t="inlineStr"/>
       <c r="D211" s="2" t="inlineStr">
@@ -8628,33 +8628,33 @@
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wek-077vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wgk</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T09:44:38+00:00</t>
+          <t>2026-08-13T04:42:13+00:00</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 HX E14WGK</t>
+          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-051VN (Ultra 9 290HX Plus | 32GB | 1TB | RTX 5070 12GB | 16 inch)</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>69990000</v>
+        <v>74990000</v>
       </c>
       <c r="C212" s="2" t="inlineStr"/>
       <c r="D212" s="2" t="inlineStr">
@@ -8666,33 +8666,33 @@
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 14900HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ Oled 165Hz</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-hx-e14wgk</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-051vn</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T04:42:13+00:00</t>
+          <t>2026-10-18T07:10:50+00:00</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-051VN (Ultra 9 290HX Plus | 32GB | 1TB | RTX 5070 12GB | 16 inch)</t>
+          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-052VN  (Ultra 7 251HX | 16GB | 1TB | RTX 5070 12GB | 16 inch OLED 165Hz )</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>74990000</v>
+        <v>63990000</v>
       </c>
       <c r="C213" s="2" t="inlineStr"/>
       <c r="D213" s="2" t="inlineStr">
@@ -8704,33 +8704,33 @@
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ Oled 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 251HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ OLED 165Hz</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-051vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-052vn</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:10:50+00:00</t>
+          <t>2026-10-18T07:10:37+00:00</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair 16 Max HX E2WGXK-052VN  (Ultra 7 251HX | 16GB | 1TB | RTX 5070 12GB | 16 inch OLED 165Hz )</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>63990000</v>
+        <v>64990000</v>
       </c>
       <c r="C214" s="2" t="inlineStr"/>
       <c r="D214" s="2" t="inlineStr">
@@ -8742,22 +8742,22 @@
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 251HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 12GB | Màn hình: 16" QHD+ OLED 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-16-max-hx-e2wgxk-052vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:10:37+00:00</t>
+          <t>2026-10-18T07:12:50+00:00</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>64990000</v>
+        <v>56990000</v>
       </c>
       <c r="C215" s="2" t="inlineStr"/>
       <c r="D215" s="2" t="inlineStr">
@@ -8780,33 +8780,33 @@
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 7 8840HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk-1</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:12:50+00:00</t>
+          <t>2026-10-18T07:12:37+00:00</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX E8WFK</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WFK-067VN (Ryzen 9 8940HX | RTX 5060 | 16GB | 1TB | 16inch QHD+)</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>56990000</v>
+        <v>59990000</v>
       </c>
       <c r="C216" s="2" t="inlineStr"/>
       <c r="D216" s="2" t="inlineStr">
@@ -8818,33 +8818,33 @@
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 7 8840HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-e8wfk-1</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wfk-067vn</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:12:37+00:00</t>
+          <t>2026-10-18T08:12:52+00:00</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WFK-067VN (Ryzen 9 8940HX | RTX 5060 | 16GB | 1TB | 16inch QHD+)</t>
+          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WGK-093VN (Ryzen 9 8940HX | RTX 5070 | 16GB | 1TB | 16inch QHD+)</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>59990000</v>
+        <v>65990000</v>
       </c>
       <c r="C217" s="2" t="inlineStr"/>
       <c r="D217" s="2" t="inlineStr">
@@ -8856,33 +8856,33 @@
       <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wfk-067vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wgk-093vn</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T08:12:52+00:00</t>
+          <t>2026-10-12T04:33:12+00:00</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Crosshair A16 HX MLG Edition E8WGK-093VN (Ryzen 9 8940HX | RTX 5070 | 16GB | 1TB | 16inch QHD+)</t>
+          <t>Laptop Gaming MSI Cyborg 15 A13VEK 2089VN</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
-        <v>65990000</v>
+        <v>30990000</v>
       </c>
       <c r="C218" s="2" t="inlineStr"/>
       <c r="D218" s="2" t="inlineStr">
@@ -8894,189 +8894,189 @@
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: R9 8940HX | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-crosshair-a16-hx-mlg-edition-e8wgk-093vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-a13vek-2089vn</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T04:33:12+00:00</t>
+          <t>2026-07-12T09:35:09+00:00</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 A13VEK 2089VN</t>
+          <t>Laptop Gaming MSI Cyborg 15 B13WEKG-676VN</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C219" s="2" t="inlineStr"/>
+        <v>26990000</v>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v>32490000</v>
+      </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-17%</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr"/>
       <c r="F219" s="2" t="inlineStr"/>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-a13vek-2089vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wekg-676vn</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12T09:35:09+00:00</t>
+          <t>2026-10-12T08:19:31+00:00</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 B13WEKG-676VN</t>
+          <t>Laptop Gaming MSI Cyborg 15 B13WFKG 658VN</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="C220" s="2" t="n">
-        <v>32490000</v>
-      </c>
+        <v>34490000</v>
+      </c>
+      <c r="C220" s="2" t="inlineStr"/>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>-17%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wekg-676vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wfkg-658vn</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T08:19:31+00:00</t>
+          <t>2026-10-24T13:32:22+00:00</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 B13WFKG 658VN</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VE-2410VN (Core i5-13420H | RTX 4050 | 16GB | 512GB | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>34490000</v>
-      </c>
-      <c r="C221" s="2" t="inlineStr"/>
+        <v>18990000</v>
+      </c>
+      <c r="C221" s="2" t="n">
+        <v>27490000</v>
+      </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-31%</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr"/>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-b13wfkg-658vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13ve-2410vn</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:32:22+00:00</t>
+          <t>2026-10-18T07:12:25+00:00</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VE-2410VN (Core i5-13420H | RTX 4050 | 16GB | 512GB | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2608VN (i7 13620H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz )</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="C222" s="2" t="n">
-        <v>27490000</v>
-      </c>
+        <v>28990000</v>
+      </c>
+      <c r="C222" s="2" t="inlineStr"/>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>-31%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr"/>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13ve-2410vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:12:25+00:00</t>
+          <t>2026-10-22T15:21:42+00:00</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2608VN (i7 13620H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz )</t>
+          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2610VN (i5 13420H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>28990000</v>
+        <v>26490000</v>
       </c>
       <c r="C223" s="2" t="inlineStr"/>
       <c r="D223" s="2" t="inlineStr">
@@ -9088,33 +9088,33 @@
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T15:21:42+00:00</t>
+          <t>2026-10-22T15:19:36+00:00</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Black Edition A13VEO 2610VN (i5 13420H | 16GB | 512GB | RTX 4050 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming MSI Cyborg 15 Max C13WE-422VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5050 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>26490000</v>
+        <v>36990000</v>
       </c>
       <c r="C224" s="2" t="inlineStr"/>
       <c r="D224" s="2" t="inlineStr">
@@ -9126,33 +9126,33 @@
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T15:19:36+00:00</t>
+          <t>2026-10-05T06:42:06+00:00</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Max C13WE-422VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5050 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming MSI Cyborg 15 Max C13WF-421VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5060 | 15.6 inch FHD 144Hz)</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>36990000</v>
+        <v>41990000</v>
       </c>
       <c r="C225" s="2" t="inlineStr"/>
       <c r="D225" s="2" t="inlineStr">
@@ -9164,351 +9164,351 @@
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13wf-421vn</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T06:42:06+00:00</t>
+          <t>2026-10-18T07:10:23+00:00</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 Max C13WF-421VN (i7 13620H | 16GB RAM | 512GB SSD | RTX 5060 | 15.6 inch FHD 144Hz)</t>
+          <t>Laptop Gaming MSI Katana 15 B13UDXK 2412VN (Core i5-13420H | RTX 3050 | 8GB | 1TB | 15.6 inch FHD)</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="C226" s="2" t="inlineStr"/>
+        <v>22890000</v>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>25990000</v>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-cyborg-15-max-c13wf-421vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13udxk-2412vn</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:10:23+00:00</t>
+          <t>2026-10-18T07:35:06+00:00</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 B13UDXK 2412VN (Core i5-13420H | RTX 3050 | 8GB | 1TB | 15.6 inch FHD)</t>
+          <t>Laptop Gaming MSI Katana 15 B13VEK-2440VN (Core i7 | RTX 4050 | 16GB | 1TB | 144Hz)</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>22890000</v>
+        <v>29990000</v>
       </c>
       <c r="C227" s="2" t="n">
-        <v>25990000</v>
+        <v>32590000</v>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr"/>
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7-13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13udxk-2412vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:35:06+00:00</t>
+          <t>2026-10-19T09:26:53+00:00</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 B13VEK-2440VN (Core i7 | RTX 4050 | 16GB | 1TB | 144Hz)</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WEK 027VN (Core i7 | RTX 5050 | 32GB | 512GB | 2K)</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>29990000</v>
+        <v>37990000</v>
       </c>
       <c r="C228" s="2" t="n">
-        <v>32590000</v>
+        <v>39990000</v>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr"/>
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7-13620H | RAM: 16GB DDR5 | Ổ cứng: 1TB | VGA: RTX 4050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19T09:26:53+00:00</t>
+          <t>2026-09-18T15:12:31+00:00</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WEK 027VN (Core i7 | RTX 5050 | 32GB | 512GB | 2K)</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WEK 286VN (Core i5 | RTX 5050 | 16GB | 512GB | 2K)</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>37990000</v>
+        <v>34990000</v>
       </c>
       <c r="C229" s="2" t="n">
-        <v>39990000</v>
+        <v>35990000</v>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr"/>
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 14450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-286vn</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T15:12:31+00:00</t>
+          <t>2026-10-22T15:27:31+00:00</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WEK 286VN (Core i5 | RTX 5050 | 16GB | 512GB | 2K)</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WFK 025VN (Core i7 14650HX | RTX 5060 | 16GB | 512GB | 15.6inch 165Hz)</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>34990000</v>
+        <v>38990000</v>
       </c>
       <c r="C230" s="2" t="n">
-        <v>35990000</v>
+        <v>42990000</v>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 14450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wek-286vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-025vn</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T15:27:31+00:00</t>
+          <t>2026-10-18T07:35:29+00:00</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WFK 025VN (Core i7 14650HX | RTX 5060 | 16GB | 512GB | 15.6inch 165Hz)</t>
+          <t>Laptop Gaming MSI Katana 15 HX B14WFK 267VN (Core i7 14650HX | RTX 5060 | 32GB | 512GB | 15.6inch 165Hz)</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>38990000</v>
+        <v>40990000</v>
       </c>
       <c r="C231" s="2" t="n">
-        <v>42990000</v>
+        <v>48990000</v>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-025vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-267vn</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:35:29+00:00</t>
+          <t>2026-10-18T07:31:54+00:00</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Katana 15 HX B14WFK 267VN (Core i7 14650HX | RTX 5060 | 32GB | 512GB | 15.6inch 165Hz)</t>
+          <t>Laptop Gaming MSI Pulse 16 AI C1VGKG 061VN</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>40990000</v>
+        <v>39990000</v>
       </c>
       <c r="C232" s="2" t="n">
-        <v>48990000</v>
+        <v>52990000</v>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-25%</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5060 | Màn hình: 15.6" QHD 165Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 185H | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-katana-15-hx-b14wfk-267vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-pulse-16-ai-c1vgkg-061vn</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:31:54+00:00</t>
+          <t>2026-10-18T07:32:38+00:00</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Pulse 16 AI C1VGKG 061VN</t>
+          <t>Laptop Gaming MSI Raider 16 HX B2WH 258VN (Ultra 9 275HX | 32GB | 1TB | RTX 5070 Ti | 16inch)</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C233" s="2" t="n">
-        <v>52990000</v>
-      </c>
+        <v>81990000</v>
+      </c>
+      <c r="C233" s="2" t="inlineStr"/>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>-25%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr"/>
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 185H | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-pulse-16-ai-c1vgkg-061vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wh-258vn</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:32:38+00:00</t>
+          <t>2026-10-12T10:46:21+00:00</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 HX B2WH 258VN (Ultra 9 275HX | 32GB | 1TB | RTX 5070 Ti | 16inch)</t>
+          <t>Laptop Gaming MSI Raider 16 HX B2WI-257VN</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>81990000</v>
+        <v>92990000</v>
       </c>
       <c r="C234" s="2" t="inlineStr"/>
       <c r="D234" s="2" t="inlineStr">
@@ -9520,33 +9520,33 @@
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5080 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wh-258vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wi-257vn</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T10:46:21+00:00</t>
+          <t>2026-10-18T07:13:26+00:00</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 HX B2WI-257VN</t>
+          <t>Laptop Gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX | RTX5070Ti | 32GB | 1TB | 16inch)</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>92990000</v>
+        <v>79490000</v>
       </c>
       <c r="C235" s="2" t="inlineStr"/>
       <c r="D235" s="2" t="inlineStr">
@@ -9558,33 +9558,33 @@
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5080 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070Ti | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b2wi-257vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b8wh-031vn</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:13:26+00:00</t>
+          <t>2026-10-18T07:12:14+00:00</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX | RTX5070Ti | 32GB | 1TB | 16inch)</t>
+          <t>Laptop Gaming MSI Raider 16 Max HX B2WI-095VN (Ultra 9 290HX Plus | RTX 5080 | 64GB | 2TB | 16 inch OLED QHD+)</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>79490000</v>
+        <v>128990000</v>
       </c>
       <c r="C236" s="2" t="inlineStr"/>
       <c r="D236" s="2" t="inlineStr">
@@ -9596,33 +9596,33 @@
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen 9 8940HX | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070Ti | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5080 | Màn hình: 16" UHD+ MiniLED 240Hz</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-hx-b8wh-031vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-max-hx-b2wi-095vn</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:12:14+00:00</t>
+          <t>2026-10-18T10:29:36+00:00</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 Max HX B2WI-095VN (Ultra 9 290HX Plus | RTX 5080 | 64GB | 2TB | 16 inch OLED QHD+)</t>
+          <t>Laptop Gaming MSI Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>128990000</v>
+        <v>139990000</v>
       </c>
       <c r="C237" s="2" t="inlineStr"/>
       <c r="D237" s="2" t="inlineStr">
@@ -9634,33 +9634,33 @@
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5080 | Màn hình: 16" UHD+ MiniLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 16" UHD+ MiniLED 240Hz</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-max-hx-b2wi-095vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-max-hx-b2wj</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T10:29:36+00:00</t>
+          <t>2026-10-18T08:06:02+00:00</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 16 Max HX B2WJ</t>
+          <t>Laptop Gaming MSI Raider 18 Max HX A2WI 1285VN (Ultra 9 290HX | RTX 5080 | 64GB | 2TB | 18inch)</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>139990000</v>
+        <v>142990000</v>
       </c>
       <c r="C238" s="2" t="inlineStr"/>
       <c r="D238" s="2" t="inlineStr">
@@ -9672,33 +9672,33 @@
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 16" UHD+ MiniLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5080 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-16-max-hx-b2wj</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-18-max-hx-a2wi-1285vn</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T08:06:02+00:00</t>
+          <t>2026-10-20T04:49:17+00:00</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 18 Max HX A2WI 1285VN (Ultra 9 290HX | RTX 5080 | 64GB | 2TB | 18inch)</t>
+          <t>Laptop Gaming MSI Raider 18 Max HX A2WJ</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>142990000</v>
+        <v>149990000</v>
       </c>
       <c r="C239" s="2" t="inlineStr"/>
       <c r="D239" s="2" t="inlineStr">
@@ -9710,33 +9710,33 @@
       <c r="F239" s="2" t="inlineStr"/>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5080 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-18-max-hx-a2wi-1285vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-raider-18-max-hx-a2wj</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T04:49:17+00:00</t>
+          <t>2026-10-18T08:06:25+00:00</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Raider 18 Max HX A2WJ</t>
+          <t>Laptop Gaming MSI Stealth 16 AI+ B3WF 007VN (Ultra 9 386H | RTX 5060 | 32GB | 1TB | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>149990000</v>
+        <v>74490000</v>
       </c>
       <c r="C240" s="2" t="inlineStr"/>
       <c r="D240" s="2" t="inlineStr">
@@ -9748,33 +9748,33 @@
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ OLED 240Hz</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-raider-18-max-hx-a2wj</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wf-007vn</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T08:06:25+00:00</t>
+          <t>2026-10-10T07:28:24+00:00</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth 16 AI+ B3WF 007VN (Ultra 9 386H | RTX 5060 | 32GB | 1TB | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9 386H | RTX 5070 | 32GB | 1TB | 16 inch QHD+ 240Hz)</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>74490000</v>
+        <v>80590000</v>
       </c>
       <c r="C241" s="2" t="inlineStr"/>
       <c r="D241" s="2" t="inlineStr">
@@ -9786,33 +9786,33 @@
       <c r="F241" s="2" t="inlineStr"/>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5060 | Màn hình: 16" QHD+ OLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ OLED 240Hz</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wf-007vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T07:28:24+00:00</t>
+          <t>2026-10-18T07:13:15+00:00</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:20:13</t>
+          <t>2026-10-26 17:21:00</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9 386H | RTX 5070 | 32GB | 1TB | 16 inch QHD+ 240Hz)</t>
+          <t>Laptop Gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9 386H | RTX 5070 12GB | 32GB | 1TB | 16 inch)</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>80590000</v>
+        <v>81490000</v>
       </c>
       <c r="C242" s="2" t="inlineStr"/>
       <c r="D242" s="2" t="inlineStr">
@@ -9829,30 +9829,32 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wgx-051vn</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:13:15+00:00</t>
+          <t>2026-10-18T07:11:49+00:00</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 12:34:48</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9 386H | RTX 5070 12GB | 32GB | 1TB | 16 inch)</t>
+          <t>Laptop Gaming MSI Stealth 18 HX AI A2XWJG 073VN</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>81490000</v>
-      </c>
-      <c r="C243" s="2" t="inlineStr"/>
+        <v>140990000</v>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>140990000</v>
+      </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -9862,314 +9864,314 @@
       <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: RTX 5070 | Màn hình: 16" QHD+ OLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 24GB | Màn hình: 18" UHD+ MiniLED 120Hz</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-16-ai-b3wgx-051vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-18-hx-ai-a2xwjg-073vn</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:11:49+00:00</t>
+          <t>2026-10-18T07:15:18+00:00</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth 18 HX AI A2XWJG 073VN</t>
+          <t>Laptop Gaming MSI Stealth A16 Mercedes AMG AI+ A3XWGGG 032VN (AMD Ryzen AI 9 HX 370 | RTX 5070 | 32GB | 2TB | 16 inch QHD+ OLED 240Hz)</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>140990000</v>
+        <v>77890000</v>
       </c>
       <c r="C244" s="2" t="n">
-        <v>140990000</v>
+        <v>79990000</v>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr"/>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 24GB | Màn hình: 18" UHD+ MiniLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen AI 9 HX370 | RAM: 32GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-18-hx-ai-a2xwjg-073vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-stealth-a16-mercedes-amg-ai-a3xwggg-032vn</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:15:18+00:00</t>
+          <t>2026-10-18T07:15:31+00:00</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Stealth A16 Mercedes AMG AI+ A3XWGGG 032VN (AMD Ryzen AI 9 HX 370 | RTX 5070 | 32GB | 2TB | 16 inch QHD+ OLED 240Hz)</t>
+          <t>Laptop Gaming MSI Sword 16 HX B14VGKG 466VN (20th Edition)</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>77890000</v>
+        <v>37890000</v>
       </c>
       <c r="C245" s="2" t="n">
-        <v>79990000</v>
+        <v>43990000</v>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr"/>
       <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen AI 9 HX370 | RAM: 32GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-stealth-a16-mercedes-amg-ai-a3xwggg-032vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-sword-16-hx-b14vgkg-466vn-20th-edition</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:15:31+00:00</t>
+          <t>2026-10-18T07:37:12+00:00</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Sword 16 HX B14VGKG 466VN (20th Edition)</t>
+          <t>Laptop Gaming MSI Thin 15 B13UC 3247VN</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>37890000</v>
+        <v>21990000</v>
       </c>
       <c r="C246" s="2" t="n">
-        <v>43990000</v>
+        <v>24590000</v>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr"/>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 14650HX | RAM: 16GB DDR5 | VGA: RTX 4070 | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR4 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-sword-16-hx-b14vgkg-466vn-20th-edition</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-thin-15-b13uc-3247vn</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:37:12+00:00</t>
+          <t>2026-10-20T02:33:47+00:00</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Thin 15 B13UC 3247VN</t>
+          <t>Laptop Gaming MSI Titan 18 HX A2WJ 1200VN (Ultra 9 290HX Plus | RTX 5090 | 96GB | 2TB | UHD)</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>21990000</v>
+        <v>192990000</v>
       </c>
       <c r="C247" s="2" t="n">
-        <v>24590000</v>
+        <v>199000000</v>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr"/>
       <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i5 13420H | RAM: 8GB DDR4 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 96GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 240Hz</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-thin-15-b13uc-3247vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-titan-18-hx-a2wj-1200vn</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T02:33:47+00:00</t>
+          <t>2026-10-18T07:31:08+00:00</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Titan 18 HX A2WJ 1200VN (Ultra 9 290HX Plus | RTX 5090 | 96GB | 2TB | UHD)</t>
+          <t>Laptop Gaming MSI Titan 18 HX Dragon Edition Draco Epic A2W 1245VN</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>192990000</v>
-      </c>
-      <c r="C248" s="2" t="n">
-        <v>199000000</v>
-      </c>
+        <v>212990000</v>
+      </c>
+      <c r="C248" s="2" t="inlineStr"/>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr"/>
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 96GB DDR5 | Ổ cứng: 2TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 96GB DDR5 | Ổ cứng: 4TB SSD | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 240Hz</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-titan-18-hx-a2wj-1200vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-titan-18-hx-dragon-edition-draco-epic-a2w-1245vn</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:31:08+00:00</t>
+          <t>2026-10-18T07:14:40+00:00</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Titan 18 HX Dragon Edition Draco Epic A2W 1245VN</t>
+          <t>Laptop Gaming MSI Titan 18 HX AI A2XWJG 034VN Dragon Edition Norse Myth</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>212990000</v>
-      </c>
-      <c r="C249" s="2" t="inlineStr"/>
+        <v>174990000</v>
+      </c>
+      <c r="C249" s="2" t="n">
+        <v>184990000</v>
+      </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr"/>
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 290HX Plus | RAM: 96GB DDR5 | Ổ cứng: 4TB SSD | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 285HX | RAM: 96GB DDR5 | Ổ cứng: 6TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-titan-18-hx-dragon-edition-draco-epic-a2w-1245vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-titan-18hx-ai-a2xwjg-034vn-dragon-edition-norse-myth</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:14:40+00:00</t>
+          <t>2026-10-18T07:15:55+00:00</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Titan 18 HX AI A2XWJG 034VN Dragon Edition Norse Myth</t>
+          <t>Laptop Gaming MSI Vector 16 HX AI A2XWHG 010VN</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>174990000</v>
+        <v>63490000</v>
       </c>
       <c r="C250" s="2" t="n">
-        <v>184990000</v>
+        <v>69990000</v>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr"/>
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 285HX | RAM: 96GB DDR5 | Ổ cứng: 6TB | VGA: RTX 5090 | Màn hình: 18" UHD+ MiniLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-titan-18hx-ai-a2xwjg-034vn-dragon-edition-norse-myth</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-vector-16-hx-ai-a2xwhg-010vn</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:15:55+00:00</t>
+          <t>2026-08-03T04:28:37+00:00</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Vector 16 HX AI A2XWHG 010VN</t>
+          <t>Laptop Gaming MSI Vector 16 HX AI A2XWJG 470VN (Ultra 9 | RTX 5090 | 32GB | 1TB | QHD)</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>63490000</v>
+        <v>108990000</v>
       </c>
       <c r="C251" s="2" t="n">
-        <v>69990000</v>
+        <v>119990000</v>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
@@ -10180,73 +10182,71 @@
       <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 255HX | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | VGA: RTX 5070 Ti | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5090 24GB | Màn hình: 16" QHD+ 240Hz</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-vector-16-hx-ai-a2xwhg-010vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-vector-16-hx-ai-a2xwjg-470vn</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T04:28:37+00:00</t>
+          <t>2026-10-18T07:36:56+00:00</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Vector 16 HX AI A2XWJG 470VN (Ultra 9 | RTX 5090 | 32GB | 1TB | QHD)</t>
+          <t>Laptop Gaming MSI Vector GP68 HX 12VH 070VN</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>108990000</v>
-      </c>
-      <c r="C252" s="2" t="n">
-        <v>119990000</v>
-      </c>
+        <v>61990000</v>
+      </c>
+      <c r="C252" s="2" t="inlineStr"/>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr"/>
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 275HX | RAM: 32GB DDR5 | Ổ cứng: 1TB Gen 4 | VGA: RTX 5090 24GB | Màn hình: 16" QHD+ 240Hz</t>
+          <t>Thương hiệu: MSI | CPU: i9 12900HX | RAM: 16GB DDR5 | VGA: RTX 4080 | Màn hình: 16" FHD+ 144Hz</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-vector-16-hx-ai-a2xwjg-470vn</t>
+          <t>https://xgear.net/products/laptop-gaming-msi-vector-gp68-hx-12vh-070vn</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:36:56+00:00</t>
+          <t>2026-10-18T07:33:33+00:00</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Vector GP68 HX 12VH 070VN</t>
+          <t>Laptop Gaming OMEN MAX 16 16-ah0186TX</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>61990000</v>
+        <v>94990000</v>
       </c>
       <c r="C253" s="2" t="inlineStr"/>
       <c r="D253" s="2" t="inlineStr">
@@ -10258,309 +10258,309 @@
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i9 12900HX | RAM: 16GB DDR5 | VGA: RTX 4080 | Màn hình: 16" FHD+ 144Hz</t>
+          <t>Thương hiệu: HP | CPU: Ultra 7 255HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-msi-vector-gp68-hx-12vh-070vn</t>
+          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0186tx</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:33:33+00:00</t>
+          <t>2026-06-02T13:15:28+00:00</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 16-ah0186TX</t>
+          <t>Laptop Gaming OMEN MAX 16 16-ah0212TX C1WR1PA</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>94990000</v>
-      </c>
-      <c r="C254" s="2" t="inlineStr"/>
+        <v>137990000</v>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>139000000</v>
+      </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr"/>
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: Ultra 7 255HX | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5080 | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: HP | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5090 | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0186tx</t>
+          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0212tx</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02T13:15:28+00:00</t>
+          <t>2026-10-17T11:07:39+00:00</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 16-ah0212TX C1WR1PA</t>
+          <t>Laptop Gaming OMEN MAX 16 16-ah0213TX C1WR2PA</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>137990000</v>
-      </c>
-      <c r="C255" s="2" t="n">
-        <v>139000000</v>
-      </c>
+        <v>129990000</v>
+      </c>
+      <c r="C255" s="2" t="inlineStr"/>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr"/>
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5090 | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: HP | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5080 | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0212tx</t>
+          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0213tx</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T11:07:39+00:00</t>
+          <t>2026-09-02T14:51:19+00:00</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming OMEN MAX 16 16-ah0213TX C1WR2PA</t>
+          <t>Laptop Gaming Gigabyte A5 K1 AVN1030SB</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>129990000</v>
-      </c>
-      <c r="C256" s="2" t="inlineStr"/>
+        <v>17290000</v>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>23490000</v>
+      </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr"/>
       <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: Ultra 9 275HX | RAM: 64GB DDR5 | Ổ cứng: 2TB SSD | VGA: RTX 5080 | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: R5 5600H | RAM: 8GB DDR4 | VGA: RTX 3060 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gaming-omen-max-16-16-ah0213tx</t>
+          <t>https://xgear.net/products/laptop-gigabyte-a5-k1-avn1030sb</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:51:19+00:00</t>
+          <t>2026-04-08T03:48:41+00:00</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Gigabyte A5 K1 AVN1030SB</t>
+          <t>Laptop Gigabyte AERO X16 1VH93VNC64AH (Ryzen AI 7 | RTX 5060 | 32GB | 1TB | sRGB 100%)</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>17290000</v>
+        <v>37990000</v>
       </c>
       <c r="C257" s="2" t="n">
-        <v>23490000</v>
+        <v>39990000</v>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr"/>
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: R5 5600H | RAM: 8GB DDR4 | VGA: RTX 3060 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen Ai 7 350 | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-a5-k1-avn1030sb</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-1vh93vnc64ah</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08T03:48:41+00:00</t>
+          <t>2026-09-18T14:12:38+00:00</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 1VH93VNC64AH (Ryzen AI 7 | RTX 5060 | 32GB | 1TB | sRGB 100%)</t>
+          <t>Laptop Gigabyte AERO X16 1VH93VNC94DH (Ryzen AI 7 350 | RTX 5060 | 16GB | 1TB | sRGB 100%)</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>37990000</v>
+        <v>39990000</v>
       </c>
       <c r="C258" s="2" t="n">
         <v>39990000</v>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr"/>
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen Ai 7 350 | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" WQXGA 165Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen Ai 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-1vh93vnc64ah</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-1vh93vnc94dh</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T14:12:38+00:00</t>
+          <t>2026-10-18T06:19:08+00:00</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 1VH93VNC94DH (Ryzen AI 7 350 | RTX 5060 | 16GB | 1TB | sRGB 100%)</t>
+          <t>Laptop Gigabyte AERO X16 4WHN3VNC93AH (R9 AI 465 | RTX 5070 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
         <v>39990000</v>
       </c>
       <c r="C259" s="2" t="n">
-        <v>39990000</v>
+        <v>49990000</v>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr"/>
       <c r="F259" s="2" t="inlineStr"/>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen Ai 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" WQXGA 165Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 9 465 | RAM: 16GB DDR5 | Ổ cứng: 512 GB SSD | VGA: RTX 5070 | Màn hình: 16" WQXGA 165Hz</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-1vh93vnc94dh</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-4whn3vnc93ah</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T06:19:08+00:00</t>
+          <t>2026-10-18T05:35:12+00:00</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 4WHN3VNC93AH (R9 AI 465 | RTX 5070 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop Gigabyte AERO X16 EG61H-1VH93MY894AH  (Ryzen AI 7 350 | RTX 5060 | 16GB | 1TB | sRGB 100%)</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C260" s="2" t="n">
-        <v>49990000</v>
-      </c>
+        <v>38990000</v>
+      </c>
+      <c r="C260" s="2" t="inlineStr"/>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr"/>
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 9 465 | RAM: 16GB DDR5 | Ổ cứng: 512 GB SSD | VGA: RTX 5070 | Màn hình: 16" WQXGA 165Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" FHD+ 165Hz</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-4whn3vnc93ah</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-eg61h-1vh93my894ah</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:35:12+00:00</t>
+          <t>2026-09-19T12:56:52+00:00</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 EG61H-1VH93MY894AH  (Ryzen AI 7 350 | RTX 5060 | 16GB | 1TB | sRGB 100%)</t>
+          <t>Laptop Gigabyte AERO X16 EG61H-1VH93VNC94AH (Ryzen AI 7 | RTX 5060 | 16GB | 1TB | QHD+| sRGB 100%)</t>
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>38990000</v>
+        <v>40590000</v>
       </c>
       <c r="C261" s="2" t="inlineStr"/>
       <c r="D261" s="2" t="inlineStr">
@@ -10572,33 +10572,33 @@
       <c r="F261" s="2" t="inlineStr"/>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16" FHD+ 165Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16"QHD+ 165Hz</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-eg61h-1vh93my894ah</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-eg61h-1vh93vnc94ah</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:56:52+00:00</t>
+          <t>2026-10-18T05:33:01+00:00</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte AERO X16 EG61H-1VH93VNC94AH (Ryzen AI 7 | RTX 5060 | 16GB | 1TB | QHD+| sRGB 100%)</t>
+          <t>Laptop Gigabyte Aorus Master 16 6XJM4VNE64SH (R9 9955HX3D | RTX 5070 Ti | 32GB | 1TB | OLED)</t>
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>40590000</v>
+        <v>79990000</v>
       </c>
       <c r="C262" s="2" t="inlineStr"/>
       <c r="D262" s="2" t="inlineStr">
@@ -10610,34 +10610,32 @@
       <c r="F262" s="2" t="inlineStr"/>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: Ryzen AI 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5060 | Màn hình: 16"QHD+ 165Hz</t>
+          <t>Thương hiệu: Gigabyte | CPU: R9 9955HX3D | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti | Màn hình: 16" 2.5K OLED 240Hz</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aero-x16-eg61h-1vh93vnc94ah</t>
+          <t>https://xgear.net/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T05:33:01+00:00</t>
+          <t>2026-10-18T10:19:03+00:00</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gigabyte Aorus Master 16 6XJM4VNE64SH (R9 9955HX3D | RTX 5070 Ti | 32GB | 1TB | OLED)</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="n">
-        <v>79990000</v>
-      </c>
+          <t>Laptop Gaming HP Victus 16-s1146AX AZ0D1PA</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr"/>
       <c r="C263" s="2" t="inlineStr"/>
       <c r="D263" s="2" t="inlineStr">
         <is>
@@ -10648,109 +10646,111 @@
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Gigabyte | CPU: R9 9955HX3D | RAM: 32GB DDR5 | Ổ cứng: 1TB SSD | VGA: RTX 5070 Ti | Màn hình: 16" 2.5K OLED 240Hz</t>
+          <t>Thương hiệu: HP | CPU: R5 8460H | RAM: 16GB DDR5 | Ổ cứng: 512SSD | VGA: RTX 4050 8GB</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh</t>
+          <t>https://xgear.net/products/laptop-hp-victus-16-s1146ax-az0d1pa</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T10:19:03+00:00</t>
+          <t>2026-07-29T10:26:36+00:00</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming HP Victus 16-s1146AX AZ0D1PA</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr"/>
-      <c r="C264" s="2" t="inlineStr"/>
+          <t>Laptop Lenovo LOQ Essential 15IAX9E 83LK0079VN (i5-12450HX, RTX 3050 6GB, 100% sRGB)</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>22990000</v>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>23990000</v>
+      </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr"/>
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: HP | CPU: R5 8460H | RAM: 16GB DDR5 | Ổ cứng: 512SSD | VGA: RTX 4050 8GB</t>
+          <t>Thương hiệu: Lenovo | CPU: i5 12450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-hp-victus-16-s1146ax-az0d1pa</t>
+          <t>https://xgear.net/products/laptop-lenovo-loq-essential-15iax9e-83lk0079vn</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T10:26:36+00:00</t>
+          <t>2026-09-18T13:40:37+00:00</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo LOQ Essential 15IAX9E 83LK0079VN (i5-12450HX, RTX 3050 6GB, 100% sRGB)</t>
+          <t>Laptop LENOVO Yoga Pro 7 15ASH11 83W5000SVN (Ryzen AI Max+ 388 | AMD Radeon 8060S | 32GB | 512 GB | OLED)</t>
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C265" s="2" t="n">
-        <v>23990000</v>
-      </c>
+        <v>62990000</v>
+      </c>
+      <c r="C265" s="2" t="inlineStr"/>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr"/>
       <c r="F265" s="2" t="inlineStr"/>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i5 12450HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Ryzen AI Max+ 388 | RAM: 32GB | Ổ cứng: 512GB SSD | VGA: RTX 5050 8GB | Màn hình: 15.3" WQXGA</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-loq-essential-15iax9e-83lk0079vn</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15ash11-83w5000svn</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:40:37+00:00</t>
+          <t>2026-10-23T05:22:17+00:00</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Laptop LENOVO Yoga Pro 7 15ASH11 83W5000SVN (Ryzen AI Max+ 388 | AMD Radeon 8060S | 32GB | 512 GB | OLED)</t>
+          <t>Laptop LENOVO Yoga Pro 7 15IPH11 83SN000BVN (Ultra 7 356H | RTX 5050 | 32GB | 1TB | 2.5K)</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>62990000</v>
+        <v>71990000</v>
       </c>
       <c r="C266" s="2" t="inlineStr"/>
       <c r="D266" s="2" t="inlineStr">
@@ -10762,33 +10762,33 @@
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ryzen AI Max+ 388 | RAM: 32GB | Ổ cứng: 512GB SSD | VGA: RTX 5050 8GB | Màn hình: 15.3" WQXGA</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 32GB | Ổ cứng: 1TB SSD | VGA: RTX 5050 8GB | Màn hình: 15.3" WUXGA 2.5K</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15ash11-83w5000svn</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15iph11-83sn000bvn</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T05:22:17+00:00</t>
+          <t>2026-10-23T05:23:17+00:00</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Laptop LENOVO Yoga Pro 7 15IPH11 83SN000BVN (Ultra 7 356H | RTX 5050 | 32GB | 1TB | 2.5K)</t>
+          <t>Laptop Lenovo Yoga Pro 7 15IPH11 83SN0059VN (Ultra 7 356H | RTX 5050 | 24GB | 512GB | OLED 2.5K 100%sRGB)</t>
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>71990000</v>
+        <v>76990000</v>
       </c>
       <c r="C267" s="2" t="inlineStr"/>
       <c r="D267" s="2" t="inlineStr">
@@ -10800,33 +10800,33 @@
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 32GB | Ổ cứng: 1TB SSD | VGA: RTX 5050 8GB | Màn hình: 15.3" WUXGA 2.5K</t>
+          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 24GB LPDDR5X | Ổ cứng: 512GB | VGA: RTX 5050 8GB | Màn hình: 15.3" 2.5K</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15iph11-83sn000bvn</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15iph11-83sn0059vn</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T05:23:17+00:00</t>
+          <t>2026-10-13T08:06:29+00:00</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Pro 7 15IPH11 83SN0059VN (Ultra 7 356H | RTX 5050 | 24GB | 512GB | OLED 2.5K 100%sRGB)</t>
+          <t>Laptop Lenovo Yoga Pro 9 15N1X11 83SR001HVN (Spark N1X | 64GB RAM | 1TB SSD | RTX Blackwell | 15.3 inch 2.8K OLED 165Hz)</t>
         </is>
       </c>
       <c r="B268" s="2" t="n">
-        <v>76990000</v>
+        <v>126990000</v>
       </c>
       <c r="C268" s="2" t="inlineStr"/>
       <c r="D268" s="2" t="inlineStr">
@@ -10838,34 +10838,32 @@
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Ultra 7 356H | RAM: 24GB LPDDR5X | Ổ cứng: 512GB | VGA: RTX 5050 8GB | Màn hình: 15.3" 2.5K</t>
+          <t>Thương hiệu: Lenovo | CPU: Nvidia N1x | RAM: 64GB DDR5 | Ổ cứng: 1TB | VGA: RTX Blackwell | Màn hình: 15.3" 2.8K 165Hz</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-7-15iph11-83sn0059vn</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-9-15n1x11-83sr001hvn</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:06:29+00:00</t>
+          <t>2026-10-17T13:13:43+00:00</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Pro 9 15N1X11 83SR001HVN (Spark N1X | 64GB RAM | 1TB SSD | RTX Blackwell | 15.3 inch 2.8K OLED 165Hz)</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="n">
-        <v>126990000</v>
-      </c>
+          <t>Laptop Lenovo Yoga Slim 7x Snapdragon X Elite/16GB/512GB/14.5 3K 90Hz/Touch/Win11</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr"/>
       <c r="C269" s="2" t="inlineStr"/>
       <c r="D269" s="2" t="inlineStr">
         <is>
@@ -10876,32 +10874,34 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Nvidia N1x | RAM: 64GB DDR5 | Ổ cứng: 1TB | VGA: RTX Blackwell | Màn hình: 15.3" 2.8K 165Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: Snapdragon X Elite | RAM: 16GB DDR5 | Ổ cứng: 512GB NVMe | VGA: Qualcomm Adreno | Màn hình: 14.5" 3K OLED</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-pro-9-15n1x11-83sr001hvn</t>
+          <t>https://xgear.net/products/laptop-lenovo-yoga-slim-7x-snapdragon-x-elite</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T13:13:43+00:00</t>
+          <t>2026-05-28T08:56:37+00:00</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7x Snapdragon X Elite/16GB/512GB/14.5 3K 90Hz/Touch/Win11</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr"/>
+          <t>Laptop Gaming MSI Cyborg 15 C13WEO-417VN</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>31990000</v>
+      </c>
       <c r="C270" s="2" t="inlineStr"/>
       <c r="D270" s="2" t="inlineStr">
         <is>
@@ -10912,111 +10912,111 @@
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: Snapdragon X Elite | RAM: 16GB DDR5 | Ổ cứng: 512GB NVMe | VGA: Qualcomm Adreno | Màn hình: 14.5" 3K OLED</t>
+          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-lenovo-yoga-slim-7x-snapdragon-x-elite</t>
+          <t>https://xgear.net/products/laptop-msi-cyborg-15-c13weo-417vn</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28T08:56:37+00:00</t>
+          <t>2026-10-25T02:30:57+00:00</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming MSI Cyborg 15 C13WEO-417VN</t>
+          <t>Laptop MSI Gaming GF63 Thin 11UC 1228VN i7 11800H/8GB/512GB/15.6"F 144Hz/RTX3050MaxQ 4GB/Win11</t>
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C271" s="2" t="inlineStr"/>
+        <v>16490000</v>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>20490000</v>
+      </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-20%</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 13620H | RAM: 16GB DDR4 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: i7 11800H | RAM: 8GB DDR4 | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-cyborg-15-c13weo-417vn</t>
+          <t>https://xgear.net/products/laptop-msi-gaming-gf63-thin-11uc-1228vn</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T02:30:57+00:00</t>
+          <t>2026-10-18T07:33:24+00:00</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Gaming GF63 Thin 11UC 1228VN i7 11800H/8GB/512GB/15.6"F 144Hz/RTX3050MaxQ 4GB/Win11</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Ultra 7 355 | 32GB | 1TB | Intel® Arc™ graphics | 16 inch)</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>16490000</v>
-      </c>
-      <c r="C272" s="2" t="n">
-        <v>20490000</v>
-      </c>
+        <v>43990000</v>
+      </c>
+      <c r="C272" s="2" t="inlineStr"/>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr"/>
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: i7 11800H | RAM: 8GB DDR4 | VGA: RTX 3050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 355H | RAM: 32GB DDR5 | Ổ cứng: 1TB | Màn hình: 16" FHD+ OLED 120Hz</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-gaming-gf63-thin-11uc-1228vn</t>
+          <t>https://xgear.net/products/laptop-msi-modern-16s-ai-g3mg-058vn</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:33:24+00:00</t>
+          <t>2026-10-18T07:40:24+00:00</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Ultra 7 355 | 32GB | 1TB | Intel® Arc™ graphics | 16 inch)</t>
+          <t>Laptop  MSI Modern 16S G3MG-016VN  (Core 7 350 | 16GB | 1TB | Intel® Arc™ graphics | 16inch)</t>
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>43990000</v>
+        <v>32990000</v>
       </c>
       <c r="C273" s="2" t="inlineStr"/>
       <c r="D273" s="2" t="inlineStr">
@@ -11028,33 +11028,33 @@
       <c r="F273" s="2" t="inlineStr"/>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 355H | RAM: 32GB DDR5 | Ổ cứng: 1TB | Màn hình: 16" FHD+ OLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Core 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | Màn hình: 16" FHD+ 120Hz</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-modern-16s-ai-g3mg-058vn</t>
+          <t>https://xgear.net/products/laptop-msi-modern-16s-g3mg-016vn</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:40:24+00:00</t>
+          <t>2026-10-18T07:40:15+00:00</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Laptop  MSI Modern 16S G3MG-016VN  (Core 7 350 | 16GB | 1TB | Intel® Arc™ graphics | 16inch)</t>
+          <t>Laptop MSI Prestige 13 AI+ A3MG-036VN (Ultra 9-386H | Arc Graphics | 32GB | 1TB | 13.3 inch)</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>32990000</v>
+        <v>50990000</v>
       </c>
       <c r="C274" s="2" t="inlineStr"/>
       <c r="D274" s="2" t="inlineStr">
@@ -11066,74 +11066,76 @@
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Core 7 350 | RAM: 16GB DDR5 | Ổ cứng: 1TB SSD | Màn hình: 16" FHD+ 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9-386H | RAM: 32GB LPDDR5x | VGA: Intel® Arc™ Graphics | Màn hình: 13.3" 2.8K OLED</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-modern-16s-g3mg-016vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-a3mg-036vn</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:40:15+00:00</t>
+          <t>2026-10-18T07:30:59+00:00</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ A3MG-036VN (Ultra 9-386H | Arc Graphics | 32GB | 1TB | 13.3 inch)</t>
+          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>50990000</v>
-      </c>
-      <c r="C275" s="2" t="inlineStr"/>
+        <v>33790000</v>
+      </c>
+      <c r="C275" s="2" t="n">
+        <v>34390000</v>
+      </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr"/>
       <c r="F275" s="2" t="inlineStr"/>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9-386H | RAM: 32GB LPDDR5x | VGA: Intel® Arc™ Graphics | Màn hình: 13.3" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 155H | RAM: 32GB DDR5 | VGA: Intel Arc 16GB | Màn hình: 13.3" 2.8K OLED</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-a3mg-036vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:30:59+00:00</t>
+          <t>2026-10-18T07:33:15+00:00</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI Evo A1MG 062VN</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 062VN</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>33790000</v>
+        <v>39990000</v>
       </c>
       <c r="C276" s="2" t="n">
-        <v>34390000</v>
+        <v>40990000</v>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
@@ -11144,73 +11146,71 @@
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 155H | RAM: 32GB DDR5 | VGA: Intel Arc 16GB | Màn hình: 13.3" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 288V | RAM: 32GB DDR5 | VGA: Intel® Arc™ Graphics | Màn hình: 13.3" 2.8K OLED</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-evo-a1mg-062vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-evo-a2vmg-062vn</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:33:15+00:00</t>
+          <t>2026-05-09T07:28:55+00:00</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 062VN</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7 355 | Arc Graphics | 32GB | 1TB | 14 inch)</t>
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C277" s="2" t="n">
-        <v>40990000</v>
-      </c>
+        <v>44990000</v>
+      </c>
+      <c r="C277" s="2" t="inlineStr"/>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 288V | RAM: 32GB DDR5 | VGA: Intel® Arc™ Graphics | Màn hình: 13.3" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 7 355 | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-13-ai-evo-a2vmg-062vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09T07:28:55+00:00</t>
+          <t>2026-10-18T07:34:56+00:00</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7 355 | Arc Graphics | 32GB | 1TB | 14 inch)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ D3MTG-021VN (Ultra 9 386H | Arc Graphics | 32 GB | 1TB | 14 inch)</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>44990000</v>
+        <v>52990000</v>
       </c>
       <c r="C278" s="2" t="inlineStr"/>
       <c r="D278" s="2" t="inlineStr">
@@ -11222,35 +11222,37 @@
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 7 355 | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-d3mtg-021vn</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:34:56+00:00</t>
+          <t>2026-10-18T07:34:46+00:00</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ D3MTG-021VN (Ultra 9 386H | Arc Graphics | 32 GB | 1TB | 14 inch)</t>
+          <t>Laptop MSI Prestige 14 AI Evo C1MG 080VN</t>
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>52990000</v>
-      </c>
-      <c r="C279" s="2" t="inlineStr"/>
+        <v>32990000</v>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>32990000</v>
+      </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
           <t>-0%</t>
@@ -11260,109 +11262,107 @@
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 386H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 5 125H | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-d3mtg-021vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-evo-c1mg-080vn</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:34:46+00:00</t>
+          <t>2026-10-18T07:32:51+00:00</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI Evo C1MG 080VN</t>
+          <t>Laptop MSI Prestige 14 AI Evo C1MG 081VN</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>32990000</v>
+        <v>28990000</v>
       </c>
       <c r="C280" s="2" t="n">
-        <v>32990000</v>
+        <v>30990000</v>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr"/>
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 5 125H | RAM: 32GB DDR5 | Ổ cứng: 512GB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 5 125H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: Intel Arc Graphics | Màn hình: 14" FHD+ 144Hz</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-evo-c1mg-080vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-evo-c1mg-081vn</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:32:51+00:00</t>
+          <t>2026-10-13T07:19:14+00:00</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI Evo C1MG 081VN</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent Van Gogh Edition Starry Night Over the Rhone - 260VN (Ultra X9 378H | Intel Arc B390 | 32GB | 1TB | 14 inch FHD+ OLED)</t>
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C281" s="2" t="n">
-        <v>30990000</v>
-      </c>
+        <v>57490000</v>
+      </c>
+      <c r="C281" s="2" t="inlineStr"/>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr"/>
       <c r="F281" s="2" t="inlineStr"/>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 5 125H | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: Intel Arc Graphics | Màn hình: 14" FHD+ 144Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra 9 378H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-ai-evo-c1mg-081vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:19:14+00:00</t>
+          <t>2026-10-18T07:36:20+00:00</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent Van Gogh Edition Starry Night Over the Rhone - 260VN (Ultra X9 378H | Intel Arc B390 | 32GB | 1TB | 14 inch FHD+ OLED)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent Van Gogh Edition The Starry Night - 259VN (Ultra X9 378H | Intel Arc B390 | 32GB | 1TB | 14 inch FHD+ OLED)</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
@@ -11383,28 +11383,28 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-295vn</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:36:20+00:00</t>
+          <t>2026-10-18T07:36:37+00:00</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent Van Gogh Edition The Starry Night - 259VN (Ultra X9 378H | Intel Arc B390 | 32GB | 1TB | 14 inch FHD+ OLED)</t>
+          <t>Laptop MSI Prestige 16 AI+ C3MG-024VN (Ultra X9-388H | Intel Arc B390| 32GB | 1TB | 16 inch 2.8K OLED)</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>57490000</v>
+        <v>54990000</v>
       </c>
       <c r="C283" s="2" t="inlineStr"/>
       <c r="D283" s="2" t="inlineStr">
@@ -11416,33 +11416,33 @@
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra 9 378H | RAM: 32GB LPDDR5x | Ổ cứng: 1TB | VGA: Intel Arc Graphics | Màn hình: 14" 2.8K OLED</t>
+          <t>Thương hiệu: MSI | CPU: Ultra X9 388H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: Intel Arc B90 | Màn hình: 16" 2.8K OLED 120Hz</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-295vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-16-ai-c3mg-024vn</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T07:36:37+00:00</t>
+          <t>2026-10-15T04:41:17+00:00</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 16 AI+ C3MG-024VN (Ultra X9-388H | Intel Arc B390| 32GB | 1TB | 16 inch 2.8K OLED)</t>
+          <t>Laptop MSI Prestige N16 Flip AI+ C1XMT-016VN (Spark N1x | 128GB RAM | 2TB SSD | RTX Black Well | 16 inch OLED 120Hz)</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>54990000</v>
+        <v>220990000</v>
       </c>
       <c r="C284" s="2" t="inlineStr"/>
       <c r="D284" s="2" t="inlineStr">
@@ -11454,33 +11454,33 @@
       <c r="F284" s="2" t="inlineStr"/>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra X9 388H | RAM: 32GB DDR5 | Ổ cứng: 1TB | VGA: Intel Arc B90 | Màn hình: 16" 2.8K OLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Nvidia N1x | RAM: 128GB DDR5 | Ổ cứng: 2TB | VGA: RTX Blackwell | Màn hình: 16" UHD+ 120Hz</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-16-ai-c3mg-024vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-n16-flip-ai-c1xmt-016vn</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:41:17+00:00</t>
+          <t>2026-10-20T04:21:30+00:00</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige N16 Flip AI+ C1XMT-016VN (Spark N1x | 128GB RAM | 2TB SSD | RTX Black Well | 16 inch OLED 120Hz)</t>
+          <t>Laptop MSI Prestige N16 Flip AI+ C1XMT-017VN (Spark N1X | 64GB RAM | 2TB SSD | RTX Black Well | 16 inch 2.8K OLED 120Hz)</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>220990000</v>
+        <v>135990000</v>
       </c>
       <c r="C285" s="2" t="inlineStr"/>
       <c r="D285" s="2" t="inlineStr">
@@ -11492,33 +11492,33 @@
       <c r="F285" s="2" t="inlineStr"/>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Nvidia N1x | RAM: 128GB DDR5 | Ổ cứng: 2TB | VGA: RTX Blackwell | Màn hình: 16" UHD+ 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Nvidia N1x | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX Blackwell | Màn hình: 16" 2.8K OLED 120Hz</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-n16-flip-ai-c1xmt-016vn</t>
+          <t>https://xgear.net/products/laptop-msi-prestige-n16-flip-ai-c1xmt-017vn</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T04:21:30+00:00</t>
+          <t>2026-10-20T04:22:20+00:00</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige N16 Flip AI+ C1XMT-017VN (Spark N1X | 64GB RAM | 2TB SSD | RTX Black Well | 16 inch 2.8K OLED 120Hz)</t>
+          <t>Laptop MSI Venture 15 AI+ B3M-007VN (Ultra X7 358H | Intel Arc B390 | 16GB | 512GB | 100% sRGB)</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>135990000</v>
+        <v>34990000</v>
       </c>
       <c r="C286" s="2" t="inlineStr"/>
       <c r="D286" s="2" t="inlineStr">
@@ -11530,151 +11530,151 @@
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Nvidia N1x | RAM: 64GB DDR5 | Ổ cứng: 2TB | VGA: RTX Blackwell | Màn hình: 16" 2.8K OLED 120Hz</t>
+          <t>Thương hiệu: MSI | CPU: Ultra X7 358H | RAM: 16 GB | Ổ cứng: 512 GB SSD | VGA: Intel ARC B390 | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-prestige-n16-flip-ai-c1xmt-017vn</t>
+          <t>https://xgear.net/products/laptop-msi-venture-15-ai-b3m-007vn</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T04:22:20+00:00</t>
+          <t>2026-10-07T05:13:43+00:00</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Venture 15 AI+ B3M-007VN (Ultra X7 358H | Intel Arc B390 | 16GB | 512GB | 100% sRGB)</t>
+          <t>Laptop MSI Venture A14 AI+ A3HMG 004VN</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C287" s="2" t="inlineStr"/>
+        <v>24990000</v>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>25990000</v>
+      </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr"/>
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ultra X7 358H | RAM: 16 GB | Ổ cứng: 512 GB SSD | VGA: Intel ARC B390 | Màn hình: 15.6" FHD 144Hz 100% sRGB</t>
+          <t>Thương hiệu: MSI | CPU: Ryzen AI 5 340 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | Màn hình: 14" OLED 2.8K 120Hz</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-venture-15-ai-b3m-007vn</t>
+          <t>https://xgear.net/products/laptop-msi-venture-a14-ai-a3hmg-004vn</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T05:13:43+00:00</t>
+          <t>2026-10-18T08:03:56+00:00</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Venture A14 AI+ A3HMG 004VN</t>
+          <t>Laptop Gaming Lenovo LOQ 15IRX10 83JE00PEVN (Core i7-13650HX | RTX 5050 | 16GB | 512GB | 15.6 inch)</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>24990000</v>
+        <v>32990000</v>
       </c>
       <c r="C288" s="2" t="n">
-        <v>25990000</v>
+        <v>38990000</v>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr"/>
       <c r="F288" s="2" t="inlineStr"/>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: MSI | CPU: Ryzen AI 5 340 | RAM: 16GB DDR5 | Ổ cứng: 512GB SSD | Màn hình: 14" OLED 2.8K 120Hz</t>
+          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/laptop-msi-venture-a14-ai-a3hmg-004vn</t>
+          <t>https://xgear.net/products/lenovo-loq-15irx10-83je00pevn-core-i7-13650hx</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T08:03:56+00:00</t>
+          <t>2026-10-22T07:20:17+00:00</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>Laptop Gaming Lenovo LOQ 15IRX10 83JE00PEVN (Core i7-13650HX | RTX 5050 | 16GB | 512GB | 15.6 inch)</t>
+          <t>MacBook Air M5 13 inch 2026 10CPU 10GPU 16GB 1TB</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C289" s="2" t="n">
-        <v>38990000</v>
-      </c>
+        <v>42690000</v>
+      </c>
+      <c r="C289" s="2" t="inlineStr"/>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr"/>
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Lenovo | CPU: i7 13650HX | RAM: 16GB DDR5 | Ổ cứng: 512GB | VGA: RTX 5050 | Màn hình: 15.6" FHD 144Hz</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 16GB | Ổ cứng: 1TB | Màn hình: 13.6 inch</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/lenovo-loq-15irx10-83je00pevn-core-i7-13650hx</t>
+          <t>https://xgear.net/products/macbook-air-m5-13-inch-2026-10cpu-10gpu-16gb-1tb</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22T07:20:17+00:00</t>
+          <t>2026-06-26T12:03:05+00:00</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>MacBook Air M5 13 inch 2026 10CPU 10GPU 16GB 1TB</t>
+          <t>MacBook Air M5 13 inch 2026 10CPU 10GPU 24GB 1TB</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>42690000</v>
+        <v>45990000</v>
       </c>
       <c r="C290" s="2" t="inlineStr"/>
       <c r="D290" s="2" t="inlineStr">
@@ -11686,33 +11686,33 @@
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 16GB | Ổ cứng: 1TB | Màn hình: 13.6 inch</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 13.6 inch</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-air-m5-13-inch-2026-10cpu-10gpu-16gb-1tb</t>
+          <t>https://xgear.net/products/macbook-air-m5-13-inch-2026-10cpu-10gpu-24gb-1tb</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T12:03:05+00:00</t>
+          <t>2026-10-18T09:26:38+00:00</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>MacBook Air M5 13 inch 2026 10CPU 10GPU 24GB 1TB</t>
+          <t>MacBook Air M5 15 inch 2026 10CPU 10GPU 16GB 1TB</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>45990000</v>
+        <v>47990000</v>
       </c>
       <c r="C291" s="2" t="inlineStr"/>
       <c r="D291" s="2" t="inlineStr">
@@ -11724,33 +11724,33 @@
       <c r="F291" s="2" t="inlineStr"/>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 13.6 inch</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 16GB | Ổ cứng: 1TB | Màn hình: 15.3 inches</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-air-m5-13-inch-2026-10cpu-10gpu-24gb-1tb</t>
+          <t>https://xgear.net/products/macbook-air-m5-15-inch-2026-10cpu-10gpu-16gb-1tb</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T09:26:38+00:00</t>
+          <t>2026-06-26T12:09:01+00:00</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>MacBook Air M5 15 inch 2026 10CPU 10GPU 16GB 1TB</t>
+          <t>MacBook Air M5 15 inch 2026 10CPU 10GPU 24GB 1TB</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>47990000</v>
+        <v>52990000</v>
       </c>
       <c r="C292" s="2" t="inlineStr"/>
       <c r="D292" s="2" t="inlineStr">
@@ -11762,33 +11762,33 @@
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 16GB | Ổ cứng: 1TB | Màn hình: 15.3 inches</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 15.3 inches</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-air-m5-15-inch-2026-10cpu-10gpu-16gb-1tb</t>
+          <t>https://xgear.net/products/macbook-air-m5-15-inch-2026-10cpu-10gpu-24gb-1tb</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T12:09:01+00:00</t>
+          <t>2026-06-26T12:31:23+00:00</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>MacBook Air M5 15 inch 2026 10CPU 10GPU 24GB 1TB</t>
+          <t>MacBook Neo 13 inch A18 Pro 8GB-256GB</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>52990000</v>
+        <v>17490000</v>
       </c>
       <c r="C293" s="2" t="inlineStr"/>
       <c r="D293" s="2" t="inlineStr">
@@ -11800,33 +11800,33 @@
       <c r="F293" s="2" t="inlineStr"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 15.3 inches</t>
+          <t>Thương hiệu: Apple | CPU: Apple A18 Pro | RAM: 8GB | Ổ cứng: 256TB | Màn hình: 13 inch</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-air-m5-15-inch-2026-10cpu-10gpu-24gb-1tb</t>
+          <t>https://xgear.net/products/macbook-neo-13-inch-a18-pro-2026-6cpu-5gpu-8gb-256gb</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T12:31:23+00:00</t>
+          <t>2026-10-18T09:19:17+00:00</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>MacBook Neo 13 inch A18 Pro 8GB-256GB</t>
+          <t>MacBook Neo 13 inch A18 Pro 8GB-512GB</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>17490000</v>
+        <v>21890000</v>
       </c>
       <c r="C294" s="2" t="inlineStr"/>
       <c r="D294" s="2" t="inlineStr">
@@ -11838,33 +11838,33 @@
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple A18 Pro | RAM: 8GB | Ổ cứng: 256TB | Màn hình: 13 inch</t>
+          <t>Thương hiệu: Apple</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-neo-13-inch-a18-pro-2026-6cpu-5gpu-8gb-256gb</t>
+          <t>https://xgear.net/products/macbook-neo-13-inch-a18-pro-8gb-512gb</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T09:19:17+00:00</t>
+          <t>2026-10-20T11:45:35+00:00</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>MacBook Neo 13 inch A18 Pro 8GB-512GB</t>
+          <t>MacBook Pro M5 Max 16 inch 2026 18CPU 32GPU 36GB 2TB</t>
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>21890000</v>
+        <v>116890000</v>
       </c>
       <c r="C295" s="2" t="inlineStr"/>
       <c r="D295" s="2" t="inlineStr">
@@ -11876,33 +11876,33 @@
       <c r="F295" s="2" t="inlineStr"/>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 36GB | Ổ cứng: 2TB | Màn hình: 16.2 inch</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-neo-13-inch-a18-pro-8gb-512gb</t>
+          <t>https://xgear.net/products/macbook-pro-m5-max-16-inch-18cpu-32gpu-36gb-2tb</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:45:35+00:00</t>
+          <t>2026-10-20T11:57:28+00:00</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>MacBook Pro M5 Max 16 inch 2026 18CPU 32GPU 36GB 2TB</t>
+          <t>MacBook Pro M5 Pro 14 inch 2026 15CPU 16GPU 24GB 1TB</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>116890000</v>
+        <v>65990000</v>
       </c>
       <c r="C296" s="2" t="inlineStr"/>
       <c r="D296" s="2" t="inlineStr">
@@ -11914,33 +11914,33 @@
       <c r="F296" s="2" t="inlineStr"/>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 36GB | Ổ cứng: 2TB | Màn hình: 16.2 inch</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 36GB | Ổ cứng: 2TB | Màn hình: 14.2 inch</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-pro-m5-max-16-inch-18cpu-32gpu-36gb-2tb</t>
+          <t>https://xgear.net/products/macbook-pro-m5-pro-14-inch-15cpu-16gpu-24gb-1tb</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:57:28+00:00</t>
+          <t>2026-10-18T11:06:01+00:00</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>MacBook Pro M5 Pro 14 inch 2026 15CPU 16GPU 24GB 1TB</t>
+          <t>MacBook Pro M5 Pro 14 inch 2026 18CPU 20GPU 24GB 2TB</t>
         </is>
       </c>
       <c r="B297" s="2" t="n">
-        <v>65990000</v>
+        <v>85890000</v>
       </c>
       <c r="C297" s="2" t="inlineStr"/>
       <c r="D297" s="2" t="inlineStr">
@@ -11952,33 +11952,33 @@
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 36GB | Ổ cứng: 2TB | Màn hình: 14.2 inch</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 24GB | Ổ cứng: 2TB | Màn hình: 16.2 inch</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-pro-m5-pro-14-inch-15cpu-16gpu-24gb-1tb</t>
+          <t>https://xgear.net/products/macbook-pro-m5-pro-14-inch-2026-18cpu-20gpu-24gb-2tb</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T11:06:01+00:00</t>
+          <t>2026-10-18T11:16:22+00:00</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>MacBook Pro M5 Pro 14 inch 2026 18CPU 20GPU 24GB 2TB</t>
+          <t>MacBook Pro M5 Pro 16 inch 2026 18CPU 20GPU 24GB 1TB</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
-        <v>85890000</v>
+        <v>79390000</v>
       </c>
       <c r="C298" s="2" t="inlineStr"/>
       <c r="D298" s="2" t="inlineStr">
@@ -11990,60 +11990,22 @@
       <c r="F298" s="2" t="inlineStr"/>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 24GB | Ổ cứng: 2TB | Màn hình: 16.2 inch</t>
+          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 16.2 inch</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>https://xgear.net/products/macbook-pro-m5-pro-14-inch-2026-18cpu-20gpu-24gb-2tb</t>
+          <t>https://xgear.net/products/macbook-pro-m5-pro-16-inch-18cpu-20gpu-24gb-1tb</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18T11:16:22+00:00</t>
+          <t>2026-06-26T12:42:09+00:00</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 08:19:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>MacBook Pro M5 Pro 16 inch 2026 18CPU 20GPU 24GB 1TB</t>
-        </is>
-      </c>
-      <c r="B299" s="2" t="n">
-        <v>79390000</v>
-      </c>
-      <c r="C299" s="2" t="inlineStr"/>
-      <c r="D299" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
-      <c r="E299" s="2" t="inlineStr"/>
-      <c r="F299" s="2" t="inlineStr"/>
-      <c r="G299" s="2" t="inlineStr">
-        <is>
-          <t>Thương hiệu: Apple | CPU: Apple M5 Pro | RAM: 24GB | Ổ cứng: 1TB | Màn hình: 16.2 inch</t>
-        </is>
-      </c>
-      <c r="H299" s="2" t="inlineStr">
-        <is>
-          <t>https://xgear.net/products/macbook-pro-m5-pro-16-inch-18cpu-20gpu-24gb-1tb</t>
-        </is>
-      </c>
-      <c r="I299" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26T12:42:09+00:00</t>
-        </is>
-      </c>
-      <c r="J299" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26 08:19:53</t>
+          <t>2026-10-26 17:20:44</t>
         </is>
       </c>
     </row>
